--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,1147 +429,1147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>entityid</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>teamid</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>shortname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>rowid</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>teamabbreviation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>secondsplayed</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gamesplayed</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>plusminus</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>offposs</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>defposs</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>penaltyoffposs</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>penaltydefposs</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>secondchanceoffposs</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>totalposs</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>atrimfgm</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>atrimfga</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimfgm</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimfga</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimfgm</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimfga</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangefgm</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangefga</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>longmidrangefgm</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>longmidrangefga</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>corner3fgm</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>corner3fga</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3fgm</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3fga</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3fgm</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3fga</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>arc3fgm</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>arc3fga</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3fgm</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3fga</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3fgm</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3fga</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>fg2m</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>fg2a</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>fg3m</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>fg3a</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ftpoints</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>opponentpoints</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg2m</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg2a</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg3m</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg3a</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>secondchanceftpoints</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>secondchancepoints</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg2m</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg2a</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg3m</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg3a</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>penaltyftpoints</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>penaltypoints</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>ptsassisted2s</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>ptsunassisted2s</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>ptsassisted3s</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>ptsunassisted3s</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>ptsputbacks</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>nonheavearc3fga</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>nonheavearc3fgm</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>fg2ablocked</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>fg3ablocked</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>twoptassists</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>threeptassists</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>assists</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>arc3assists</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>corner3assists</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>atrimassists</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangeassists</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>longmidrangeassists</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>assistpoints</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>offthreeptrebounds</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>offtwoptrebounds</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>ftoffrebounds</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>defthreeptrebounds</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>deftwoptrebounds</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>ftdefrebounds</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>defrebounds</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>offrebounds</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>rebounds</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>selforeb</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>steals</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>badpasssteals</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>lostballsteals</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>liveballturnovers</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>badpassoutofboundsturnovers</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>badpassturnovers</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>deadballturnovers</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>lostballoutofboundsturnovers</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>lostballturnovers</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>travels</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>turnovers</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>secondchanceturnovers</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>penaltyturnovers</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>shootingfouls</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>fouls</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>charge fouls</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>loose ball fouls</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>offensive fouls</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>foulsdrawn</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>charge fouls drawn</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>loose ball fouls drawn</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>offensive fouls drawn</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>fta</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>2pt and 1 free throw trips</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>3pt and 1 free throw trips</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>technical free throw trips</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>twoptshootingfoulsdrawn</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>threeptshootingfoulsdrawn</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>nonshootingfoulsdrawn</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>blocked2s</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>blocked3s</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>blockedarc3</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>blockedatrim</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>blockedcorner3</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>blockedlongmidrange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>blockedshortmidrange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>blocks</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>recoveredblocks</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>defensivegoaltends</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>offensivegoaltends</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>firstchancepoints</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>penaltypointsexcludingtakefouls</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>penaltyoffpossexcludingtakefouls</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>nonshootingpenaltynontakefouls</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>nonshootingpenaltynontakefoulsdrawn</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>assisted2spct</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>nonputbacksassisted2spct</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>assisted3spct</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>fg3pct</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg3pct</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg3pct</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>nonheavefg3pct</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>fg2pct</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg2pct</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg2pct</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>efgpct</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>secondchanceefgpct</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>penaltyefgpct</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>tspct</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>secondchancetspct</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>penaltytspct</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>fg3apct</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>fg3apctblocked</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>fg2apctblocked</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>atrimpctblocked</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangepctblocked</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>longmidrangepctblocked</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>corner3pctblocked</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>liveballturnoverpct</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>defftreboundpct</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>offftreboundpct</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>deftwoptreboundpct</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>offtwoptreboundpct</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>defthreeptreboundpct</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>offthreeptreboundpct</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>deffgreboundpct</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>offfgreboundpct</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>offatrimreboundpct</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>offshortmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>offlongmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>offarc3reboundpct</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>offcorner3reboundpct</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>defatrimreboundpct</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>defshortmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>deflongmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>defarc3reboundpct</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>defcorner3reboundpct</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>selforebpct</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>pace</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>blocksrecoveredpct</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>secondsperpossoff</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>secondsperpossdef</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>secondsexcludingorebsperpossoff</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>secondsexcludingorebsperpossdef</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>atrimfrequency</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>atrimaccuracy</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>unblockedatrimaccuracy</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>atrimpctassisted</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangefrequency</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>unblockedshortmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangepctassisted</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>longmidrangefrequency</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>longmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>unblockedlongmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>longmidrangepctassisted</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>corner3frequency</t>
         </is>
       </c>
-      <c r="GJ1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>corner3accuracy</t>
         </is>
       </c>
-      <c r="GK1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>unblockedcorner3accuracy</t>
         </is>
       </c>
-      <c r="GL1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>corner3pctassisted</t>
         </is>
       </c>
-      <c r="GM1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>arc3frequency</t>
         </is>
       </c>
-      <c r="GN1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>arc3accuracy</t>
         </is>
       </c>
-      <c r="GO1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>unblockedarc3accuracy</t>
         </is>
       </c>
-      <c r="GP1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>arc3pctassisted</t>
         </is>
       </c>
-      <c r="GQ1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimfrequency</t>
         </is>
       </c>
-      <c r="GR1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimaccuracy</t>
         </is>
       </c>
-      <c r="GS1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimpctassisted</t>
         </is>
       </c>
-      <c r="GT1" t="inlineStr">
+      <c r="GT1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3frequency</t>
         </is>
       </c>
-      <c r="GU1" t="inlineStr">
+      <c r="GU1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3accuracy</t>
         </is>
       </c>
-      <c r="GV1" t="inlineStr">
+      <c r="GV1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3pctassisted</t>
         </is>
       </c>
-      <c r="GW1" t="inlineStr">
+      <c r="GW1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3frequency</t>
         </is>
       </c>
-      <c r="GX1" t="inlineStr">
+      <c r="GX1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3accuracy</t>
         </is>
       </c>
-      <c r="GY1" t="inlineStr">
+      <c r="GY1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3pctassisted</t>
         </is>
       </c>
-      <c r="GZ1" t="inlineStr">
+      <c r="GZ1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimfrequency</t>
         </is>
       </c>
-      <c r="HA1" t="inlineStr">
+      <c r="HA1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimaccuracy</t>
         </is>
       </c>
-      <c r="HB1" t="inlineStr">
+      <c r="HB1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3frequency</t>
         </is>
       </c>
-      <c r="HC1" t="inlineStr">
+      <c r="HC1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3accuracy</t>
         </is>
       </c>
-      <c r="HD1" t="inlineStr">
+      <c r="HD1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3frequency</t>
         </is>
       </c>
-      <c r="HE1" t="inlineStr">
+      <c r="HE1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3accuracy</t>
         </is>
       </c>
-      <c r="HF1" t="inlineStr">
+      <c r="HF1" s="1" t="inlineStr">
         <is>
           <t>atrimfg3afrequency</t>
         </is>
       </c>
-      <c r="HG1" t="inlineStr">
+      <c r="HG1" s="1" t="inlineStr">
         <is>
           <t>nonheavearc3accuracy</t>
         </is>
       </c>
-      <c r="HH1" t="inlineStr">
+      <c r="HH1" s="1" t="inlineStr">
         <is>
           <t>shotqualityavg</t>
         </is>
       </c>
-      <c r="HI1" t="inlineStr">
+      <c r="HI1" s="1" t="inlineStr">
         <is>
           <t>secondchanceshotqualityavg</t>
         </is>
       </c>
-      <c r="HJ1" t="inlineStr">
+      <c r="HJ1" s="1" t="inlineStr">
         <is>
           <t>penaltyshotqualityavg</t>
         </is>
       </c>
-      <c r="HK1" t="inlineStr">
+      <c r="HK1" s="1" t="inlineStr">
         <is>
           <t>shootingfoulsdrawnpct</t>
         </is>
       </c>
-      <c r="HL1" t="inlineStr">
+      <c r="HL1" s="1" t="inlineStr">
         <is>
           <t>twoptshootingfoulsdrawnpct</t>
         </is>
       </c>
-      <c r="HM1" t="inlineStr">
+      <c r="HM1" s="1" t="inlineStr">
         <is>
           <t>threeptshootingfoulsdrawnpct</t>
         </is>
       </c>
-      <c r="HN1" t="inlineStr">
+      <c r="HN1" s="1" t="inlineStr">
         <is>
           <t>secondchancepointspct</t>
         </is>
       </c>
-      <c r="HO1" t="inlineStr">
+      <c r="HO1" s="1" t="inlineStr">
         <is>
           <t>penaltypointspct</t>
         </is>
       </c>
-      <c r="HP1" t="inlineStr">
+      <c r="HP1" s="1" t="inlineStr">
         <is>
           <t>avg2ptshotdistance</t>
         </is>
       </c>
-      <c r="HQ1" t="inlineStr">
+      <c r="HQ1" s="1" t="inlineStr">
         <is>
           <t>avg3ptshotdistance</t>
         </is>
       </c>
-      <c r="HR1" t="inlineStr">
+      <c r="HR1" s="1" t="inlineStr">
         <is>
           <t>penaltyoffposspct</t>
         </is>
       </c>
-      <c r="HS1" t="inlineStr">
+      <c r="HS1" s="1" t="inlineStr">
         <is>
           <t>stepoutofboundsturnovers</t>
         </is>
       </c>
-      <c r="HT1" t="inlineStr">
+      <c r="HT1" s="1" t="inlineStr">
         <is>
           <t>defensive 3 seconds violations</t>
         </is>
       </c>
-      <c r="HU1" t="inlineStr">
+      <c r="HU1" s="1" t="inlineStr">
         <is>
           <t>arc3pctblocked</t>
         </is>
@@ -5042,67 +5054,67 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>38040</v>
+        <v>40920</v>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>-22</v>
       </c>
       <c r="J7" t="n">
-        <v>1244</v>
+        <v>1342</v>
       </c>
       <c r="K7" t="n">
-        <v>1249</v>
+        <v>1349</v>
       </c>
       <c r="L7" t="n">
-        <v>318</v>
+        <v>361</v>
       </c>
       <c r="M7" t="n">
-        <v>404</v>
+        <v>455</v>
       </c>
       <c r="N7" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="O7" t="n">
-        <v>2493</v>
+        <v>2691</v>
       </c>
       <c r="P7" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="Q7" t="n">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="R7" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="S7" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="T7" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="U7" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="V7" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="W7" t="n">
-        <v>290</v>
+        <v>319</v>
       </c>
       <c r="X7" t="n">
         <v>41</v>
       </c>
       <c r="Y7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Z7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AA7" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AB7" t="n">
         <v>6</v>
@@ -5111,257 +5123,257 @@
         <v>17</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AF7" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="n">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="AH7" t="n">
         <v>15</v>
       </c>
       <c r="AI7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK7" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="AL7" t="n">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="AM7" t="n">
-        <v>743</v>
+        <v>789</v>
       </c>
       <c r="AN7" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="AO7" t="n">
-        <v>381</v>
+        <v>420</v>
       </c>
       <c r="AP7" t="n">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1429</v>
+        <v>1523</v>
       </c>
       <c r="AR7" t="n">
-        <v>1420</v>
+        <v>1545</v>
       </c>
       <c r="AS7" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AT7" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="AU7" t="n">
         <v>21</v>
       </c>
       <c r="AV7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AW7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AX7" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="AY7" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="AZ7" t="n">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="BA7" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="BB7" t="n">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="BC7" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="BD7" t="n">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="BE7" t="n">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="BF7" t="n">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="BG7" t="n">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="BH7" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="BI7" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="BJ7" t="n">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="BK7" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="BL7" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="BM7" t="n">
         <v>3</v>
       </c>
       <c r="BN7" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="BO7" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="BP7" t="n">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="BQ7" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="BR7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="BT7" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="BU7" t="n">
         <v>17</v>
       </c>
       <c r="BV7" t="n">
-        <v>781</v>
+        <v>833</v>
       </c>
       <c r="BW7" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="BX7" t="n">
+        <v>140</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>233</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>156</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>44</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>433</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>224</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>657</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>23</v>
+      </c>
+      <c r="CG7" t="n">
         <v>133</v>
       </c>
-      <c r="BY7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>219</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>147</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>36</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>402</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>209</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>611</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>19</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>126</v>
-      </c>
       <c r="CH7" t="n">
+        <v>77</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>56</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>111</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>27</v>
+      </c>
+      <c r="CL7" t="n">
         <v>74</v>
       </c>
-      <c r="CI7" t="n">
-        <v>52</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>101</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>26</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>69</v>
-      </c>
       <c r="CM7" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="CN7" t="n">
         <v>15</v>
       </c>
       <c r="CO7" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="CP7" t="n">
         <v>5</v>
       </c>
       <c r="CQ7" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="CR7" t="n">
         <v>28</v>
       </c>
       <c r="CS7" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="CT7" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="CU7" t="n">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="CV7" t="n">
         <v>3</v>
       </c>
       <c r="CW7" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="CX7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="CY7" t="n">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="CZ7" t="n">
         <v>2</v>
       </c>
       <c r="DA7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="DB7" t="n">
         <v>19</v>
       </c>
       <c r="DC7" t="n">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="DD7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="DE7" t="inlineStr"/>
       <c r="DF7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DG7" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="DH7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DI7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="DJ7" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="DK7" t="n">
         <v>7</v>
@@ -5370,7 +5382,7 @@
         <v>4</v>
       </c>
       <c r="DM7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DN7" t="n">
         <v>3</v>
@@ -5379,251 +5391,251 @@
         <v>3</v>
       </c>
       <c r="DP7" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="DQ7" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="DR7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DS7" t="n">
         <v>1</v>
       </c>
       <c r="DT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DU7" t="n">
-        <v>1231</v>
+        <v>1314</v>
       </c>
       <c r="DV7" t="n">
-        <v>364</v>
+        <v>406</v>
       </c>
       <c r="DW7" t="n">
-        <v>315</v>
+        <v>358</v>
       </c>
       <c r="DX7" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="DY7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.5235602094240838</v>
+        <v>0.5275</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.5586592178770949</v>
+        <v>0.5656836461126006</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.8782051282051282</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.3779527559055118</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.3620689655172414</v>
+        <v>0.3559322033898305</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.2989690721649484</v>
+        <v>0.3017241379310345</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.3779527559055118</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.5141318977119784</v>
+        <v>0.5069708491761724</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.494949494949495</v>
+        <v>0.4818181818181818</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.5187165775401069</v>
+        <v>0.4975609756097561</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.5320284697508897</v>
+        <v>0.5244003308519437</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.5127388535031847</v>
+        <v>0.5</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.4947183098591549</v>
+        <v>0.4813084112149533</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.5658207771609833</v>
+        <v>0.5592347314201619</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.5439560439560439</v>
+        <v>0.5304568527918782</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.5473372781065089</v>
+        <v>0.5365535248041775</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.3389679715302491</v>
+        <v>0.347394540942928</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.007874015748031496</v>
+        <v>0.007142857142857143</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.09152086137281291</v>
+        <v>0.09125475285171103</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.1135734072022161</v>
+        <v>0.1117021276595745</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.08620689655172414</v>
+        <v>0.0877742946708464</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.02173913043478261</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="EV7" t="inlineStr"/>
       <c r="EW7" t="n">
-        <v>0.4975369458128079</v>
+        <v>0.5091743119266054</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8301886792452831</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.1714285714285714</v>
+        <v>0.1891891891891892</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.5951417004048583</v>
+        <v>0.5864661654135338</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.3757062146892655</v>
+        <v>0.3664921465968586</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.6996805111821086</v>
+        <v>0.6934523809523809</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.3056768558951965</v>
+        <v>0.3019607843137255</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.6535714285714286</v>
+        <v>0.6461794019933554</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.3481989708404803</v>
+        <v>0.3406593406593407</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.4477611940298508</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.3604651162790697</v>
+        <v>0.34375</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.24</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.283132530120482</v>
+        <v>0.2780748663101604</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.3676470588235294</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.691358024691358</v>
+        <v>0.6705882352941176</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.5070422535211268</v>
+        <v>0.5095541401273885</v>
       </c>
       <c r="FM7" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.7033898305084746</v>
+        <v>0.6929133858267716</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.6883116883116883</v>
+        <v>0.6951219512195121</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.03696498054474708</v>
+        <v>0.04078014184397163</v>
       </c>
       <c r="FQ7" t="n">
-        <v>94.37223974763407</v>
+        <v>94.69794721407625</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.4647887323943662</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="FS7" t="n">
-        <v>15.09991961414791</v>
+        <v>15.0795827123696</v>
       </c>
       <c r="FT7" t="n">
-        <v>15.41689351481185</v>
+        <v>15.33224610822832</v>
       </c>
       <c r="FU7" t="n">
-        <v>14.38585209003215</v>
+        <v>14.36602086438152</v>
       </c>
       <c r="FV7" t="n">
-        <v>14.58462770216173</v>
+        <v>14.5232023721275</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.3211743772241993</v>
+        <v>0.3110008271298594</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.6260387811634349</v>
+        <v>0.625</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.70625</v>
+        <v>0.7035928143712575</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.5929203539823009</v>
+        <v>0.5914893617021276</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.2580071174377224</v>
+        <v>0.2638544251447477</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.396551724137931</v>
+        <v>0.3887147335423197</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.4339622641509434</v>
+        <v>0.4261168384879725</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.4260869565217391</v>
+        <v>0.4435483870967742</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.08185053380782918</v>
+        <v>0.07775020678246485</v>
       </c>
       <c r="GF7" t="n">
+        <v>0.4361702127659575</v>
+      </c>
+      <c r="GG7" t="n">
         <v>0.4456521739130435</v>
-      </c>
-      <c r="GG7" t="n">
-        <v>0.4555555555555555</v>
       </c>
       <c r="GH7" t="n">
         <v>0.4146341463414634</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.08629893238434164</v>
+        <v>0.08602150537634409</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.3402061855670103</v>
+        <v>0.3365384615384616</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.3402061855670103</v>
+        <v>0.3365384615384616</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.2526690391459075</v>
+        <v>0.261373035566584</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3908450704225352</v>
+        <v>0.3829113924050633</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.3950177935943061</v>
+        <v>0.3865814696485623</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.8558558558558559</v>
+        <v>0.8512396694214877</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.4140127388535032</v>
+        <v>0.4201183431952663</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.5076923076923077</v>
+        <v>0.5211267605633803</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.1082802547770701</v>
+        <v>0.1005917159763314</v>
       </c>
       <c r="GU7" t="n">
         <v>0.3529411764705883</v>
@@ -5632,70 +5644,70 @@
         <v>1</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.2611464968152866</v>
+        <v>0.2485207100591716</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="GY7" t="n">
         <v>0.9333333333333333</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.3908450704225352</v>
+        <v>0.3613707165109034</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.6306306306306306</v>
+        <v>0.6293103448275862</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.09507042253521127</v>
+        <v>0.102803738317757</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.2464788732394366</v>
+        <v>0.2585669781931464</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.3132530120481928</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.6601423487544484</v>
+        <v>0.6583953680727874</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.3908450704225352</v>
+        <v>0.3829113924050633</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.5542004014272971</v>
+        <v>0.5497948175787728</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.5432174311926605</v>
+        <v>0.5403324786324786</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.5698083629893239</v>
+        <v>0.5592921383647799</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.1090317331163548</v>
+        <v>0.108843537414966</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.1540284360189574</v>
+        <v>0.1547884187082405</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.01038961038961039</v>
+        <v>0.01176470588235294</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.1385584324702589</v>
+        <v>0.1372291529875246</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.2589223233030091</v>
+        <v>0.2705187130663165</v>
       </c>
       <c r="HP7" t="n">
-        <v>6.267833109017497</v>
+        <v>6.27743979721166</v>
       </c>
       <c r="HQ7" t="n">
-        <v>25.66358839050132</v>
+        <v>25.75358851674641</v>
       </c>
       <c r="HR7" t="n">
-        <v>0.2556270096463023</v>
+        <v>0.2690014903129657</v>
       </c>
       <c r="HS7" t="n">
         <v>5</v>
@@ -5704,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="HU7" t="n">
-        <v>0.01056338028169014</v>
+        <v>0.00949367088607595</v>
       </c>
     </row>
     <row r="8">
@@ -7812,328 +7824,328 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>37740</v>
+        <v>40620</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>-54</v>
+        <v>-23</v>
       </c>
       <c r="J11" t="n">
-        <v>1218</v>
+        <v>1317</v>
       </c>
       <c r="K11" t="n">
-        <v>1229</v>
+        <v>1328</v>
       </c>
       <c r="L11" t="n">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="M11" t="n">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="N11" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="O11" t="n">
-        <v>2447</v>
+        <v>2645</v>
       </c>
       <c r="P11" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="Q11" t="n">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="R11" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="S11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="T11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="U11" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="V11" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="W11" t="n">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z11" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AA11" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="AB11" t="n">
         <v>5</v>
       </c>
       <c r="AC11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="AF11" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="AG11" t="n">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI11" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AK11" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="AL11" t="n">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="AM11" t="n">
-        <v>603</v>
+        <v>654</v>
       </c>
       <c r="AN11" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="AO11" t="n">
-        <v>455</v>
+        <v>490</v>
       </c>
       <c r="AP11" t="n">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1321</v>
+        <v>1446</v>
       </c>
       <c r="AR11" t="n">
-        <v>1375</v>
+        <v>1469</v>
       </c>
       <c r="AS11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AT11" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="AU11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV11" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AW11" t="n">
+        <v>64</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>207</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>204</v>
+      </c>
+      <c r="BA11" t="n">
         <v>55</v>
       </c>
-      <c r="AX11" t="n">
-        <v>189</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>73</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>178</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>50</v>
-      </c>
       <c r="BB11" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="BC11" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="BD11" t="n">
-        <v>419</v>
+        <v>485</v>
       </c>
       <c r="BE11" t="n">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="BF11" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="BG11" t="n">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="BH11" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="BI11" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="BJ11" t="n">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="BK11" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="BL11" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM11" t="n">
         <v>2</v>
       </c>
       <c r="BN11" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="BO11" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="BP11" t="n">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="BQ11" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="BR11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="BS11" t="n">
+        <v>77</v>
+      </c>
+      <c r="BT11" t="n">
         <v>73</v>
       </c>
-      <c r="BT11" t="n">
-        <v>56</v>
-      </c>
       <c r="BU11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>728</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>89</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>122</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>180</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>242</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>28</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>450</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>219</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>18</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>125</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>71</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>54</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>122</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>22</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>69</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>89</v>
+      </c>
+      <c r="CN11" t="n">
         <v>15</v>
       </c>
-      <c r="BV11" t="n">
-        <v>657</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>80</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>161</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>221</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>27</v>
-      </c>
-      <c r="CC11" t="n">
-        <v>409</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>199</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>608</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>13</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>115</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>66</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>49</v>
-      </c>
-      <c r="CJ11" t="n">
-        <v>115</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>21</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>66</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>83</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>13</v>
-      </c>
       <c r="CO11" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="CP11" t="n">
         <v>12</v>
       </c>
       <c r="CQ11" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="CR11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CS11" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="CT11" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="CU11" t="n">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="CV11" t="n">
         <v>1</v>
       </c>
       <c r="CW11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CX11" t="n">
         <v>13</v>
       </c>
       <c r="CY11" t="n">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="CZ11" t="n">
         <v>2</v>
       </c>
       <c r="DA11" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="DB11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="DC11" t="n">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="DD11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="DE11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DG11" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="DH11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DI11" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="DJ11" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="DK11" t="n">
         <v>4</v>
@@ -8142,20 +8154,20 @@
         <v>2</v>
       </c>
       <c r="DM11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DN11" t="n">
         <v>2</v>
       </c>
       <c r="DO11" t="inlineStr"/>
       <c r="DP11" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="DQ11" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="DR11" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="DS11" t="n">
         <v>2</v>
@@ -8164,247 +8176,247 @@
         <v>1</v>
       </c>
       <c r="DU11" t="n">
-        <v>1132</v>
+        <v>1239</v>
       </c>
       <c r="DV11" t="n">
-        <v>418</v>
+        <v>484</v>
       </c>
       <c r="DW11" t="n">
-        <v>394</v>
+        <v>444</v>
       </c>
       <c r="DX11" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="DY11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.4897959183673469</v>
+        <v>0.50920245398773</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.5373134328358209</v>
+        <v>0.5570469798657718</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.8145695364238411</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.3306122448979592</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.3265306122448979</v>
+        <v>0.3207547169811321</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3038674033149171</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.3306122448979592</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.4875621890547264</v>
+        <v>0.4984709480122324</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.4574468085106383</v>
+        <v>0.4554455445544555</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.4101123595505618</v>
+        <v>0.4411764705882353</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.4919659735349716</v>
+        <v>0.4973776223776224</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.4685314685314685</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.4314868804664723</v>
+        <v>0.448051948051948</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.5378973105134475</v>
+        <v>0.5416354088522131</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.5279329608938548</v>
+        <v>0.5253807106598984</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.497624703087886</v>
+        <v>0.510548523206751</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.4300567107750473</v>
+        <v>0.4283216783216783</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.004395604395604396</v>
+        <v>0.004081632653061225</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.1575456053067993</v>
+        <v>0.1529051987767584</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.1762295081967213</v>
+        <v>0.1725490196078431</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.1661016949152542</v>
+        <v>0.1586826347305389</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.046875</v>
+        <v>0.04615384615384616</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.008849557522123894</v>
+        <v>0.00819672131147541</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.5808080808080808</v>
+        <v>0.5781990521327014</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.6443148688046647</v>
+        <v>0.6522911051212938</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3777089783281734</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.6680497925311203</v>
+        <v>0.6741573033707865</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.2730375426621161</v>
+        <v>0.2816455696202532</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.6541095890410958</v>
+        <v>0.6614420062695925</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.321608040201005</v>
+        <v>0.3302034428794992</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.3814432989690721</v>
+        <v>0.3960396039603961</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.3837209302325582</v>
+        <v>0.3903743315508021</v>
       </c>
       <c r="FH11" t="n">
         <v>0.2571428571428571</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.2456140350877193</v>
+        <v>0.2601626016260163</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.3692307692307693</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.6226415094339622</v>
+        <v>0.625</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.6502732240437158</v>
+        <v>0.6650246305418719</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6607142857142857</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.6914285714285714</v>
+        <v>0.6989795918367347</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.6056338028169014</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.02594810379241517</v>
+        <v>0.03345724907063197</v>
       </c>
       <c r="FQ11" t="n">
-        <v>93.36724960254372</v>
+        <v>93.76661742983752</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.5125</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="FS11" t="n">
-        <v>15.33546798029557</v>
+        <v>15.2665907365224</v>
       </c>
       <c r="FT11" t="n">
-        <v>15.50968266883645</v>
+        <v>15.44721385542169</v>
       </c>
       <c r="FU11" t="n">
-        <v>14.49835796387521</v>
+        <v>14.45299924069856</v>
       </c>
       <c r="FV11" t="n">
-        <v>14.66696501220505</v>
+        <v>14.61513554216868</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.2306238185255199</v>
+        <v>0.2229020979020979</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.5942622950819673</v>
+        <v>0.596078431372549</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.7213930348258707</v>
+        <v>0.7203791469194313</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.503448275862069</v>
+        <v>0.506578947368421</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.27882797731569</v>
+        <v>0.291958041958042</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.4067796610169492</v>
+        <v>0.4311377245508982</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.5124555160142349</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5069444444444444</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.06049149338374291</v>
+        <v>0.05681818181818182</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.453125</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.4754098360655737</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="GH11" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="GI11" t="n">
-        <v>0.1068052930056711</v>
+        <v>0.1066433566433566</v>
       </c>
       <c r="GJ11" t="n">
-        <v>0.4247787610619469</v>
+        <v>0.4262295081967213</v>
       </c>
       <c r="GK11" t="n">
+        <v>0.4297520661157025</v>
+      </c>
+      <c r="GL11" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="GM11" t="n">
+        <v>0.3216783216783217</v>
+      </c>
+      <c r="GN11" t="n">
+        <v>0.2989130434782609</v>
+      </c>
+      <c r="GO11" t="n">
+        <v>0.2997275204359673</v>
+      </c>
+      <c r="GP11" t="n">
+        <v>0.7545454545454545</v>
+      </c>
+      <c r="GQ11" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="GL11" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="GM11" t="n">
-        <v>0.3232514177693762</v>
-      </c>
-      <c r="GN11" t="n">
-        <v>0.3011695906432749</v>
-      </c>
-      <c r="GO11" t="n">
-        <v>0.3020527859237537</v>
-      </c>
-      <c r="GP11" t="n">
-        <v>0.7572815533980582</v>
-      </c>
-      <c r="GQ11" t="n">
-        <v>0.4195804195804196</v>
-      </c>
       <c r="GR11" t="n">
-        <v>0.5166666666666667</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="GS11" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="GT11" t="n">
-        <v>0.1118881118881119</v>
+        <v>0.1103896103896104</v>
       </c>
       <c r="GU11" t="n">
-        <v>0.3125</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="GV11" t="n">
         <v>0.6</v>
       </c>
       <c r="GW11" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2337662337662338</v>
       </c>
       <c r="GX11" t="n">
         <v>0.3333333333333333</v>
@@ -8413,70 +8425,70 @@
         <v>1</v>
       </c>
       <c r="GZ11" t="n">
-        <v>0.1982507288629738</v>
+        <v>0.1922077922077922</v>
       </c>
       <c r="HA11" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4864864864864865</v>
       </c>
       <c r="HB11" t="n">
-        <v>0.1253644314868805</v>
+        <v>0.1272727272727273</v>
       </c>
       <c r="HC11" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.4081632653061225</v>
       </c>
       <c r="HD11" t="n">
-        <v>0.3556851311953353</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="HE11" t="n">
-        <v>0.2622950819672131</v>
+        <v>0.2651515151515151</v>
       </c>
       <c r="HF11" t="n">
-        <v>0.6606805293005671</v>
+        <v>0.6512237762237763</v>
       </c>
       <c r="HG11" t="n">
-        <v>0.3011695906432749</v>
+        <v>0.2989130434782609</v>
       </c>
       <c r="HH11" t="n">
-        <v>0.5238248331744518</v>
+        <v>0.5216345542806707</v>
       </c>
       <c r="HI11" t="n">
-        <v>0.5339724489795918</v>
+        <v>0.5334653846153846</v>
       </c>
       <c r="HJ11" t="n">
-        <v>0.5170406528189911</v>
+        <v>0.5146907407407407</v>
       </c>
       <c r="HK11" t="n">
-        <v>0.123728813559322</v>
+        <v>0.127443315089914</v>
       </c>
       <c r="HL11" t="n">
-        <v>0.1933240611961057</v>
+        <v>0.1979565772669221</v>
       </c>
       <c r="HM11" t="n">
-        <v>0.01518438177874186</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="HN11" t="n">
-        <v>0.1430734292202877</v>
+        <v>0.1431535269709543</v>
       </c>
       <c r="HO11" t="n">
-        <v>0.3171839515518546</v>
+        <v>0.3354080221300138</v>
       </c>
       <c r="HP11" t="n">
-        <v>6.376451077943615</v>
+        <v>6.324770642201834</v>
       </c>
       <c r="HQ11" t="n">
-        <v>25.91108647450111</v>
+        <v>25.95030927835051</v>
       </c>
       <c r="HR11" t="n">
-        <v>0.3251231527093596</v>
+        <v>0.3386484434320425</v>
       </c>
       <c r="HS11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="HT11" t="n">
         <v>2</v>
       </c>
       <c r="HU11" t="n">
-        <v>0.002923976608187134</v>
+        <v>0.002717391304347826</v>
       </c>
     </row>
     <row r="12">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -7129,310 +7129,310 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>23040</v>
+        <v>26520</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>-133</v>
+        <v>-126</v>
       </c>
       <c r="J10" t="n">
-        <v>758</v>
+        <v>870</v>
       </c>
       <c r="K10" t="n">
-        <v>761</v>
+        <v>874</v>
       </c>
       <c r="L10" t="n">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="M10" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="N10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="O10" t="n">
-        <v>1519</v>
+        <v>1744</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="Q10" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="R10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="S10" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="T10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="U10" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="V10" t="n">
+        <v>86</v>
+      </c>
+      <c r="W10" t="n">
+        <v>175</v>
+      </c>
+      <c r="X10" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA10" t="n">
         <v>82</v>
-      </c>
-      <c r="W10" t="n">
-        <v>163</v>
-      </c>
-      <c r="X10" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>69</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>66</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
       </c>
       <c r="AC10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>78</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>229</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>13</v>
       </c>
-      <c r="AD10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AK10" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>236</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>450</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>109</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>311</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>959</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1085</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>71</v>
+      </c>
+      <c r="AU10" t="n">
         <v>14</v>
       </c>
-      <c r="AF10" t="n">
-        <v>69</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>202</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK10" t="n">
+      <c r="AV10" t="n">
         <v>40</v>
       </c>
-      <c r="AL10" t="n">
-        <v>208</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>397</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>96</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>268</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>133</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>837</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>59</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>36</v>
-      </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="AY10" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AZ10" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BB10" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="BC10" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="BD10" t="n">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="BE10" t="n">
+        <v>248</v>
+      </c>
+      <c r="BF10" t="n">
         <v>224</v>
       </c>
-      <c r="BF10" t="n">
-        <v>192</v>
-      </c>
       <c r="BG10" t="n">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="BH10" t="n">
         <v>63</v>
       </c>
       <c r="BI10" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BJ10" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="BK10" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="BL10" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="BO10" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="BP10" t="n">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="BQ10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="BR10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BS10" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="BT10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="BU10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BV10" t="n">
-        <v>449</v>
+        <v>512</v>
       </c>
       <c r="BW10" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="BX10" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="BY10" t="n">
         <v>3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="CA10" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="CB10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CC10" t="n">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="CD10" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="CE10" t="n">
-        <v>356</v>
+        <v>424</v>
       </c>
       <c r="CF10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="CG10" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="CH10" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="CI10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CJ10" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="CK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CL10" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="CM10" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="CN10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CO10" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="CP10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CQ10" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="CR10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS10" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="CT10" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="CU10" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="CV10" t="n">
         <v>6</v>
       </c>
       <c r="CW10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CX10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CY10" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="CZ10" t="n">
         <v>1</v>
       </c>
       <c r="DA10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DB10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DC10" t="n">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="DD10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="DE10" t="n">
         <v>4</v>
@@ -7441,38 +7441,38 @@
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="DH10" t="n">
         <v>7</v>
       </c>
       <c r="DI10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="DJ10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="DK10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DL10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DM10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="DN10" t="inlineStr"/>
       <c r="DO10" t="n">
         <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="DQ10" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="DR10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="DS10" t="n">
         <v>3</v>
@@ -7481,315 +7481,315 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>721</v>
+        <v>830</v>
       </c>
       <c r="DV10" t="n">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="DW10" t="n">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="DX10" t="n">
         <v>21</v>
       </c>
       <c r="DY10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5254237288135594</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5863874345549738</v>
+        <v>0.5767441860465117</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.78125</v>
+        <v>0.8073394495412844</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3582089552238806</v>
+        <v>0.3504823151125402</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.35</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3582089552238806</v>
+        <v>0.3504823151125402</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5239294710327456</v>
+        <v>0.5244444444444445</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5423728813559322</v>
+        <v>0.5070422535211268</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.5595238095238095</v>
+        <v>0.5567010309278351</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5293233082706766</v>
+        <v>0.5249671484888305</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5421052631578948</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.4927536231884058</v>
+        <v>0.50625</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5688010899182562</v>
+        <v>0.5676156583629893</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.5742574257425742</v>
+        <v>0.5466101694915254</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5598802395209581</v>
+        <v>0.576530612244898</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4030075187969925</v>
+        <v>0.4086727989487516</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.003731343283582089</v>
+        <v>0.003215434083601286</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.09319899244332494</v>
+        <v>0.1</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.1527093596059113</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06134969325153374</v>
+        <v>0.06285714285714286</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="EV10" t="inlineStr"/>
       <c r="EW10" t="n">
-        <v>0.5899280575539568</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6625</v>
+        <v>0.680628272251309</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.328042328042328</v>
+        <v>0.3286384976525822</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.7019230769230769</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.3147208121827411</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6735294117647059</v>
+        <v>0.6917293233082706</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3165266106442577</v>
+        <v>0.3219512195121951</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4307692307692308</v>
+        <v>0.4303797468354431</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2839506172839506</v>
+        <v>0.2808988764044944</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2558139534883721</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.3178294573643411</v>
+        <v>0.3219178082191781</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5961538461538461</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7954545454545454</v>
+        <v>0.8043478260869565</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.6444444444444445</v>
+        <v>0.6623376623376623</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.8</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.05625</v>
+        <v>0.06010928961748634</v>
       </c>
       <c r="FQ10" t="n">
-        <v>94.9375</v>
+        <v>94.69683257918552</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="FS10" t="n">
-        <v>15.65197889182058</v>
+        <v>15.76712643678161</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.68567674113009</v>
+        <v>14.64828375286041</v>
       </c>
       <c r="FU10" t="n">
-        <v>14.98641160949868</v>
+        <v>15.09873563218391</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.06215505913272</v>
+        <v>14.02871853546911</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.2481203007518797</v>
+        <v>0.266754270696452</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.6059113300492611</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7092198581560284</v>
+        <v>0.7151162790697675</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.59</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.2451127819548872</v>
+        <v>0.2299605781865966</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.5030674846625767</v>
+        <v>0.4914285714285714</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.5359477124183006</v>
+        <v>0.524390243902439</v>
       </c>
       <c r="GD10" t="n">
+        <v>0.4883720930232558</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0.09461235216819974</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="GH10" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="GI10" t="n">
+        <v>0.1077529566360053</v>
+      </c>
+      <c r="GJ10" t="n">
+        <v>0.3780487804878049</v>
+      </c>
+      <c r="GK10" t="n">
+        <v>0.3780487804878049</v>
+      </c>
+      <c r="GL10" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="GM10" t="n">
+        <v>0.3009198423127464</v>
+      </c>
+      <c r="GN10" t="n">
+        <v>0.3406113537117904</v>
+      </c>
+      <c r="GO10" t="n">
+        <v>0.3421052631578947</v>
+      </c>
+      <c r="GP10" t="n">
+        <v>0.7564102564102564</v>
+      </c>
+      <c r="GQ10" t="n">
+        <v>0.4324324324324325</v>
+      </c>
+      <c r="GR10" t="n">
         <v>0.5</v>
       </c>
-      <c r="GE10" t="n">
-        <v>0.1037593984962406</v>
-      </c>
-      <c r="GF10" t="n">
-        <v>0.3768115942028986</v>
-      </c>
-      <c r="GG10" t="n">
-        <v>0.3939393939393939</v>
-      </c>
-      <c r="GH10" t="n">
-        <v>0.4615384615384616</v>
-      </c>
-      <c r="GI10" t="n">
-        <v>0.09924812030075188</v>
-      </c>
-      <c r="GJ10" t="n">
-        <v>0.4090909090909091</v>
-      </c>
-      <c r="GK10" t="n">
-        <v>0.4090909090909091</v>
-      </c>
-      <c r="GL10" t="n">
-        <v>0.9259259259259259</v>
-      </c>
-      <c r="GM10" t="n">
-        <v>0.3037593984962406</v>
-      </c>
-      <c r="GN10" t="n">
-        <v>0.3415841584158416</v>
-      </c>
-      <c r="GO10" t="n">
-        <v>0.3432835820895522</v>
-      </c>
-      <c r="GP10" t="n">
-        <v>0.7246376811594203</v>
-      </c>
-      <c r="GQ10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="GR10" t="n">
-        <v>0.5263157894736842</v>
-      </c>
       <c r="GS10" t="n">
-        <v>0.15</v>
+        <v>0.125</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.1368421052631579</v>
+        <v>0.1351351351351351</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="GV10" t="n">
         <v>0.8</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2421052631578947</v>
+        <v>0.2252252252252252</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.36</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.75</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.2536231884057971</v>
+        <v>0.275</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1014492753623188</v>
+        <v>0.1125</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2898550724637681</v>
+        <v>0.28125</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.6511278195488722</v>
+        <v>0.6754270696452037</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3415841584158416</v>
+        <v>0.3406113537117904</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5239349697885196</v>
+        <v>0.5277263192612137</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5186838709677419</v>
+        <v>0.5208295774647888</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5065525925925927</v>
+        <v>0.5095175159235669</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.101813110181311</v>
+        <v>0.1044957472660996</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1479820627802691</v>
+        <v>0.1552062868369352</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.02583025830258303</v>
+        <v>0.02229299363057325</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1385902031063321</v>
+        <v>0.1345151199165798</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.2234169653524492</v>
+        <v>0.2356621480709072</v>
       </c>
       <c r="HP10" t="n">
-        <v>7.30831234256927</v>
+        <v>6.907999999999999</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.90861423220974</v>
+        <v>25.85516129032258</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.2229551451187335</v>
+        <v>0.2298850574712644</v>
       </c>
       <c r="HS10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="HT10" t="inlineStr"/>
       <c r="HU10" t="n">
-        <v>0.004950495049504951</v>
+        <v>0.004366812227074236</v>
       </c>
     </row>
     <row r="11">
@@ -9915,73 +9915,73 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>31680</v>
+        <v>35160</v>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>-159</v>
+        <v>-166</v>
       </c>
       <c r="J14" t="n">
-        <v>1087</v>
+        <v>1199</v>
       </c>
       <c r="K14" t="n">
-        <v>1095</v>
+        <v>1208</v>
       </c>
       <c r="L14" t="n">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M14" t="n">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="N14" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="O14" t="n">
-        <v>2182</v>
+        <v>2407</v>
       </c>
       <c r="P14" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="Q14" t="n">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="R14" t="n">
         <v>44</v>
       </c>
       <c r="S14" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="T14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V14" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="W14" t="n">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="X14" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Y14" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Z14" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AA14" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="AB14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AD14" t="n">
         <v>10</v>
@@ -9990,249 +9990,249 @@
         <v>31</v>
       </c>
       <c r="AF14" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AG14" t="n">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="AH14" t="n">
         <v>10</v>
       </c>
       <c r="AI14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AL14" t="n">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="AM14" t="n">
-        <v>622</v>
+        <v>678</v>
       </c>
       <c r="AN14" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="AO14" t="n">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="AP14" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1127</v>
+        <v>1242</v>
       </c>
       <c r="AR14" t="n">
-        <v>1286</v>
+        <v>1408</v>
       </c>
       <c r="AS14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AT14" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AU14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV14" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AW14" t="n">
         <v>32</v>
       </c>
       <c r="AX14" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AY14" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AZ14" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="BA14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BB14" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BC14" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="BD14" t="n">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="BE14" t="n">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="BF14" t="n">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="BG14" t="n">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="BH14" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="BI14" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ14" t="n">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="BK14" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="BL14" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="BM14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN14" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="BO14" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="BP14" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="BQ14" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="BR14" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BS14" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="BT14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BU14" t="n">
         <v>16</v>
       </c>
       <c r="BV14" t="n">
-        <v>559</v>
+        <v>625</v>
       </c>
       <c r="BW14" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="BX14" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="CA14" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="CB14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CC14" t="n">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="CD14" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="CE14" t="n">
-        <v>549</v>
+        <v>597</v>
       </c>
       <c r="CF14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CG14" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="CH14" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="CI14" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="CJ14" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="CK14" t="n">
         <v>16</v>
       </c>
       <c r="CL14" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="CM14" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="CN14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CO14" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="CR14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CS14" t="n">
         <v>48</v>
       </c>
       <c r="CT14" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="CU14" t="n">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CX14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CY14" t="n">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="CZ14" t="n">
         <v>9</v>
       </c>
       <c r="DA14" t="n">
+        <v>29</v>
+      </c>
+      <c r="DB14" t="n">
         <v>26</v>
       </c>
-      <c r="DB14" t="n">
+      <c r="DC14" t="n">
+        <v>275</v>
+      </c>
+      <c r="DD14" t="n">
         <v>24</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>256</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>22</v>
       </c>
       <c r="DE14" t="inlineStr"/>
       <c r="DF14" t="n">
         <v>4</v>
       </c>
       <c r="DG14" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="DH14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DI14" t="n">
         <v>31</v>
       </c>
       <c r="DJ14" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="DK14" t="n">
         <v>4</v>
@@ -10241,7 +10241,7 @@
         <v>1</v>
       </c>
       <c r="DM14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10250,330 +10250,330 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DQ14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="DR14" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="DS14" t="inlineStr"/>
       <c r="DT14" t="n">
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>926</v>
+        <v>1033</v>
       </c>
       <c r="DV14" t="n">
+        <v>362</v>
+      </c>
+      <c r="DW14" t="n">
         <v>347</v>
       </c>
-      <c r="DW14" t="n">
-        <v>337</v>
-      </c>
       <c r="DX14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="DY14" t="n">
         <v>28</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4596491228070175</v>
+        <v>0.4530744336569579</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5261044176706827</v>
+        <v>0.5147058823529411</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8114754098360656</v>
+        <v>0.8273381294964028</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3160621761658031</v>
+        <v>0.3225058004640371</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.3469387755102041</v>
+        <v>0.3653846153846154</v>
       </c>
       <c r="EE14" t="n">
+        <v>0.3363636363636364</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.3225058004640371</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.4557522123893805</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.4666366095581605</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.5673076923076923</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.4658703071672355</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0.5032467532467533</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0.5157142857142857</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.3886384129846709</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.0185614849187935</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.1312684365781711</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.1735294117647059</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1146245059288538</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.01176470588235294</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0.02205882352941177</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.6280487804878049</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.6866197183098591</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.3424657534246575</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.7125506072874493</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.2350877192982456</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.6986817325800376</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0.2953846153846154</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0.3892617449664429</v>
+      </c>
+      <c r="FG14" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="EF14" t="n">
-        <v>0.3160621761658031</v>
-      </c>
-      <c r="EG14" t="n">
-        <v>0.4581993569131833</v>
-      </c>
-      <c r="EH14" t="n">
-        <v>0.6020408163265306</v>
-      </c>
-      <c r="EI14" t="n">
-        <v>0.4342857142857143</v>
-      </c>
-      <c r="EJ14" t="n">
-        <v>0.4642857142857143</v>
-      </c>
-      <c r="EK14" t="n">
-        <v>0.5748299319727891</v>
-      </c>
-      <c r="EL14" t="n">
-        <v>0.4593639575971731</v>
-      </c>
-      <c r="EM14" t="n">
-        <v>0.5008904719501336</v>
-      </c>
-      <c r="EN14" t="n">
-        <v>0.6017964071856288</v>
-      </c>
-      <c r="EO14" t="n">
-        <v>0.5103244837758112</v>
-      </c>
-      <c r="EP14" t="n">
-        <v>0.382936507936508</v>
-      </c>
-      <c r="EQ14" t="n">
-        <v>0.01813471502590673</v>
-      </c>
-      <c r="ER14" t="n">
-        <v>0.1334405144694534</v>
-      </c>
-      <c r="ES14" t="n">
-        <v>0.1762820512820513</v>
-      </c>
-      <c r="ET14" t="n">
-        <v>0.1173913043478261</v>
-      </c>
-      <c r="EU14" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="EV14" t="n">
-        <v>0.02521008403361345</v>
-      </c>
-      <c r="EW14" t="n">
-        <v>0.6174496644295302</v>
-      </c>
-      <c r="EX14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="EY14" t="n">
-        <v>0.1470588235294118</v>
-      </c>
-      <c r="EZ14" t="n">
-        <v>0.6884615384615385</v>
-      </c>
-      <c r="FA14" t="n">
-        <v>0.3532934131736527</v>
-      </c>
-      <c r="FB14" t="n">
-        <v>0.7247706422018348</v>
-      </c>
-      <c r="FC14" t="n">
-        <v>0.2412451361867704</v>
-      </c>
-      <c r="FD14" t="n">
-        <v>0.7050209205020921</v>
-      </c>
-      <c r="FE14" t="n">
-        <v>0.3045685279187818</v>
-      </c>
-      <c r="FF14" t="n">
-        <v>0.391304347826087</v>
-      </c>
-      <c r="FG14" t="n">
-        <v>0.3533333333333333</v>
-      </c>
       <c r="FH14" t="n">
-        <v>0.2391304347826087</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2430939226519337</v>
+        <v>0.24</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2235294117647059</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.6494845360824743</v>
+        <v>0.6396396396396397</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.6902654867256637</v>
+        <v>0.6942148760330579</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.76</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7076023391812866</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.75</v>
+        <v>0.7236842105263158</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03386454183266932</v>
+        <v>0.03249097472924187</v>
       </c>
       <c r="FQ14" t="n">
-        <v>99.18181818181819</v>
+        <v>98.580204778157</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.8</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="FS14" t="n">
-        <v>14.81747930082797</v>
+        <v>14.79015846538782</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.22228310502283</v>
+        <v>14.42599337748344</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.03495860165593</v>
+        <v>14.02485404503753</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.6510502283105</v>
+        <v>13.8444536423841</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.3065825067628494</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5576923076923077</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6770428015564203</v>
+        <v>0.6761565836298933</v>
       </c>
       <c r="FZ14" t="n">
         <v>0.5</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2281746031746032</v>
+        <v>0.2281334535617674</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.3391304347826087</v>
+        <v>0.3280632411067194</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.3842364532019704</v>
+        <v>0.3705357142857143</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3493975903614458</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.07936507936507936</v>
+        <v>0.07664562669071236</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.4125</v>
+        <v>0.4235294117647059</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.4177215189873418</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1180555555555556</v>
+        <v>0.1226330027051398</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3445378151260504</v>
+        <v>0.3602941176470588</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.353448275862069</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.975609756097561</v>
+        <v>0.9795918367346939</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.2648809523809524</v>
+        <v>0.2660054102795311</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.303370786516854</v>
+        <v>0.3050847457627119</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3079847908745247</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.7283950617283951</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4743589743589743</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="GS14" t="n">
         <v>0.25</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.1020408163265306</v>
+        <v>0.108974358974359</v>
       </c>
       <c r="GU14" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="GV14" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2312925170068027</v>
+        <v>0.2243589743589744</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="GY14" t="n">
         <v>0.7</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3498233215547703</v>
+        <v>0.348122866894198</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1095406360424028</v>
+        <v>0.10580204778157</v>
       </c>
       <c r="HC14" t="n">
         <v>0.3225806451612903</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.2720848056537102</v>
+        <v>0.2696245733788396</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3376623376623377</v>
+        <v>0.3417721518987342</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6924603174603174</v>
+        <v>0.6952209197475203</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.303370786516854</v>
+        <v>0.3050847457627119</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5510973579262213</v>
+        <v>0.5505714221014493</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5494995412844036</v>
+        <v>0.5436353448275862</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5464845878136201</v>
+        <v>0.5447358131487889</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09706959706959707</v>
+        <v>0.09658617818484597</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.148936170212766</v>
+        <v>0.1484375</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.002583979328165375</v>
+        <v>0.004618937644341801</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1783496007098491</v>
+        <v>0.1682769726247987</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.3078970718722271</v>
+        <v>0.2914653784219002</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.266398713826367</v>
+        <v>6.286430678466076</v>
       </c>
       <c r="HQ14" t="n">
-        <v>25.01439790575916</v>
+        <v>24.98992974238876</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.3100275988960441</v>
+        <v>0.2894078398665554</v>
       </c>
       <c r="HS14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.0149812734082397</v>
+        <v>0.01694915254237288</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -5054,307 +5054,307 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>40920</v>
+        <v>44100</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>-22</v>
+        <v>-11</v>
       </c>
       <c r="J7" t="n">
-        <v>1342</v>
+        <v>1450</v>
       </c>
       <c r="K7" t="n">
-        <v>1349</v>
+        <v>1455</v>
       </c>
       <c r="L7" t="n">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="M7" t="n">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="N7" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="O7" t="n">
-        <v>2691</v>
+        <v>2905</v>
       </c>
       <c r="P7" t="n">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="Q7" t="n">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="R7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="T7" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="U7" t="n">
+        <v>123</v>
+      </c>
+      <c r="V7" t="n">
+        <v>134</v>
+      </c>
+      <c r="W7" t="n">
+        <v>337</v>
+      </c>
+      <c r="X7" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>111</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>127</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>342</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>45</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>89</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>432</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>845</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>166</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>453</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>276</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1638</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1649</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT7" t="n">
         <v>116</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AU7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>63</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>226</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>107</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>216</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB7" t="n">
         <v>124</v>
       </c>
-      <c r="W7" t="n">
-        <v>319</v>
-      </c>
-      <c r="X7" t="n">
-        <v>41</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>94</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>104</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>33</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>121</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>316</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>83</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>400</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>789</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>156</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>420</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>255</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1523</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1545</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>53</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>59</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>209</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>102</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>205</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>35</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>116</v>
-      </c>
       <c r="BC7" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="BD7" t="n">
-        <v>412</v>
+        <v>445</v>
       </c>
       <c r="BE7" t="n">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="BF7" t="n">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="BG7" t="n">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="BH7" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="BI7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="BJ7" t="n">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="BK7" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="BL7" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="BM7" t="n">
         <v>3</v>
       </c>
       <c r="BN7" t="n">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="BO7" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="BP7" t="n">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="BQ7" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="BR7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="BT7" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="BU7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV7" t="n">
-        <v>833</v>
+        <v>880</v>
       </c>
       <c r="BW7" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="BX7" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BZ7" t="n">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="CA7" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="CB7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CC7" t="n">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="CD7" t="n">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="CE7" t="n">
-        <v>657</v>
+        <v>715</v>
       </c>
       <c r="CF7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="CG7" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="CH7" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="CI7" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="CJ7" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="CK7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CL7" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="CM7" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="CN7" t="n">
         <v>15</v>
       </c>
       <c r="CO7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="CP7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CQ7" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="CR7" t="n">
+        <v>32</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>60</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>171</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>358</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>32</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>29</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>308</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="DA7" t="n">
         <v>28</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>56</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>160</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>332</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>29</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>27</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>279</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>22</v>
       </c>
       <c r="DB7" t="n">
         <v>19</v>
       </c>
       <c r="DC7" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="DD7" t="n">
         <v>30</v>
@@ -5364,16 +5364,16 @@
         <v>5</v>
       </c>
       <c r="DG7" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="DH7" t="n">
         <v>5</v>
       </c>
       <c r="DI7" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="DJ7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="DK7" t="n">
         <v>7</v>
@@ -5382,332 +5382,332 @@
         <v>4</v>
       </c>
       <c r="DM7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DN7" t="n">
         <v>3</v>
       </c>
       <c r="DO7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP7" t="n">
         <v>39</v>
       </c>
       <c r="DQ7" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="DR7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DS7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DT7" t="n">
         <v>2</v>
       </c>
       <c r="DU7" t="n">
-        <v>1314</v>
+        <v>1412</v>
       </c>
       <c r="DV7" t="n">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="DW7" t="n">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="DX7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="DY7" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.5275</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.5656836461126006</v>
+        <v>0.5544554455445545</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.8782051282051282</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.3664459161147903</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.3559322033898305</v>
+        <v>0.3968253968253968</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.3017241379310345</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.3664459161147903</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.5069708491761724</v>
+        <v>0.5112426035502958</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.4818181818181818</v>
+        <v>0.4741379310344828</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.4975609756097561</v>
+        <v>0.4953703703703703</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.5244003308519437</v>
+        <v>0.524653312788906</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.5</v>
+        <v>0.5167597765363129</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.4813084112149533</v>
+        <v>0.4823529411764706</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.5592347314201619</v>
+        <v>0.5584016393442623</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.5304568527918782</v>
+        <v>0.5406698564593302</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.5365535248041775</v>
+        <v>0.5362318840579711</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.347394540942928</v>
+        <v>0.3489984591679507</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.007142857142857143</v>
+        <v>0.006622516556291391</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.09125475285171103</v>
+        <v>0.09230769230769231</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.1117021276595745</v>
+        <v>0.1127450980392157</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0877742946708464</v>
+        <v>0.08902077151335312</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.02</v>
       </c>
       <c r="EV7" t="inlineStr"/>
       <c r="EW7" t="n">
-        <v>0.5091743119266054</v>
+        <v>0.5147679324894515</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.8301886792452831</v>
+        <v>0.8363636363636363</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.5864661654135338</v>
+        <v>0.5979020979020979</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.3664921465968586</v>
+        <v>0.3694581280788177</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.6934523809523809</v>
+        <v>0.6945945945945946</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.3019607843137255</v>
+        <v>0.296028880866426</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.6461794019933554</v>
+        <v>0.6524390243902439</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.3406593406593407</v>
+        <v>0.3396778916544656</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.4428571428571428</v>
+        <v>0.4342105263157895</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.34375</v>
+        <v>0.355</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.24</v>
+        <v>0.2407407407407407</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2780748663101604</v>
+        <v>0.2718446601941747</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.3676470588235294</v>
+        <v>0.3661971830985916</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.6705882352941176</v>
+        <v>0.6631578947368421</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.5095541401273885</v>
+        <v>0.5214723926380368</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.6929133858267716</v>
+        <v>0.6942446043165468</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.6951219512195121</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.04078014184397163</v>
+        <v>0.04470198675496689</v>
       </c>
       <c r="FQ7" t="n">
-        <v>94.69794721407625</v>
+        <v>94.85714285714286</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.4487179487179487</v>
       </c>
       <c r="FS7" t="n">
-        <v>15.0795827123696</v>
+        <v>15.05675862068965</v>
       </c>
       <c r="FT7" t="n">
-        <v>15.33224610822832</v>
+        <v>15.30426116838488</v>
       </c>
       <c r="FU7" t="n">
-        <v>14.36602086438152</v>
+        <v>14.32041379310345</v>
       </c>
       <c r="FV7" t="n">
-        <v>14.5232023721275</v>
+        <v>14.50508591065292</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.3110008271298594</v>
+        <v>0.3143297380585516</v>
       </c>
       <c r="FX7" t="n">
         <v>0.625</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.7035928143712575</v>
+        <v>0.7044198895027625</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.5914893617021276</v>
+        <v>0.5803921568627451</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.2638544251447477</v>
+        <v>0.2596302003081664</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.3887147335423197</v>
+        <v>0.3976261127596439</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.4261168384879725</v>
+        <v>0.4364820846905538</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.4435483870967742</v>
+        <v>0.4328358208955224</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.07775020678246485</v>
+        <v>0.07704160246533127</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.4361702127659575</v>
+        <v>0.43</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.4456521739130435</v>
+        <v>0.4387755102040816</v>
       </c>
       <c r="GH7" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.08602150537634409</v>
+        <v>0.08551617873651772</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.3365384615384616</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.3365384615384616</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.261373035566584</v>
+        <v>0.263482280431433</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3829113924050633</v>
+        <v>0.3713450292397661</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.3865814696485623</v>
+        <v>0.3746312684365782</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.8512396694214877</v>
+        <v>0.8346456692913385</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.4201183431952663</v>
+        <v>0.4189944134078212</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.5211267605633803</v>
+        <v>0.5066666666666667</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.2702702702702703</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.1005917159763314</v>
+        <v>0.1005586592178771</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="GV7" t="n">
         <v>1</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.2485207100591716</v>
+        <v>0.2513966480446927</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.4</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.3613707165109034</v>
+        <v>0.3617647058823529</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.6293103448275862</v>
+        <v>0.6260162601626016</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.102803738317757</v>
+        <v>0.1029411764705882</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.2585669781931464</v>
+        <v>0.261764705882353</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.3132530120481928</v>
+        <v>0.303370786516854</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.6583953680727874</v>
+        <v>0.6633281972265023</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.3829113924050633</v>
+        <v>0.3713450292397661</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.5497948175787728</v>
+        <v>0.5502963292117465</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.5403324786324786</v>
+        <v>0.5412296</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.5592921383647799</v>
+        <v>0.5580925595238095</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.108843537414966</v>
+        <v>0.107670654468684</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.1547884187082405</v>
+        <v>0.1536863966770509</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.01176470588235294</v>
+        <v>0.01091703056768559</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.1372291529875246</v>
+        <v>0.137973137973138</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.2705187130663165</v>
+        <v>0.2716727716727717</v>
       </c>
       <c r="HP7" t="n">
-        <v>6.27743979721166</v>
+        <v>6.219763313609468</v>
       </c>
       <c r="HQ7" t="n">
-        <v>25.75358851674641</v>
+        <v>25.72022222222222</v>
       </c>
       <c r="HR7" t="n">
-        <v>0.2690014903129657</v>
+        <v>0.2703448275862069</v>
       </c>
       <c r="HS7" t="n">
         <v>5</v>
@@ -5716,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="HU7" t="n">
-        <v>0.00949367088607595</v>
+        <v>0.008771929824561403</v>
       </c>
     </row>
     <row r="8">
@@ -5751,326 +5751,328 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>28800</v>
+        <v>31980</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>-194</v>
+        <v>-205</v>
       </c>
       <c r="J8" t="n">
-        <v>955</v>
+        <v>1061</v>
       </c>
       <c r="K8" t="n">
-        <v>960</v>
+        <v>1068</v>
       </c>
       <c r="L8" t="n">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="M8" t="n">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="N8" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="O8" t="n">
-        <v>1915</v>
+        <v>2129</v>
       </c>
       <c r="P8" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Q8" t="n">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="R8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="T8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U8" t="n">
+        <v>71</v>
+      </c>
+      <c r="V8" t="n">
         <v>66</v>
       </c>
-      <c r="V8" t="n">
-        <v>60</v>
-      </c>
       <c r="W8" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="X8" t="n">
         <v>30</v>
       </c>
       <c r="Y8" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD8" t="n">
         <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF8" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AG8" t="n">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="AH8" t="n">
         <v>7</v>
       </c>
       <c r="AI8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AK8" t="n">
+        <v>92</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>273</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>511</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>125</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>404</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>193</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1114</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1319</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>41</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>134</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>68</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>146</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>33</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>115</v>
+      </c>
+      <c r="BC8" t="n">
         <v>79</v>
       </c>
-      <c r="AL8" t="n">
-        <v>253</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>471</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>109</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>353</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>177</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1010</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1204</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>37</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>64</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>135</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>101</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>74</v>
-      </c>
       <c r="BD8" t="n">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="BE8" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="BF8" t="n">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="BG8" t="n">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="BH8" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="BI8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BJ8" t="n">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="BK8" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="BL8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BM8" t="n">
         <v>5</v>
       </c>
       <c r="BN8" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="BO8" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="BP8" t="n">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="BQ8" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="BR8" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="BS8" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="BT8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BU8" t="n">
         <v>14</v>
       </c>
       <c r="BV8" t="n">
-        <v>523</v>
+        <v>584</v>
       </c>
       <c r="BW8" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY8" t="n">
         <v>3</v>
       </c>
       <c r="BZ8" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="CA8" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="CB8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="CC8" t="n">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="CD8" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="CE8" t="n">
-        <v>417</v>
+        <v>466</v>
       </c>
       <c r="CF8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CG8" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="CH8" t="n">
+        <v>44</v>
+      </c>
+      <c r="CI8" t="n">
         <v>37</v>
       </c>
-      <c r="CI8" t="n">
-        <v>33</v>
-      </c>
       <c r="CJ8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="CK8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CL8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="CM8" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="CN8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CO8" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="CP8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CQ8" t="n">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="CR8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CS8" t="n">
+        <v>35</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>106</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>257</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CW8" t="n">
         <v>29</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>97</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>228</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>2</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>23</v>
       </c>
       <c r="CX8" t="n">
         <v>13</v>
       </c>
       <c r="CY8" t="n">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="CZ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>31</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>18</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>262</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="DE8" t="n">
         <v>2</v>
       </c>
-      <c r="DA8" t="n">
-        <v>28</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>16</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>239</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>20</v>
-      </c>
-      <c r="DE8" t="inlineStr"/>
       <c r="DF8" t="n">
         <v>5</v>
       </c>
       <c r="DG8" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="DH8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DI8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="DJ8" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="DK8" t="n">
         <v>3</v>
@@ -6079,7 +6081,7 @@
         <v>2</v>
       </c>
       <c r="DM8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
@@ -6088,13 +6090,13 @@
         <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DQ8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="DR8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="DS8" t="n">
         <v>1</v>
@@ -6103,315 +6105,317 @@
         <v>2</v>
       </c>
       <c r="DU8" t="n">
-        <v>890</v>
+        <v>980</v>
       </c>
       <c r="DV8" t="n">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="DW8" t="n">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="DX8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="DY8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.4822134387351779</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.5374449339207048</v>
+        <v>0.5284552845528455</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.8532110091743119</v>
+        <v>0.864</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.3087818696883853</v>
+        <v>0.3094059405940594</v>
       </c>
       <c r="ED8" t="n">
+        <v>0.3214285714285715</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0.2869565217391304</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0.3094059405940594</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0.5342465753424658</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0.5857142857142857</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0.4657534246575342</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0.5032786885245901</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.5561224489795918</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0.4501915708812261</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0.5377906976744186</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0.5782608695652174</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0.4968051118210863</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0.4415300546448088</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0.01237623762376238</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0.0821917808219178</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0.07392996108949416</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0.111731843575419</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0.01724137931034483</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0.5688622754491018</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0.8157894736842105</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0.6051502145922747</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0.2742616033755274</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0.7251184834123223</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0.2664233576642336</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0.6621621621621622</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0.2700587084148728</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0.2475247524752475</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0.3194444444444444</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0.6413043478260869</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0.756578947368421</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0.6440677966101694</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0.02365591397849462</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>95.86491557223265</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>14.38605089538172</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>15.65205992509363</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>13.8311027332705</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>14.9749063670412</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0.2808743169398907</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0.688715953307393</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0.7436974789915967</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0.5310734463276836</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0.1956284153005464</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0.3687150837988827</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0.4150943396226415</v>
+      </c>
+      <c r="GD8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="EE8" t="n">
-        <v>0.2871287128712871</v>
-      </c>
-      <c r="EF8" t="n">
-        <v>0.3087818696883853</v>
-      </c>
-      <c r="EG8" t="n">
-        <v>0.5371549893842887</v>
-      </c>
-      <c r="EH8" t="n">
-        <v>0.578125</v>
-      </c>
-      <c r="EI8" t="n">
-        <v>0.4814814814814815</v>
-      </c>
-      <c r="EJ8" t="n">
-        <v>0.5054611650485437</v>
-      </c>
-      <c r="EK8" t="n">
-        <v>0.5568181818181818</v>
-      </c>
-      <c r="EL8" t="n">
-        <v>0.4597457627118644</v>
-      </c>
-      <c r="EM8" t="n">
-        <v>0.5402792696025779</v>
-      </c>
-      <c r="EN8" t="n">
-        <v>0.5776699029126213</v>
-      </c>
-      <c r="EO8" t="n">
-        <v>0.5070422535211268</v>
-      </c>
-      <c r="EP8" t="n">
-        <v>0.4283980582524272</v>
-      </c>
-      <c r="EQ8" t="n">
-        <v>0.0141643059490085</v>
-      </c>
-      <c r="ER8" t="n">
-        <v>0.08492569002123142</v>
-      </c>
-      <c r="ES8" t="n">
-        <v>0.07725321888412018</v>
-      </c>
-      <c r="ET8" t="n">
-        <v>0.1197604790419162</v>
-      </c>
-      <c r="EU8" t="n">
-        <v>0.02816901408450704</v>
-      </c>
-      <c r="EV8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="EW8" t="n">
-        <v>0.5821917808219178</v>
-      </c>
-      <c r="EX8" t="n">
-        <v>0.8484848484848485</v>
-      </c>
-      <c r="EY8" t="n">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="EZ8" t="n">
-        <v>0.6076555023923444</v>
-      </c>
-      <c r="FA8" t="n">
-        <v>0.2764976958525346</v>
-      </c>
-      <c r="FB8" t="n">
-        <v>0.7195767195767195</v>
-      </c>
-      <c r="FC8" t="n">
-        <v>0.2625</v>
-      </c>
-      <c r="FD8" t="n">
-        <v>0.6608040201005025</v>
-      </c>
-      <c r="FE8" t="n">
-        <v>0.2691466083150985</v>
-      </c>
-      <c r="FF8" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="FG8" t="n">
-        <v>0.2547169811320755</v>
-      </c>
-      <c r="FH8" t="n">
-        <v>0.3170731707317073</v>
-      </c>
-      <c r="FI8" t="n">
-        <v>0.2415730337078652</v>
-      </c>
-      <c r="FJ8" t="n">
-        <v>0.3225806451612903</v>
-      </c>
-      <c r="FK8" t="n">
-        <v>0.5306122448979592</v>
-      </c>
-      <c r="FL8" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="FM8" t="n">
-        <v>0.7037037037037037</v>
-      </c>
-      <c r="FN8" t="n">
-        <v>0.7518796992481203</v>
-      </c>
-      <c r="FO8" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="FP8" t="n">
-        <v>0.02421307506053269</v>
-      </c>
-      <c r="FQ8" t="n">
-        <v>95.75</v>
-      </c>
-      <c r="FR8" t="n">
-        <v>0.5952380952380952</v>
-      </c>
-      <c r="FS8" t="n">
-        <v>14.32366492146597</v>
-      </c>
-      <c r="FT8" t="n">
-        <v>15.7509375</v>
-      </c>
-      <c r="FU8" t="n">
-        <v>13.78188481675393</v>
-      </c>
-      <c r="FV8" t="n">
-        <v>15.11229166666667</v>
-      </c>
-      <c r="FW8" t="n">
-        <v>0.2827669902912621</v>
-      </c>
-      <c r="FX8" t="n">
-        <v>0.6995708154506438</v>
-      </c>
-      <c r="FY8" t="n">
-        <v>0.7581395348837209</v>
-      </c>
-      <c r="FZ8" t="n">
-        <v>0.5460122699386503</v>
-      </c>
-      <c r="GA8" t="n">
-        <v>0.2026699029126214</v>
-      </c>
-      <c r="GB8" t="n">
-        <v>0.3592814371257485</v>
-      </c>
-      <c r="GC8" t="n">
-        <v>0.4081632653061225</v>
-      </c>
-      <c r="GD8" t="n">
-        <v>0.3166666666666667</v>
-      </c>
       <c r="GE8" t="n">
-        <v>0.08616504854368932</v>
+        <v>0.08196721311475409</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.4225352112676056</v>
+        <v>0.4</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="GH8" t="n">
         <v>0.4666666666666667</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.1213592233009709</v>
+        <v>0.126775956284153</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.38</v>
+        <v>0.3793103448275862</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.3877551020408163</v>
+        <v>0.3859649122807017</v>
       </c>
       <c r="GL8" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.9318181818181818</v>
       </c>
       <c r="GM8" t="n">
-        <v>0.3070388349514563</v>
+        <v>0.3147540983606558</v>
       </c>
       <c r="GN8" t="n">
-        <v>0.2806324110671937</v>
+        <v>0.28125</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.284</v>
+        <v>0.2842105263157895</v>
       </c>
       <c r="GP8" t="n">
-        <v>0.8169014084507042</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="GQ8" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4489795918367347</v>
       </c>
       <c r="GR8" t="n">
-        <v>0.75</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="GS8" t="n">
-        <v>0.2</v>
+        <v>0.21875</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="GU8" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="GV8" t="inlineStr"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="GV8" t="n">
+        <v>0.5</v>
+      </c>
       <c r="GW8" t="n">
-        <v>0.2045454545454546</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="GX8" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="GY8" t="n">
         <v>1</v>
       </c>
       <c r="GZ8" t="n">
-        <v>0.2796610169491525</v>
+        <v>0.2720306513409962</v>
       </c>
       <c r="HA8" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5774647887323944</v>
       </c>
       <c r="HB8" t="n">
-        <v>0.09322033898305085</v>
+        <v>0.08812260536398467</v>
       </c>
       <c r="HC8" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.3347457627118644</v>
+        <v>0.3524904214559387</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2911392405063291</v>
+        <v>0.2934782608695652</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.7111650485436893</v>
+        <v>0.7224043715846995</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.2806324110671937</v>
+        <v>0.28125</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.5489994498777506</v>
+        <v>0.5502903634361234</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.5338773584905661</v>
+        <v>0.53215</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.5336212121212121</v>
+        <v>0.5301135294117647</v>
       </c>
       <c r="HK8" t="n">
-        <v>0.1086474501108647</v>
+        <v>0.1088911088911089</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.1755027422303473</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.005633802816901409</v>
+        <v>0.009852216748768473</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.1188118811881188</v>
+        <v>0.1202872531418312</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.2881188118811881</v>
+        <v>0.2818671454219031</v>
       </c>
       <c r="HP8" t="n">
-        <v>6.474309978768578</v>
+        <v>6.338551859099804</v>
       </c>
       <c r="HQ8" t="n">
-        <v>25.37220630372493</v>
+        <v>25.35238095238095</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.2848167539267016</v>
+        <v>0.2855796418473139</v>
       </c>
       <c r="HS8" t="n">
         <v>3</v>
       </c>
       <c r="HT8" t="inlineStr"/>
       <c r="HU8" t="n">
-        <v>0.01185770750988142</v>
+        <v>0.01041666666666667</v>
       </c>
     </row>
     <row r="9">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -7133,67 +7133,67 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>26520</v>
+        <v>29400</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>-126</v>
+        <v>-135</v>
       </c>
       <c r="J10" t="n">
-        <v>870</v>
+        <v>967</v>
       </c>
       <c r="K10" t="n">
-        <v>874</v>
+        <v>972</v>
       </c>
       <c r="L10" t="n">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="M10" t="n">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="N10" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="O10" t="n">
-        <v>1744</v>
+        <v>1939</v>
       </c>
       <c r="P10" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="Q10" t="n">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="R10" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="S10" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="T10" t="n">
+        <v>35</v>
+      </c>
+      <c r="U10" t="n">
+        <v>56</v>
+      </c>
+      <c r="V10" t="n">
+        <v>88</v>
+      </c>
+      <c r="W10" t="n">
+        <v>182</v>
+      </c>
+      <c r="X10" t="n">
         <v>30</v>
       </c>
-      <c r="U10" t="n">
-        <v>44</v>
-      </c>
-      <c r="V10" t="n">
-        <v>86</v>
-      </c>
-      <c r="W10" t="n">
-        <v>175</v>
-      </c>
-      <c r="X10" t="n">
-        <v>27</v>
-      </c>
       <c r="Y10" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="Z10" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -7202,241 +7202,241 @@
         <v>15</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AG10" t="n">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AL10" t="n">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="AM10" t="n">
-        <v>450</v>
+        <v>494</v>
       </c>
       <c r="AN10" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="AO10" t="n">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="AP10" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="AQ10" t="n">
-        <v>959</v>
+        <v>1072</v>
       </c>
       <c r="AR10" t="n">
-        <v>1085</v>
+        <v>1207</v>
       </c>
       <c r="AS10" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AT10" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="AU10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AW10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AX10" t="n">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="AY10" t="n">
+        <v>62</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>116</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>69</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>265</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>262</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>260</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>309</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>66</v>
+      </c>
+      <c r="BI10" t="n">
         <v>54</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>97</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>63</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>64</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>226</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>248</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>224</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>264</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>63</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>42</v>
-      </c>
       <c r="BJ10" t="n">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="BK10" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="BL10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="BO10" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="BP10" t="n">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="BQ10" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="BR10" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BU10" t="n">
         <v>13</v>
       </c>
       <c r="BV10" t="n">
-        <v>512</v>
+        <v>571</v>
       </c>
       <c r="BW10" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="BX10" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="BY10" t="n">
         <v>3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="CA10" t="n">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="CB10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CC10" t="n">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="CD10" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="CE10" t="n">
-        <v>424</v>
+        <v>472</v>
       </c>
       <c r="CF10" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="CG10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="CH10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CI10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="CJ10" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="CK10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CL10" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="CM10" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="CN10" t="n">
         <v>9</v>
       </c>
       <c r="CO10" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="CP10" t="n">
         <v>3</v>
       </c>
       <c r="CQ10" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="CR10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CS10" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="CT10" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="CU10" t="n">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="CV10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CW10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="CX10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CY10" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="CZ10" t="n">
         <v>1</v>
       </c>
       <c r="DA10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DB10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="DC10" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="DD10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DE10" t="n">
         <v>4</v>
@@ -7445,38 +7445,40 @@
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="DH10" t="n">
         <v>7</v>
       </c>
       <c r="DI10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DJ10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="DK10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DL10" t="n">
         <v>4</v>
       </c>
       <c r="DM10" t="n">
-        <v>11</v>
-      </c>
-      <c r="DN10" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>1</v>
+      </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP10" t="n">
         <v>11</v>
       </c>
       <c r="DQ10" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="DR10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="DS10" t="n">
         <v>3</v>
@@ -7485,236 +7487,236 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>830</v>
+        <v>921</v>
       </c>
       <c r="DV10" t="n">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="DW10" t="n">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="DX10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="DY10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.5254237288135594</v>
+        <v>0.5019157088122606</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5767441860465117</v>
+        <v>0.5598290598290598</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.8073394495412844</v>
+        <v>0.824</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3504823151125402</v>
+        <v>0.3561253561253561</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.35</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3504823151125402</v>
+        <v>0.3561253561253561</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5244444444444445</v>
+        <v>0.52834008097166</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5070422535211268</v>
+        <v>0.525</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.5567010309278351</v>
+        <v>0.5344827586206896</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5249671484888305</v>
+        <v>0.5307692307692308</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5135135135135135</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.50625</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5676156583629893</v>
+        <v>0.5721925133689839</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.5466101694915254</v>
+        <v>0.571969696969697</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.576530612244898</v>
+        <v>0.5735930735930735</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4086727989487516</v>
+        <v>0.4153846153846154</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.003215434083601286</v>
+        <v>0.002849002849002849</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.1</v>
+        <v>0.09716599190283401</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1527093596059113</v>
+        <v>0.1459227467811159</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06285714285714286</v>
+        <v>0.06043956043956044</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.0379746835443038</v>
       </c>
       <c r="EV10" t="inlineStr"/>
       <c r="EW10" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.6010928961748634</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.15</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.680628272251309</v>
+        <v>0.6866359447004609</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3286384976525822</v>
+        <v>0.3491379310344828</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.7019230769230769</v>
+        <v>0.6796536796536796</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.3147208121827411</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6917293233082706</v>
+        <v>0.6830357142857143</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3219512195121951</v>
+        <v>0.3289183222958058</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4303797468354431</v>
+        <v>0.449438202247191</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2808988764044944</v>
+        <v>0.2978723404255319</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2653061224489796</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.3219178082191781</v>
+        <v>0.3148148148148148</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.5961538461538461</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.8043478260869565</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.6623376623376623</v>
+        <v>0.6227544910179641</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.828125</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.06010928961748634</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="FQ10" t="n">
-        <v>94.69683257918552</v>
+        <v>94.97142857142858</v>
       </c>
       <c r="FR10" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>15.6076525336091</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>14.71954732510288</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>14.96814891416753</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>14.06574074074074</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0.2757396449704142</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0.6137339055793991</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0.7185929648241206</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.5244755244755245</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0.2153846153846154</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.4835164835164835</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0.5146198830409356</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.4886363636363636</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0.09349112426035502</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0.379746835443038</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0.3947368421052632</v>
+      </c>
+      <c r="GH10" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="GI10" t="n">
+        <v>0.114792899408284</v>
+      </c>
+      <c r="GJ10" t="n">
+        <v>0.3917525773195876</v>
+      </c>
+      <c r="GK10" t="n">
+        <v>0.3917525773195876</v>
+      </c>
+      <c r="GL10" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="GM10" t="n">
+        <v>0.3005917159763314</v>
+      </c>
+      <c r="GN10" t="n">
+        <v>0.3425196850393701</v>
+      </c>
+      <c r="GO10" t="n">
+        <v>0.3438735177865613</v>
+      </c>
+      <c r="GP10" t="n">
+        <v>0.7701149425287356</v>
+      </c>
+      <c r="GQ10" t="n">
+        <v>0.4552845528455284</v>
+      </c>
+      <c r="GR10" t="n">
         <v>0.5357142857142857</v>
       </c>
-      <c r="FS10" t="n">
-        <v>15.76712643678161</v>
-      </c>
-      <c r="FT10" t="n">
-        <v>14.64828375286041</v>
-      </c>
-      <c r="FU10" t="n">
-        <v>15.09873563218391</v>
-      </c>
-      <c r="FV10" t="n">
-        <v>14.02871853546911</v>
-      </c>
-      <c r="FW10" t="n">
-        <v>0.266754270696452</v>
-      </c>
-      <c r="FX10" t="n">
-        <v>0.6059113300492611</v>
-      </c>
-      <c r="FY10" t="n">
-        <v>0.7151162790697675</v>
-      </c>
-      <c r="FZ10" t="n">
-        <v>0.5609756097560976</v>
-      </c>
-      <c r="GA10" t="n">
-        <v>0.2299605781865966</v>
-      </c>
-      <c r="GB10" t="n">
-        <v>0.4914285714285714</v>
-      </c>
-      <c r="GC10" t="n">
-        <v>0.524390243902439</v>
-      </c>
-      <c r="GD10" t="n">
-        <v>0.4883720930232558</v>
-      </c>
-      <c r="GE10" t="n">
-        <v>0.09461235216819974</v>
-      </c>
-      <c r="GF10" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="GG10" t="n">
-        <v>0.391304347826087</v>
-      </c>
-      <c r="GH10" t="n">
-        <v>0.4814814814814815</v>
-      </c>
-      <c r="GI10" t="n">
-        <v>0.1077529566360053</v>
-      </c>
-      <c r="GJ10" t="n">
-        <v>0.3780487804878049</v>
-      </c>
-      <c r="GK10" t="n">
-        <v>0.3780487804878049</v>
-      </c>
-      <c r="GL10" t="n">
-        <v>0.9354838709677419</v>
-      </c>
-      <c r="GM10" t="n">
-        <v>0.3009198423127464</v>
-      </c>
-      <c r="GN10" t="n">
-        <v>0.3406113537117904</v>
-      </c>
-      <c r="GO10" t="n">
-        <v>0.3421052631578947</v>
-      </c>
-      <c r="GP10" t="n">
-        <v>0.7564102564102564</v>
-      </c>
-      <c r="GQ10" t="n">
-        <v>0.4324324324324325</v>
-      </c>
-      <c r="GR10" t="n">
-        <v>0.5</v>
-      </c>
       <c r="GS10" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.1351351351351351</v>
+        <v>0.1219512195121951</v>
       </c>
       <c r="GU10" t="n">
         <v>0.3333333333333333</v>
@@ -7723,77 +7725,77 @@
         <v>0.8</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2252252252252252</v>
+        <v>0.2276422764227642</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.36</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.275</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.625</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1125</v>
+        <v>0.1197916666666667</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.28125</v>
+        <v>0.2760416666666667</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.3207547169811321</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.6754270696452037</v>
+        <v>0.6911242603550296</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3406113537117904</v>
+        <v>0.3425196850393701</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5277263192612137</v>
+        <v>0.531592458432304</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5208295774647888</v>
+        <v>0.5256284810126582</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5095175159235669</v>
+        <v>0.5166161375661376</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1044957472660996</v>
+        <v>0.1028446389496718</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1552062868369352</v>
+        <v>0.1553571428571429</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.02229299363057325</v>
+        <v>0.01977401129943503</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1345151199165798</v>
+        <v>0.1408582089552239</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.2356621480709072</v>
+        <v>0.2472014925373134</v>
       </c>
       <c r="HP10" t="n">
-        <v>6.907999999999999</v>
+        <v>6.749797570850203</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.85516129032258</v>
+        <v>25.78485714285715</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.2298850574712644</v>
+        <v>0.2440537745604964</v>
       </c>
       <c r="HS10" t="n">
         <v>3</v>
       </c>
       <c r="HT10" t="inlineStr"/>
       <c r="HU10" t="n">
-        <v>0.004366812227074236</v>
+        <v>0.003937007874015748</v>
       </c>
     </row>
     <row r="11">
@@ -9919,163 +9921,163 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>35160</v>
+        <v>38040</v>
       </c>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>-166</v>
+        <v>-157</v>
       </c>
       <c r="J14" t="n">
-        <v>1199</v>
+        <v>1296</v>
       </c>
       <c r="K14" t="n">
-        <v>1208</v>
+        <v>1306</v>
       </c>
       <c r="L14" t="n">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="M14" t="n">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="N14" t="n">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="O14" t="n">
-        <v>2407</v>
+        <v>2602</v>
       </c>
       <c r="P14" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="Q14" t="n">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="R14" t="n">
         <v>44</v>
       </c>
       <c r="S14" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T14" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="U14" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="V14" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="W14" t="n">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="X14" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Y14" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="Z14" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AA14" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="AB14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
         <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AG14" t="n">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="AH14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AJ14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK14" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AL14" t="n">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="AM14" t="n">
-        <v>678</v>
+        <v>736</v>
       </c>
       <c r="AN14" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="AO14" t="n">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="AP14" t="n">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1242</v>
+        <v>1364</v>
       </c>
       <c r="AR14" t="n">
-        <v>1408</v>
+        <v>1521</v>
       </c>
       <c r="AS14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AT14" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="AU14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV14" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="AW14" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="AX14" t="n">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="AY14" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AZ14" t="n">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="BA14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BB14" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="BC14" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="BD14" t="n">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="BE14" t="n">
-        <v>280</v>
+        <v>322</v>
       </c>
       <c r="BF14" t="n">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="BG14" t="n">
-        <v>345</v>
+        <v>384</v>
       </c>
       <c r="BH14" t="n">
         <v>72</v>
@@ -10084,159 +10086,159 @@
         <v>74</v>
       </c>
       <c r="BJ14" t="n">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="BK14" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="BL14" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="BM14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BN14" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="BO14" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="BP14" t="n">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="BQ14" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BR14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BS14" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="BT14" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="BU14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV14" t="n">
-        <v>625</v>
+        <v>706</v>
       </c>
       <c r="BW14" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="BX14" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="CA14" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="CB14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CC14" t="n">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="CD14" t="n">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="CE14" t="n">
-        <v>597</v>
+        <v>643</v>
       </c>
       <c r="CF14" t="n">
+        <v>21</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>104</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>53</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>51</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>108</v>
+      </c>
+      <c r="CK14" t="n">
         <v>18</v>
       </c>
-      <c r="CG14" t="n">
-        <v>90</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>45</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>45</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>103</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>16</v>
-      </c>
       <c r="CL14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="CM14" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="CN14" t="n">
         <v>10</v>
       </c>
       <c r="CO14" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="CR14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CS14" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="CT14" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="CU14" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CX14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CY14" t="n">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="CZ14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DA14" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="DB14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DC14" t="n">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="DD14" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="DE14" t="inlineStr"/>
       <c r="DF14" t="n">
         <v>4</v>
       </c>
       <c r="DG14" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="DH14" t="n">
         <v>2</v>
       </c>
       <c r="DI14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="DJ14" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="DK14" t="n">
         <v>4</v>
@@ -10245,7 +10247,7 @@
         <v>1</v>
       </c>
       <c r="DM14" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10257,327 +10259,327 @@
         <v>15</v>
       </c>
       <c r="DQ14" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="DR14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="DS14" t="inlineStr"/>
       <c r="DT14" t="n">
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1033</v>
+        <v>1138</v>
       </c>
       <c r="DV14" t="n">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="DW14" t="n">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="DX14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DY14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4530744336569579</v>
+        <v>0.4721407624633431</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5147058823529411</v>
+        <v>0.5296052631578947</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8273381294964028</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3225058004640371</v>
+        <v>0.3254817987152034</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.3653846153846154</v>
+        <v>0.3559322033898305</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3363636363636364</v>
+        <v>0.3247863247863248</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.3225058004640371</v>
+        <v>0.3254817987152034</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4557522123893805</v>
+        <v>0.4633152173913043</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5688073394495413</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4426229508196721</v>
+        <v>0.455</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.4666366095581605</v>
+        <v>0.4729842061512884</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.5673076923076923</v>
+        <v>0.5565476190476191</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.4658703071672355</v>
+        <v>0.4668769716088328</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5032467532467533</v>
+        <v>0.5097305389221557</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.59375</v>
+        <v>0.5854922279792746</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5157142857142857</v>
+        <v>0.5145502645502645</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3886384129846709</v>
+        <v>0.3881961762261014</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0185614849187935</v>
+        <v>0.01927194860813704</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1312684365781711</v>
+        <v>0.1277173913043478</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1735294117647059</v>
+        <v>0.1759776536312849</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.1146245059288538</v>
+        <v>0.1046931407942238</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.01176470588235294</v>
+        <v>0.0198019801980198</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.02205882352941177</v>
+        <v>0.0261437908496732</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6280487804878049</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.90625</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.1351351351351351</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6866197183098591</v>
+        <v>0.66996699669967</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3424657534246575</v>
+        <v>0.3375959079283887</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7125506072874493</v>
+        <v>0.7158671586715867</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2350877192982456</v>
+        <v>0.2564935064935065</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6986817325800376</v>
+        <v>0.6916376306620209</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.2953846153846154</v>
+        <v>0.3018597997138769</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3892617449664429</v>
+        <v>0.3935483870967742</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.329608938547486</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.24</v>
+        <v>0.2769953051643192</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.2235294117647059</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.6396396396396397</v>
+        <v>0.6198347107438017</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.6942148760330579</v>
+        <v>0.6825396825396826</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.75</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7076023391812866</v>
+        <v>0.7112299465240641</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7236842105263158</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03249097472924187</v>
+        <v>0.03517587939698492</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.580204778157</v>
+        <v>98.49842271293376</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="FS14" t="n">
-        <v>14.79015846538782</v>
+        <v>14.84429012345679</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.42599337748344</v>
+        <v>14.39647779479326</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.02485404503753</v>
+        <v>14.06373456790124</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.8444536423841</v>
+        <v>13.83032159264931</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.3065825067628494</v>
+        <v>0.2975893599334996</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5642458100558659</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6761565836298933</v>
+        <v>0.6847457627118644</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.5</v>
+        <v>0.5247524752475248</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2281334535617674</v>
+        <v>0.2302576891105569</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.3280632411067194</v>
+        <v>0.3465703971119133</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.3705357142857143</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.3493975903614458</v>
+        <v>0.3854166666666667</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.07664562669071236</v>
+        <v>0.08395677472984206</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.4235294117647059</v>
+        <v>0.4257425742574257</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4343434343434344</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1226330027051398</v>
+        <v>0.1271820448877805</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3602941176470588</v>
+        <v>0.3660130718954248</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3758389261744967</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.9795918367346939</v>
+        <v>0.9821428571428571</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.2660054102795311</v>
+        <v>0.2610141313383209</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.3050847457627119</v>
+        <v>0.3057324840764331</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.3106796116504854</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4743589743589743</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="GS14" t="n">
         <v>0.25</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.108974358974359</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="GU14" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5</v>
       </c>
       <c r="GV14" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2243589743589744</v>
+        <v>0.2321428571428572</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="GY14" t="n">
-        <v>0.7</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.348122866894198</v>
+        <v>0.3375394321766562</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5607476635514018</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.10580204778157</v>
+        <v>0.1009463722397476</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3125</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.2696245733788396</v>
+        <v>0.2681388012618297</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3417721518987342</v>
+        <v>0.3294117647058823</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6952209197475203</v>
+        <v>0.685785536159601</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.3050847457627119</v>
+        <v>0.3057324840764331</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5505714221014493</v>
+        <v>0.5494381886477462</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5436353448275862</v>
+        <v>0.543872131147541</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5447358131487889</v>
+        <v>0.5408682108626198</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09658617818484597</v>
+        <v>0.09823484267075978</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1484375</v>
+        <v>0.1510791366906475</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.004618937644341801</v>
+        <v>0.004264392324093817</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1682769726247987</v>
+        <v>0.1656891495601173</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2914653784219002</v>
+        <v>0.2859237536656892</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.286430678466076</v>
+        <v>6.533152173913043</v>
       </c>
       <c r="HQ14" t="n">
-        <v>24.98992974238876</v>
+        <v>24.95874730021598</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2894078398665554</v>
+        <v>0.2878086419753086</v>
       </c>
       <c r="HS14" t="n">
         <v>6</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.01694915254237288</v>
+        <v>0.01592356687898089</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -5054,307 +5054,307 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>44100</v>
+        <v>46980</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>-11</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>1450</v>
+        <v>1538</v>
       </c>
       <c r="K7" t="n">
-        <v>1455</v>
+        <v>1543</v>
       </c>
       <c r="L7" t="n">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="M7" t="n">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="N7" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="O7" t="n">
-        <v>2905</v>
+        <v>3081</v>
       </c>
       <c r="P7" t="n">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="Q7" t="n">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="R7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T7" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="U7" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="V7" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="W7" t="n">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y7" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Z7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>122</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE7" t="n">
         <v>39</v>
       </c>
-      <c r="AA7" t="n">
-        <v>111</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>35</v>
-      </c>
       <c r="AF7" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="AG7" t="n">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AJ7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>94</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>463</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>894</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>179</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>490</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>284</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1747</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1742</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>58</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AU7" t="n">
         <v>27</v>
       </c>
-      <c r="AK7" t="n">
-        <v>89</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>432</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>845</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>166</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>453</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>276</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1638</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1649</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>116</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>25</v>
-      </c>
       <c r="AV7" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AW7" t="n">
         <v>41</v>
       </c>
       <c r="AX7" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="AY7" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AZ7" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="BA7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB7" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="BC7" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BD7" t="n">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="BE7" t="n">
-        <v>448</v>
+        <v>486</v>
       </c>
       <c r="BF7" t="n">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="BG7" t="n">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="BH7" t="n">
         <v>66</v>
       </c>
       <c r="BI7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="BJ7" t="n">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="BK7" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="BL7" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="BM7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN7" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="BO7" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="BP7" t="n">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="BQ7" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="BR7" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="BS7" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="BT7" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BU7" t="n">
         <v>18</v>
       </c>
       <c r="BV7" t="n">
-        <v>880</v>
+        <v>957</v>
       </c>
       <c r="BW7" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="BX7" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="BY7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="CA7" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="CB7" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="CC7" t="n">
-        <v>474</v>
+        <v>512</v>
       </c>
       <c r="CD7" t="n">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="CE7" t="n">
-        <v>715</v>
+        <v>766</v>
       </c>
       <c r="CF7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CG7" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="CH7" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="CI7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="CJ7" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="CK7" t="n">
         <v>28</v>
       </c>
       <c r="CL7" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="CM7" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="CN7" t="n">
         <v>15</v>
       </c>
       <c r="CO7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CQ7" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="CR7" t="n">
         <v>32</v>
       </c>
       <c r="CS7" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="CT7" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="CU7" t="n">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="CV7" t="n">
         <v>4</v>
       </c>
       <c r="CW7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CX7" t="n">
         <v>29</v>
       </c>
       <c r="CY7" t="n">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="CZ7" t="n">
         <v>3</v>
       </c>
       <c r="DA7" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="DB7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="DC7" t="n">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="DD7" t="n">
         <v>30</v>
@@ -5364,25 +5364,25 @@
         <v>5</v>
       </c>
       <c r="DG7" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="DH7" t="n">
         <v>5</v>
       </c>
       <c r="DI7" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="DJ7" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="DK7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DL7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DM7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="DN7" t="n">
         <v>3</v>
@@ -5391,332 +5391,332 @@
         <v>4</v>
       </c>
       <c r="DP7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="DQ7" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="DR7" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="DS7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DT7" t="n">
         <v>2</v>
       </c>
       <c r="DU7" t="n">
-        <v>1412</v>
+        <v>1509</v>
       </c>
       <c r="DV7" t="n">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="DW7" t="n">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="DX7" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="DY7" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.5248380129589633</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.5544554455445545</v>
+        <v>0.5599078341013825</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.8674698795180723</v>
+        <v>0.8770949720670391</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.3664459161147903</v>
+        <v>0.3653061224489796</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.3968253968253968</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.3664459161147903</v>
+        <v>0.3653061224489796</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.5112426035502958</v>
+        <v>0.5178970917225951</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.4741379310344828</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.4953703703703703</v>
+        <v>0.5064377682403434</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.524653312788906</v>
+        <v>0.5285404624277457</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.5167597765363129</v>
+        <v>0.5211640211640212</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.4823529411764706</v>
+        <v>0.4945355191256831</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.5584016393442623</v>
+        <v>0.5600513808606294</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.5406698564593302</v>
+        <v>0.5409090909090909</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.5362318840579711</v>
+        <v>0.5440180586907449</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.3489984591679507</v>
+        <v>0.3540462427745665</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.006622516556291391</v>
+        <v>0.00816326530612245</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.09230769230769231</v>
+        <v>0.09172259507829977</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.1127450980392157</v>
+        <v>0.1126436781609195</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.08902077151335312</v>
+        <v>0.08732394366197183</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.02</v>
+        <v>0.01923076923076923</v>
       </c>
       <c r="EV7" t="inlineStr"/>
       <c r="EW7" t="n">
-        <v>0.5147679324894515</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.8363636363636363</v>
+        <v>0.85</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.5979020979020979</v>
+        <v>0.5825242718446602</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.3694581280788177</v>
+        <v>0.3632075471698113</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.6945945945945946</v>
+        <v>0.7095959595959596</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.296028880866426</v>
+        <v>0.3</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.6524390243902439</v>
+        <v>0.6539007092198581</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.3396778916544656</v>
+        <v>0.3370165745856354</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.4342105263157895</v>
+        <v>0.4213836477987422</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.355</v>
+        <v>0.3509615384615384</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.2456140350877193</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2718446601941747</v>
+        <v>0.2767857142857143</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.3661971830985916</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.6631578947368421</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.5214723926380368</v>
+        <v>0.5229885057471264</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.6942446043165468</v>
+        <v>0.71</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.04470198675496689</v>
+        <v>0.0453125</v>
       </c>
       <c r="FQ7" t="n">
-        <v>94.85714285714286</v>
+        <v>94.43678160919541</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.4487179487179487</v>
+        <v>0.4578313253012048</v>
       </c>
       <c r="FS7" t="n">
-        <v>15.05675862068965</v>
+        <v>15.20559167750325</v>
       </c>
       <c r="FT7" t="n">
-        <v>15.30426116838488</v>
+        <v>15.29086195722618</v>
       </c>
       <c r="FU7" t="n">
-        <v>14.32041379310345</v>
+        <v>14.45884265279584</v>
       </c>
       <c r="FV7" t="n">
-        <v>14.50508591065292</v>
+        <v>14.49961114711601</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.3143297380585516</v>
+        <v>0.3143063583815029</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.625</v>
+        <v>0.632183908045977</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.7044198895027625</v>
+        <v>0.7124352331606217</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.5803921568627451</v>
+        <v>0.5854545454545454</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.2596302003081664</v>
+        <v>0.2565028901734104</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.3976261127596439</v>
+        <v>0.4056338028169014</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.4364820846905538</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.4328358208955224</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.07704160246533127</v>
+        <v>0.07514450867052024</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.43</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.4387755102040816</v>
+        <v>0.4313725490196079</v>
       </c>
       <c r="GH7" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.08551617873651772</v>
+        <v>0.08815028901734104</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.360655737704918</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.360655737704918</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.263482280431433</v>
+        <v>0.2658959537572254</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3713450292397661</v>
+        <v>0.3668478260869565</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.3746312684365782</v>
+        <v>0.3708791208791209</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.8346456692913385</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.4189944134078212</v>
+        <v>0.4126984126984127</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.5066666666666667</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.275</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.1005586592178771</v>
+        <v>0.1058201058201058</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.4</v>
       </c>
       <c r="GV7" t="n">
         <v>1</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.2513966480446927</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.4</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.3617647058823529</v>
+        <v>0.3579234972677596</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.6260162601626016</v>
+        <v>0.6259541984732825</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.1065573770491803</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.261764705882353</v>
+        <v>0.2568306010928962</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.303370786516854</v>
+        <v>0.2978723404255319</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.6633281972265023</v>
+        <v>0.6683526011560693</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.3713450292397661</v>
+        <v>0.3668478260869565</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.5502963292117465</v>
+        <v>0.5506954314720812</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.5412296</v>
+        <v>0.5389345864661653</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.5580925595238095</v>
+        <v>0.5558452908587257</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.107670654468684</v>
+        <v>0.1039046988749173</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.1536863966770509</v>
+        <v>0.1496062992125984</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.01091703056768559</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.137973137973138</v>
+        <v>0.1362335432169433</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.2716727716727717</v>
+        <v>0.2764739553520321</v>
       </c>
       <c r="HP7" t="n">
-        <v>6.219763313609468</v>
+        <v>6.175391498881432</v>
       </c>
       <c r="HQ7" t="n">
-        <v>25.72022222222222</v>
+        <v>25.68374485596708</v>
       </c>
       <c r="HR7" t="n">
-        <v>0.2703448275862069</v>
+        <v>0.2724317295188556</v>
       </c>
       <c r="HS7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="HT7" t="n">
         <v>1</v>
       </c>
       <c r="HU7" t="n">
-        <v>0.008771929824561403</v>
+        <v>0.0108695652173913</v>
       </c>
     </row>
     <row r="8">
@@ -5751,310 +5751,310 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>31980</v>
+        <v>34860</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>-205</v>
+        <v>-221</v>
       </c>
       <c r="J8" t="n">
-        <v>1061</v>
+        <v>1148</v>
       </c>
       <c r="K8" t="n">
-        <v>1068</v>
+        <v>1157</v>
       </c>
       <c r="L8" t="n">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="M8" t="n">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="N8" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="O8" t="n">
-        <v>2129</v>
+        <v>2305</v>
       </c>
       <c r="P8" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="Q8" t="n">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="R8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S8" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T8" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="U8" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="V8" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W8" t="n">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="X8" t="n">
         <v>30</v>
       </c>
       <c r="Y8" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Z8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AA8" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="AB8" t="n">
         <v>2</v>
       </c>
       <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
         <v>7</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>87</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>316</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>101</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>295</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>556</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>134</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>439</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>215</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1207</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1428</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>79</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>31</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>151</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>159</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>126</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>90</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>352</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>278</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>312</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>342</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>60</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>62</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>316</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>87</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>46</v>
+      </c>
+      <c r="BM8" t="n">
         <v>6</v>
       </c>
-      <c r="AE8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>81</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>288</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>92</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>273</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>511</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>125</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>404</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>193</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1114</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1319</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>41</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="BN8" t="n">
+        <v>139</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>114</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>253</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>70</v>
       </c>
-      <c r="AU8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>134</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>68</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>146</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>33</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>115</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>79</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>314</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>260</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>286</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>324</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>51</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>54</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>288</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>81</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>130</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>108</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>238</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>67</v>
-      </c>
       <c r="BR8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BS8" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="BT8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BU8" t="n">
         <v>14</v>
       </c>
       <c r="BV8" t="n">
-        <v>584</v>
+        <v>620</v>
       </c>
       <c r="BW8" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="BX8" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="BY8" t="n">
         <v>3</v>
       </c>
       <c r="BZ8" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="CA8" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="CB8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="CC8" t="n">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="CD8" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="CE8" t="n">
-        <v>466</v>
+        <v>514</v>
       </c>
       <c r="CF8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CG8" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="CH8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="CI8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CJ8" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="CK8" t="n">
         <v>16</v>
       </c>
       <c r="CL8" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="CM8" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="CN8" t="n">
         <v>15</v>
       </c>
       <c r="CO8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CP8" t="n">
         <v>5</v>
       </c>
       <c r="CQ8" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="CR8" t="n">
         <v>17</v>
       </c>
       <c r="CS8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="CT8" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="CU8" t="n">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="CV8" t="n">
         <v>3</v>
       </c>
       <c r="CW8" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="CX8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CY8" t="n">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="CZ8" t="n">
         <v>3</v>
       </c>
       <c r="DA8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="DB8" t="n">
         <v>18</v>
       </c>
       <c r="DC8" t="n">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="DD8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DE8" t="n">
         <v>2</v>
@@ -6063,25 +6063,25 @@
         <v>5</v>
       </c>
       <c r="DG8" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="DH8" t="n">
+        <v>5</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>37</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>49</v>
+      </c>
+      <c r="DK8" t="n">
         <v>4</v>
       </c>
-      <c r="DI8" t="n">
-        <v>31</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>45</v>
-      </c>
-      <c r="DK8" t="n">
+      <c r="DL8" t="n">
         <v>3</v>
       </c>
-      <c r="DL8" t="n">
-        <v>2</v>
-      </c>
       <c r="DM8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
@@ -6090,13 +6090,13 @@
         <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DQ8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="DR8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="DS8" t="n">
         <v>1</v>
@@ -6105,317 +6105,317 @@
         <v>2</v>
       </c>
       <c r="DU8" t="n">
-        <v>980</v>
+        <v>1056</v>
       </c>
       <c r="DV8" t="n">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="DW8" t="n">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="DX8" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="DY8" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4711864406779661</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.5284552845528455</v>
+        <v>0.5265151515151515</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.864</v>
+        <v>0.8507462686567164</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.3094059405940594</v>
+        <v>0.3052391799544419</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.2869565217391304</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.3094059405940594</v>
+        <v>0.3052391799544419</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.5342465753424658</v>
+        <v>0.5305755395683454</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.5857142857142857</v>
+        <v>0.5822784810126582</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.4657534246575342</v>
+        <v>0.4842767295597484</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.5032786885245901</v>
+        <v>0.4984924623115578</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.5561224489795918</v>
+        <v>0.5545454545454546</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.4501915708812261</v>
+        <v>0.4596491228070175</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.5377906976744186</v>
+        <v>0.533717834960071</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.5782608695652174</v>
+        <v>0.5725190839694656</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.4968051118210863</v>
+        <v>0.5057971014492754</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.4415300546448088</v>
+        <v>0.4412060301507538</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.01237623762376238</v>
+        <v>0.01366742596810934</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0821917808219178</v>
+        <v>0.08273381294964029</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.07392996108949416</v>
+        <v>0.07773851590106007</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.111731843575419</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.04</v>
+        <v>0.03896103896103896</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01724137931034483</v>
+        <v>0.01626016260162602</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.5688622754491018</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.08571428571428572</v>
+        <v>0.075</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.6051502145922747</v>
+        <v>0.6175298804780877</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.2742616033755274</v>
+        <v>0.3038461538461538</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.7251184834123223</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.2664233576642336</v>
+        <v>0.25</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.6621621621621622</v>
+        <v>0.6659793814432989</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.2700587084148728</v>
+        <v>0.275</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.3</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.25</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.2978723404255319</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.2475247524752475</v>
+        <v>0.2321428571428572</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.3194444444444444</v>
+        <v>0.3026315789473684</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.6413043478260869</v>
+        <v>0.65</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.756578947368421</v>
+        <v>0.7470588235294118</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.6440677966101694</v>
+        <v>0.640625</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.02365591397849462</v>
+        <v>0.0275049115913556</v>
       </c>
       <c r="FQ8" t="n">
-        <v>95.86491557223265</v>
+        <v>95.21514629948365</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="FS8" t="n">
-        <v>14.38605089538172</v>
+        <v>14.45095818815331</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.65205992509363</v>
+        <v>15.79109766637857</v>
       </c>
       <c r="FU8" t="n">
-        <v>13.8311027332705</v>
+        <v>13.88745644599303</v>
       </c>
       <c r="FV8" t="n">
-        <v>14.9749063670412</v>
+        <v>15.0961970613656</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.2808743169398907</v>
+        <v>0.2844221105527638</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.688715953307393</v>
+        <v>0.6819787985865724</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.7436974789915967</v>
+        <v>0.7394636015325671</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.5310734463276836</v>
+        <v>0.5233160621761658</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1956284153005464</v>
+        <v>0.1969849246231156</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.3687150837988827</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.4150943396226415</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="GD8" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.08196721311475409</v>
+        <v>0.07738693467336684</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.4</v>
+        <v>0.3896103896103896</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4054054054054054</v>
       </c>
       <c r="GH8" t="n">
         <v>0.4666666666666667</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.126775956284153</v>
+        <v>0.1236180904522613</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.3793103448275862</v>
+        <v>0.3821138211382114</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.3859649122807017</v>
+        <v>0.3884297520661157</v>
       </c>
       <c r="GL8" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.9361702127659575</v>
       </c>
       <c r="GM8" t="n">
-        <v>0.3147540983606558</v>
+        <v>0.3175879396984925</v>
       </c>
       <c r="GN8" t="n">
-        <v>0.28125</v>
+        <v>0.2753164556962026</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.2842105263157895</v>
+        <v>0.2788461538461539</v>
       </c>
       <c r="GP8" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.8045977011494253</v>
       </c>
       <c r="GQ8" t="n">
-        <v>0.4489795918367347</v>
+        <v>0.4636363636363636</v>
       </c>
       <c r="GR8" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="GS8" t="n">
-        <v>0.21875</v>
+        <v>0.1944444444444444</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07272727272727272</v>
       </c>
       <c r="GU8" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="GV8" t="n">
         <v>0.5</v>
       </c>
       <c r="GW8" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2090909090909091</v>
       </c>
       <c r="GX8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="GY8" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="GZ8" t="n">
-        <v>0.2720306513409962</v>
+        <v>0.2736842105263158</v>
       </c>
       <c r="HA8" t="n">
-        <v>0.5774647887323944</v>
+        <v>0.6025641025641025</v>
       </c>
       <c r="HB8" t="n">
-        <v>0.08812260536398467</v>
+        <v>0.08771929824561403</v>
       </c>
       <c r="HC8" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.28</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.3524904214559387</v>
+        <v>0.3543859649122807</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2934782608695652</v>
+        <v>0.2871287128712871</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.7224043715846995</v>
+        <v>0.7256281407035176</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.28125</v>
+        <v>0.2753164556962026</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.5502903634361234</v>
+        <v>0.5507415991902834</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.53215</v>
+        <v>0.5367835714285714</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.5301135294117647</v>
+        <v>0.5313059139784947</v>
       </c>
       <c r="HK8" t="n">
-        <v>0.1088911088911089</v>
+        <v>0.1091743119266055</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1759259259259259</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.009852216748768473</v>
+        <v>0.01131221719457014</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.1202872531418312</v>
+        <v>0.1251035625517813</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.2818671454219031</v>
+        <v>0.2916321458160729</v>
       </c>
       <c r="HP8" t="n">
-        <v>6.338551859099804</v>
+        <v>6.237230215827338</v>
       </c>
       <c r="HQ8" t="n">
-        <v>25.35238095238095</v>
+        <v>25.32396313364055</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.2855796418473139</v>
+        <v>0.2909407665505226</v>
       </c>
       <c r="HS8" t="n">
         <v>3</v>
       </c>
       <c r="HT8" t="inlineStr"/>
       <c r="HU8" t="n">
-        <v>0.01041666666666667</v>
+        <v>0.01265822784810127</v>
       </c>
     </row>
     <row r="9">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -7133,310 +7133,310 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>29400</v>
+        <v>32280</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>-135</v>
+        <v>-150</v>
       </c>
       <c r="J10" t="n">
-        <v>967</v>
+        <v>1064</v>
       </c>
       <c r="K10" t="n">
-        <v>972</v>
+        <v>1069</v>
       </c>
       <c r="L10" t="n">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="M10" t="n">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="N10" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="O10" t="n">
-        <v>1939</v>
+        <v>2133</v>
       </c>
       <c r="P10" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="Q10" t="n">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="R10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S10" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T10" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="U10" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="V10" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="W10" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="X10" t="n">
         <v>30</v>
       </c>
       <c r="Y10" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AB10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="AG10" t="n">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>64</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>282</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>533</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>138</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>392</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>202</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>45</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>168</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>71</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>132</v>
+      </c>
+      <c r="BA10" t="n">
         <v>28</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>53</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>261</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>494</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>125</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>351</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>175</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1072</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1207</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>43</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>151</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>62</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>116</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>24</v>
-      </c>
       <c r="BB10" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="BC10" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="BD10" t="n">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="BE10" t="n">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="BF10" t="n">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="BG10" t="n">
-        <v>309</v>
+        <v>342</v>
       </c>
       <c r="BH10" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="BI10" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BJ10" t="n">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="BK10" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="BL10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="BO10" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="BP10" t="n">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="BQ10" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="BR10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="BT10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="BU10" t="n">
         <v>13</v>
       </c>
       <c r="BV10" t="n">
-        <v>571</v>
+        <v>634</v>
       </c>
       <c r="BW10" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="BX10" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="BY10" t="n">
         <v>3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="CA10" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="CB10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CC10" t="n">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="CD10" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="CE10" t="n">
-        <v>472</v>
+        <v>515</v>
       </c>
       <c r="CF10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CG10" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="CH10" t="n">
+        <v>37</v>
+      </c>
+      <c r="CI10" t="n">
         <v>33</v>
       </c>
-      <c r="CI10" t="n">
-        <v>29</v>
-      </c>
       <c r="CJ10" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="CK10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CL10" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="CM10" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="CN10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CO10" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="CP10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ10" t="n">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="CR10" t="n">
         <v>16</v>
       </c>
       <c r="CS10" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="CT10" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="CU10" t="n">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="CV10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CW10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="CX10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="CY10" t="n">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="CZ10" t="n">
         <v>1</v>
       </c>
       <c r="DA10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="DB10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DC10" t="n">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="DD10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="DE10" t="n">
         <v>4</v>
@@ -7445,40 +7445,40 @@
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="DH10" t="n">
         <v>7</v>
       </c>
       <c r="DI10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="DJ10" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="DK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL10" t="n">
         <v>5</v>
       </c>
-      <c r="DL10" t="n">
-        <v>4</v>
-      </c>
       <c r="DM10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="DP10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="DR10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="DS10" t="n">
         <v>3</v>
@@ -7487,315 +7487,315 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>921</v>
+        <v>1012</v>
       </c>
       <c r="DV10" t="n">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="DW10" t="n">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="DX10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="DY10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.5019157088122606</v>
+        <v>0.5177304964539007</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5598290598290598</v>
+        <v>0.5770750988142292</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.824</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3561253561253561</v>
+        <v>0.3520408163265306</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.3720930232558139</v>
+        <v>0.375</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3146067415730337</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3561253561253561</v>
+        <v>0.3520408163265306</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.52834008097166</v>
+        <v>0.5290806754221389</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.525</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.5344827586206896</v>
+        <v>0.5378787878787878</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5307692307692308</v>
+        <v>0.5286486486486487</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5413533834586466</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5113122171945701</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5721925133689839</v>
+        <v>0.5718446601941748</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.571969696969697</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5735930735930735</v>
+        <v>0.5802238805970149</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4153846153846154</v>
+        <v>0.4237837837837838</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.002849002849002849</v>
+        <v>0.002551020408163265</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.09716599190283401</v>
+        <v>0.09380863039399624</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1459227467811159</v>
+        <v>0.1400778210116732</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06043956043956044</v>
+        <v>0.05729166666666666</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0379746835443038</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="EV10" t="inlineStr"/>
       <c r="EW10" t="n">
-        <v>0.6010928961748634</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.15</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6866359447004609</v>
+        <v>0.6962025316455697</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3491379310344828</v>
+        <v>0.344</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.6796536796536796</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3012048192771085</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6830357142857143</v>
+        <v>0.6871165644171779</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3289183222958058</v>
+        <v>0.3226452905811623</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.449438202247191</v>
+        <v>0.4536082474226804</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2978723404255319</v>
+        <v>0.2929292929292929</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2653061224489796</v>
+        <v>0.2407407407407407</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.3148148148148148</v>
+        <v>0.3146067415730337</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.288135593220339</v>
+        <v>0.2676056338028169</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6730769230769231</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8360655737704918</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.6227544910179641</v>
+        <v>0.625</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.828125</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="FQ10" t="n">
-        <v>94.97142857142858</v>
+        <v>95.15241635687732</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.55</v>
       </c>
       <c r="FS10" t="n">
-        <v>15.6076525336091</v>
+        <v>15.48242481203008</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.71954732510288</v>
+        <v>14.78643592142189</v>
       </c>
       <c r="FU10" t="n">
-        <v>14.96814891416753</v>
+        <v>14.84389097744361</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.06574074074074</v>
+        <v>14.17034611786717</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.2757396449704142</v>
+        <v>0.2778378378378378</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6137339055793991</v>
+        <v>0.6186770428015564</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7185929648241206</v>
+        <v>0.7194570135746606</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5244755244755245</v>
+        <v>0.5408805031446541</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.2153846153846154</v>
+        <v>0.2075675675675676</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4835164835164835</v>
+        <v>0.484375</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.5146198830409356</v>
+        <v>0.5138121546961326</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4886363636363636</v>
+        <v>0.5053763440860215</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.09349112426035502</v>
+        <v>0.09081081081081081</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.379746835443038</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="GH10" t="n">
         <v>0.4333333333333333</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.114792899408284</v>
+        <v>0.1221621621621622</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3917525773195876</v>
+        <v>0.3716814159292036</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3917525773195876</v>
+        <v>0.3716814159292036</v>
       </c>
       <c r="GL10" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.3005917159763314</v>
+        <v>0.3016216216216216</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3425196850393701</v>
+        <v>0.3440860215053764</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3438735177865613</v>
+        <v>0.3453237410071943</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.7701149425287356</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.4552845528455284</v>
+        <v>0.4586466165413534</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5409836065573771</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1203007518796992</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="GV10" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2276422764227642</v>
+        <v>0.2406015037593985</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.375</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.75</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2895927601809955</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.625</v>
+        <v>0.65625</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1197916666666667</v>
+        <v>0.1131221719457014</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.32</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2760416666666667</v>
+        <v>0.2895927601809955</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3207547169811321</v>
+        <v>0.3125</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.6911242603550296</v>
+        <v>0.7016216216216217</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3425196850393701</v>
+        <v>0.3440860215053764</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.531592458432304</v>
+        <v>0.5348122559652928</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5256284810126582</v>
+        <v>0.5259648809523809</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5166161375661376</v>
+        <v>0.5191871559633028</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1028446389496718</v>
+        <v>0.1074626865671642</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1553571428571429</v>
+        <v>0.1655737704918033</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.01977401129943503</v>
+        <v>0.01772151898734177</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1408582089552239</v>
+        <v>0.1423728813559322</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.2472014925373134</v>
+        <v>0.2635593220338983</v>
       </c>
       <c r="HP10" t="n">
-        <v>6.749797570850203</v>
+        <v>6.654033771106942</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.78485714285715</v>
+        <v>25.72046035805627</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.2440537745604964</v>
+        <v>0.2612781954887218</v>
       </c>
       <c r="HS10" t="n">
         <v>3</v>
       </c>
       <c r="HT10" t="inlineStr"/>
       <c r="HU10" t="n">
-        <v>0.003937007874015748</v>
+        <v>0.003584229390681004</v>
       </c>
     </row>
     <row r="11">
@@ -9921,67 +9921,67 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>38040</v>
+        <v>40920</v>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>-157</v>
+        <v>-142</v>
       </c>
       <c r="J14" t="n">
-        <v>1296</v>
+        <v>1392</v>
       </c>
       <c r="K14" t="n">
-        <v>1306</v>
+        <v>1404</v>
       </c>
       <c r="L14" t="n">
+        <v>397</v>
+      </c>
+      <c r="M14" t="n">
+        <v>491</v>
+      </c>
+      <c r="N14" t="n">
+        <v>200</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2796</v>
+      </c>
+      <c r="P14" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q14" t="n">
         <v>373</v>
       </c>
-      <c r="M14" t="n">
-        <v>448</v>
-      </c>
-      <c r="N14" t="n">
-        <v>189</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2602</v>
-      </c>
-      <c r="P14" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>358</v>
-      </c>
       <c r="R14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="S14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="U14" t="n">
+        <v>113</v>
+      </c>
+      <c r="V14" t="n">
         <v>107</v>
       </c>
-      <c r="V14" t="n">
-        <v>96</v>
-      </c>
       <c r="W14" t="n">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="X14" t="n">
         <v>43</v>
       </c>
       <c r="Y14" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Z14" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AA14" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="AB14" t="n">
         <v>10</v>
@@ -9990,255 +9990,257 @@
         <v>20</v>
       </c>
       <c r="AD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>108</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>344</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>92</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>363</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>779</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>169</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>506</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>254</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1487</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1629</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>112</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>62</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>248</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>207</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>43</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>129</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>110</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>429</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>348</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>378</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>432</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>75</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>344</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>99</v>
+      </c>
+      <c r="BM14" t="n">
         <v>10</v>
       </c>
-      <c r="AE14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>96</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>314</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>39</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>341</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>736</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>152</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>467</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>226</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1364</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1521</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>62</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>109</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>59</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>39</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>226</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>91</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>200</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>117</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>94</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>390</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>322</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>360</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>384</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>72</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>74</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>314</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>96</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>94</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>9</v>
-      </c>
       <c r="BN14" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="BO14" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="BP14" t="n">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="BQ14" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="BR14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="BT14" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="BU14" t="n">
         <v>18</v>
       </c>
       <c r="BV14" t="n">
-        <v>706</v>
+        <v>780</v>
       </c>
       <c r="BW14" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="BX14" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="CA14" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="CB14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CC14" t="n">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="CD14" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="CE14" t="n">
-        <v>643</v>
+        <v>689</v>
       </c>
       <c r="CF14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CG14" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="CH14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CI14" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="CJ14" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="CK14" t="n">
         <v>18</v>
       </c>
       <c r="CL14" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="CM14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="CN14" t="n">
         <v>10</v>
       </c>
       <c r="CO14" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="CR14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CS14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CT14" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="CU14" t="n">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="CX14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CY14" t="n">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="CZ14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DA14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DB14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="DC14" t="n">
-        <v>299</v>
+        <v>332</v>
       </c>
       <c r="DD14" t="n">
         <v>28</v>
       </c>
-      <c r="DE14" t="inlineStr"/>
+      <c r="DE14" t="n">
+        <v>1</v>
+      </c>
       <c r="DF14" t="n">
         <v>4</v>
       </c>
       <c r="DG14" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="DH14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DI14" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="DJ14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="DK14" t="n">
         <v>4</v>
@@ -10247,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="DM14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10259,248 +10261,250 @@
         <v>15</v>
       </c>
       <c r="DQ14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="DR14" t="n">
         <v>43</v>
       </c>
-      <c r="DS14" t="inlineStr"/>
+      <c r="DS14" t="n">
+        <v>1</v>
+      </c>
       <c r="DT14" t="n">
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1138</v>
+        <v>1239</v>
       </c>
       <c r="DV14" t="n">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="DW14" t="n">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="DX14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="DY14" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4721407624633431</v>
+        <v>0.4793388429752066</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5296052631578947</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8520710059171598</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3254817987152034</v>
+        <v>0.3339920948616601</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.3559322033898305</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3247863247863248</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.3254817987152034</v>
+        <v>0.3339920948616601</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4633152173913043</v>
+        <v>0.4659820282413351</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.5688073394495413</v>
+        <v>0.5803571428571429</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.455</v>
+        <v>0.4589371980676328</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.4729842061512884</v>
+        <v>0.4797665369649806</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.5565476190476191</v>
+        <v>0.5804597701149425</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.4668769716088328</v>
+        <v>0.4747023809523809</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5097305389221557</v>
+        <v>0.5181437543614794</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.5854922279792746</v>
+        <v>0.6138613861386139</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5145502645502645</v>
+        <v>0.5270935960591133</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3881961762261014</v>
+        <v>0.3937743190661478</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01927194860813704</v>
+        <v>0.01976284584980237</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1277173913043478</v>
+        <v>0.1270860077021823</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1759776536312849</v>
+        <v>0.1715817694369973</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.1046931407942238</v>
+        <v>0.1040268456375839</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0198019801980198</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0261437908496732</v>
+        <v>0.02469135802469136</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.6270270270270271</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.1351351351351351</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.66996699669967</v>
+        <v>0.6728971962616822</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3375959079283887</v>
+        <v>0.3309002433090024</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7158671586715867</v>
+        <v>0.7190635451505016</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2564935064935065</v>
+        <v>0.2613981762917933</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6916376306620209</v>
+        <v>0.6951612903225807</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.3018597997138769</v>
+        <v>0.3</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3935483870967742</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.329608938547486</v>
+        <v>0.3227513227513227</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2769953051643192</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.6198347107438017</v>
+        <v>0.6124031007751938</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.6825396825396826</v>
+        <v>0.6870229007633588</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.75</v>
+        <v>0.7704918032786885</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7112299465240641</v>
+        <v>0.7093596059113301</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7261904761904762</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03517587939698492</v>
+        <v>0.03475513428120063</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.49842271293376</v>
+        <v>98.39296187683284</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.7678571428571429</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="FS14" t="n">
-        <v>14.84429012345679</v>
+        <v>14.89762931034483</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.39647779479326</v>
+        <v>14.375</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.06373456790124</v>
+        <v>14.15431034482759</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.83032159264931</v>
+        <v>13.80491452991453</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2975893599334996</v>
+        <v>0.2902723735408561</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5642458100558659</v>
+        <v>0.5710455764075067</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6847457627118644</v>
+        <v>0.6893203883495146</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.5247524752475248</v>
+        <v>0.5258215962441315</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2302576891105569</v>
+        <v>0.2319066147859922</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.3465703971119133</v>
+        <v>0.3590604026845637</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.400749063670412</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.3854166666666667</v>
+        <v>0.411214953271028</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.08395677472984206</v>
+        <v>0.0840466926070039</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.4257425742574257</v>
+        <v>0.3981481481481481</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.4343434343434344</v>
+        <v>0.4134615384615384</v>
       </c>
       <c r="GH14" t="n">
         <v>0.4186046511627907</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1271820448877805</v>
+        <v>0.1260700389105058</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3660130718954248</v>
+        <v>0.3765432098765432</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.3758389261744967</v>
+        <v>0.3860759493670886</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.9821428571428571</v>
+        <v>0.9836065573770492</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.2610141313383209</v>
+        <v>0.267704280155642</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.3057324840764331</v>
+        <v>0.313953488372093</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3106796116504854</v>
+        <v>0.3195266272189349</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.4482758620689655</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.6025641025641025</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.25</v>
+        <v>0.2553191489361702</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.119047619047619</v>
+        <v>0.1149425287356322</v>
       </c>
       <c r="GU14" t="n">
         <v>0.5</v>
@@ -10509,77 +10513,77 @@
         <v>0.9</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.282051282051282</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="GY14" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3375394321766562</v>
+        <v>0.3363095238095238</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5607476635514018</v>
+        <v>0.5663716814159292</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1009463722397476</v>
+        <v>0.1101190476190476</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.3125</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.2681388012618297</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3294117647058823</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.685785536159601</v>
+        <v>0.6840466926070039</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.3057324840764331</v>
+        <v>0.313953488372093</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5494381886477462</v>
+        <v>0.5480781078967943</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.543872131147541</v>
+        <v>0.5466540322580645</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5408682108626198</v>
+        <v>0.5421974320241693</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09823484267075978</v>
+        <v>0.09834888729361091</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1510791366906475</v>
+        <v>0.1504524886877828</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.004264392324093817</v>
+        <v>0.007858546168958742</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1656891495601173</v>
+        <v>0.1667787491593813</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2859237536656892</v>
+        <v>0.2885003362474781</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.533152173913043</v>
+        <v>6.627086007702182</v>
       </c>
       <c r="HQ14" t="n">
-        <v>24.95874730021598</v>
+        <v>25.00758483033932</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2878086419753086</v>
+        <v>0.2852011494252873</v>
       </c>
       <c r="HS14" t="n">
         <v>6</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.01592356687898089</v>
+        <v>0.01744186046511628</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -5054,307 +5054,307 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>46980</v>
+        <v>49860</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
-        <v>1538</v>
+        <v>1634</v>
       </c>
       <c r="K7" t="n">
-        <v>1543</v>
+        <v>1641</v>
       </c>
       <c r="L7" t="n">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="M7" t="n">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="N7" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="O7" t="n">
-        <v>3081</v>
+        <v>3275</v>
       </c>
       <c r="P7" t="n">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="Q7" t="n">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="T7" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="U7" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="V7" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="X7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Y7" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="Z7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA7" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="AB7" t="n">
         <v>8</v>
       </c>
       <c r="AC7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>142</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>389</v>
+      </c>
+      <c r="AH7" t="n">
         <v>20</v>
       </c>
-      <c r="AD7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>39</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>135</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>368</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19</v>
-      </c>
       <c r="AI7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>97</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>495</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>943</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>518</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>308</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1868</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1850</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>124</v>
+      </c>
+      <c r="AU7" t="n">
         <v>28</v>
       </c>
-      <c r="AK7" t="n">
-        <v>94</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>463</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>894</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>179</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>490</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>284</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1747</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1742</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>58</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>27</v>
-      </c>
       <c r="AV7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AW7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX7" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AY7" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="AZ7" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="BA7" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB7" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="BC7" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="BD7" t="n">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="BE7" t="n">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="BF7" t="n">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="BG7" t="n">
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="BH7" t="n">
         <v>66</v>
       </c>
       <c r="BI7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="BJ7" t="n">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="BK7" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="BL7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BM7" t="n">
         <v>4</v>
       </c>
       <c r="BN7" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="BO7" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="BP7" t="n">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="BQ7" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="BR7" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="BS7" t="n">
+        <v>174</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>66</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1022</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>92</v>
+      </c>
+      <c r="BX7" t="n">
         <v>161</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>64</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>957</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>90</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>154</v>
       </c>
       <c r="BY7" t="n">
         <v>10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="CA7" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="CB7" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="CC7" t="n">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="CD7" t="n">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="CE7" t="n">
-        <v>766</v>
+        <v>806</v>
       </c>
       <c r="CF7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CG7" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="CH7" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="CI7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="CJ7" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="CK7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="CL7" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="CM7" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="CN7" t="n">
         <v>15</v>
       </c>
       <c r="CO7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CP7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CQ7" t="n">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="CR7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CS7" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="CT7" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="CU7" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="CV7" t="n">
         <v>4</v>
       </c>
       <c r="CW7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CX7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CY7" t="n">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="CZ7" t="n">
         <v>3</v>
       </c>
       <c r="DA7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DB7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="DC7" t="n">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="DD7" t="n">
         <v>30</v>
@@ -5364,16 +5364,16 @@
         <v>5</v>
       </c>
       <c r="DG7" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="DH7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DI7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="DJ7" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="DK7" t="n">
         <v>8</v>
@@ -5382,7 +5382,7 @@
         <v>5</v>
       </c>
       <c r="DM7" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="DN7" t="n">
         <v>3</v>
@@ -5391,323 +5391,323 @@
         <v>4</v>
       </c>
       <c r="DP7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="DQ7" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="DR7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="DS7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DT7" t="n">
         <v>2</v>
       </c>
       <c r="DU7" t="n">
-        <v>1509</v>
+        <v>1620</v>
       </c>
       <c r="DV7" t="n">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="DW7" t="n">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="DX7" t="n">
         <v>55</v>
       </c>
       <c r="DY7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.5248380129589633</v>
+        <v>0.5232323232323233</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.5599078341013825</v>
+        <v>0.556989247311828</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.8770949720670391</v>
+        <v>0.8842105263157894</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.3653061224489796</v>
+        <v>0.3667953667953668</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.391304347826087</v>
+        <v>0.3943661971830986</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.3653061224489796</v>
+        <v>0.3667953667953668</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.5178970917225951</v>
+        <v>0.5249204665959704</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.5064377682403434</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.5285404624277457</v>
+        <v>0.5338809034907598</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.5211640211640212</v>
+        <v>0.5230769230769231</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.4945355191256831</v>
+        <v>0.5</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.5600513808606294</v>
+        <v>0.5661809350333941</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.5409090909090909</v>
+        <v>0.543859649122807</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.5440180586907449</v>
+        <v>0.550321199143469</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.3540462427745665</v>
+        <v>0.3545516769336071</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.00816326530612245</v>
+        <v>0.007722007722007722</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.09172259507829977</v>
+        <v>0.088016967126193</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.1126436781609195</v>
+        <v>0.1094091903719912</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.08732394366197183</v>
+        <v>0.08288770053475936</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.01923076923076923</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="EV7" t="inlineStr"/>
       <c r="EW7" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.5115384615384615</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.85</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.5825242718446602</v>
+        <v>0.5825545171339563</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.3632075471698113</v>
+        <v>0.3650793650793651</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.7095959595959596</v>
+        <v>0.7139479905437353</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.3</v>
+        <v>0.2902208201892745</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.6539007092198581</v>
+        <v>0.657258064516129</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.3370165745856354</v>
+        <v>0.3337730870712401</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.4213836477987422</v>
+        <v>0.4171779141104294</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.3509615384615384</v>
+        <v>0.3502304147465438</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2456140350877193</v>
+        <v>0.2786885245901639</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2767857142857143</v>
+        <v>0.2689075630252101</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3544303797468354</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.5229885057471264</v>
+        <v>0.5359116022099447</v>
       </c>
       <c r="FM7" t="n">
         <v>0.8</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.71</v>
+        <v>0.7111801242236024</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7227722772277227</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0453125</v>
+        <v>0.0475482912332838</v>
       </c>
       <c r="FQ7" t="n">
-        <v>94.43678160919541</v>
+        <v>94.58483754512635</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.4578313253012048</v>
+        <v>0.4482758620689655</v>
       </c>
       <c r="FS7" t="n">
-        <v>15.20559167750325</v>
+        <v>15.22417380660955</v>
       </c>
       <c r="FT7" t="n">
-        <v>15.29086195722618</v>
+        <v>15.22468007312614</v>
       </c>
       <c r="FU7" t="n">
-        <v>14.45884265279584</v>
+        <v>14.50042839657283</v>
       </c>
       <c r="FV7" t="n">
-        <v>14.49961114711601</v>
+        <v>14.44326630103595</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.3143063583815029</v>
+        <v>0.3127994524298426</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.632183908045977</v>
+        <v>0.6411378555798687</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.7124352331606217</v>
+        <v>0.7199017199017199</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.5854545454545454</v>
+        <v>0.5938566552901023</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.2565028901734104</v>
+        <v>0.2559890485968515</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.4056338028169014</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4489795918367347</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.07514450867052024</v>
+        <v>0.07665982203969883</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.4363636363636363</v>
       </c>
       <c r="GH7" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.08815028901734104</v>
+        <v>0.08829568788501027</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.360655737704918</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.360655737704918</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.9791666666666666</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.2658959537572254</v>
+        <v>0.2662559890485969</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3668478260869565</v>
+        <v>0.3650385604113111</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.3708791208791209</v>
+        <v>0.3688311688311688</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.852112676056338</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5125</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.275</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.1058201058201058</v>
+        <v>0.1076923076923077</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="GV7" t="n">
         <v>1</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3877551020408163</v>
+        <v>0.4</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.85</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.3579234972677596</v>
+        <v>0.3532467532467533</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.6259541984732825</v>
+        <v>0.6323529411764706</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.1065573770491803</v>
+        <v>0.1116883116883117</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.2568306010928962</v>
+        <v>0.2519480519480519</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.2978723404255319</v>
+        <v>0.2989690721649484</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.6683526011560693</v>
+        <v>0.6673511293634496</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.3668478260869565</v>
+        <v>0.3650385604113111</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.5506954314720812</v>
+        <v>0.5506533653846154</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.5389345864661653</v>
+        <v>0.5400384057971015</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.5558452908587257</v>
+        <v>0.5540984210526316</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.1039046988749173</v>
+        <v>0.1050656660412758</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.1496062992125984</v>
+        <v>0.1506976744186047</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.0101010101010101</v>
+        <v>0.01145038167938931</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.1362335432169433</v>
+        <v>0.132762312633833</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.2764739553520321</v>
+        <v>0.2756959314775161</v>
       </c>
       <c r="HP7" t="n">
-        <v>6.175391498881432</v>
+        <v>6.22237539766702</v>
       </c>
       <c r="HQ7" t="n">
-        <v>25.68374485596708</v>
+        <v>25.72003891050584</v>
       </c>
       <c r="HR7" t="n">
-        <v>0.2724317295188556</v>
+        <v>0.2723378212974296</v>
       </c>
       <c r="HS7" t="n">
         <v>6</v>
@@ -5716,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="HU7" t="n">
-        <v>0.0108695652173913</v>
+        <v>0.0102827763496144</v>
       </c>
     </row>
     <row r="8">
@@ -5751,199 +5751,199 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>34860</v>
+        <v>37740</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>-221</v>
+        <v>-234</v>
       </c>
       <c r="J8" t="n">
-        <v>1148</v>
+        <v>1245</v>
       </c>
       <c r="K8" t="n">
-        <v>1157</v>
+        <v>1254</v>
       </c>
       <c r="L8" t="n">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="M8" t="n">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="N8" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="O8" t="n">
-        <v>2305</v>
+        <v>2499</v>
       </c>
       <c r="P8" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="Q8" t="n">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="R8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="T8" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="U8" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="V8" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="W8" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="X8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y8" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Z8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AA8" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
         <v>7</v>
       </c>
       <c r="AE8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>97</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>350</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI8" t="n">
         <v>25</v>
       </c>
-      <c r="AF8" t="n">
-        <v>87</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>316</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>23</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="AL8" t="n">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="AM8" t="n">
-        <v>556</v>
+        <v>599</v>
       </c>
       <c r="AN8" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="AO8" t="n">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="AP8" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1207</v>
+        <v>1315</v>
       </c>
       <c r="AR8" t="n">
-        <v>1428</v>
+        <v>1549</v>
       </c>
       <c r="AS8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AW8" t="n">
         <v>29</v>
       </c>
       <c r="AX8" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="AY8" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AZ8" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="BA8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="BB8" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="BC8" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BD8" t="n">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="BE8" t="n">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="BF8" t="n">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="BG8" t="n">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="BH8" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="BI8" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="BJ8" t="n">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="BK8" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="BL8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BM8" t="n">
         <v>6</v>
       </c>
       <c r="BN8" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="BO8" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="BP8" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="BQ8" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="BR8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS8" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="BT8" t="n">
         <v>24</v>
@@ -5952,109 +5952,109 @@
         <v>14</v>
       </c>
       <c r="BV8" t="n">
-        <v>620</v>
+        <v>674</v>
       </c>
       <c r="BW8" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="BX8" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="BY8" t="n">
         <v>3</v>
       </c>
       <c r="BZ8" t="n">
+        <v>183</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>165</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>36</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>384</v>
+      </c>
+      <c r="CD8" t="n">
         <v>168</v>
       </c>
-      <c r="CA8" t="n">
-        <v>155</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>34</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>357</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>157</v>
-      </c>
       <c r="CE8" t="n">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="CF8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CG8" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="CH8" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="CI8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CJ8" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="CK8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CL8" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="CM8" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="CN8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CO8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CP8" t="n">
         <v>5</v>
       </c>
       <c r="CQ8" t="n">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="CR8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CS8" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="CT8" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="CU8" t="n">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="CV8" t="n">
         <v>3</v>
       </c>
       <c r="CW8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CX8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CY8" t="n">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="CZ8" t="n">
         <v>3</v>
       </c>
       <c r="DA8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DB8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DC8" t="n">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="DD8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="DE8" t="n">
         <v>2</v>
@@ -6063,7 +6063,7 @@
         <v>5</v>
       </c>
       <c r="DG8" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="DH8" t="n">
         <v>5</v>
@@ -6072,7 +6072,7 @@
         <v>37</v>
       </c>
       <c r="DJ8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="DK8" t="n">
         <v>4</v>
@@ -6081,7 +6081,7 @@
         <v>3</v>
       </c>
       <c r="DM8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
@@ -6093,10 +6093,10 @@
         <v>15</v>
       </c>
       <c r="DQ8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="DR8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DS8" t="n">
         <v>1</v>
@@ -6105,317 +6105,317 @@
         <v>2</v>
       </c>
       <c r="DU8" t="n">
-        <v>1056</v>
+        <v>1150</v>
       </c>
       <c r="DV8" t="n">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="DW8" t="n">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="DX8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="DY8" t="n">
         <v>33</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.4711864406779661</v>
+        <v>0.4646153846153846</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.5265151515151515</v>
+        <v>0.5189003436426117</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.8507462686567164</v>
+        <v>0.8493150684931506</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.3052391799544419</v>
+        <v>0.3041666666666666</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2765957446808511</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.3052391799544419</v>
+        <v>0.3041666666666666</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.5305755395683454</v>
+        <v>0.5425709515859767</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.5822784810126582</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.4842767295597484</v>
+        <v>0.5029585798816568</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.4984924623115578</v>
+        <v>0.5041705282669138</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.5545454545454546</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.4596491228070175</v>
+        <v>0.4629032258064516</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.533717834960071</v>
+        <v>0.5377358490566038</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.5725190839694656</v>
+        <v>0.5857142857142857</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.5057971014492754</v>
+        <v>0.5067024128686327</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.4412060301507538</v>
+        <v>0.4448563484708063</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.01366742596810934</v>
+        <v>0.0125</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.08273381294964029</v>
+        <v>0.08347245409015025</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.07773851590106007</v>
+        <v>0.08116883116883117</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1037735849056604</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.0379746835443038</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01626016260162602</v>
+        <v>0.01538461538461539</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5751295336787565</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.075</v>
+        <v>0.06976744186046512</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.6175298804780877</v>
+        <v>0.6156716417910447</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.3038461538461538</v>
+        <v>0.3088235294117647</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.717948717948718</v>
+        <v>0.7290836653386454</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.25</v>
+        <v>0.2477064220183486</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.6659793814432989</v>
+        <v>0.6705202312138728</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.275</v>
+        <v>0.2754590984974958</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.3789473684210526</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2615384615384616</v>
       </c>
       <c r="FH8" t="n">
         <v>0.2978723404255319</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.2357723577235772</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.3026315789473684</v>
+        <v>0.2839506172839506</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.5702479338842975</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.65</v>
+        <v>0.6513761467889908</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.7470588235294118</v>
+        <v>0.7554347826086957</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.640625</v>
+        <v>0.6567164179104478</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0275049115913556</v>
+        <v>0.02757352941176471</v>
       </c>
       <c r="FQ8" t="n">
-        <v>95.21514629948365</v>
+        <v>95.35135135135135</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.6415094339622641</v>
+        <v>0.6481481481481481</v>
       </c>
       <c r="FS8" t="n">
-        <v>14.45095818815331</v>
+        <v>14.44144578313253</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.79109766637857</v>
+        <v>15.75789473684211</v>
       </c>
       <c r="FU8" t="n">
-        <v>13.88745644599303</v>
+        <v>13.87253012048193</v>
       </c>
       <c r="FV8" t="n">
-        <v>15.0961970613656</v>
+        <v>15.08955342902711</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.2844221105527638</v>
+        <v>0.2854494902687674</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.6819787985865724</v>
+        <v>0.6915584415584416</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.7394636015325671</v>
+        <v>0.7526501766784452</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.5233160621761658</v>
+        <v>0.5305164319248826</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1969849246231156</v>
+        <v>0.1964782205746061</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.3673469387755102</v>
+        <v>0.3773584905660378</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.4114285714285714</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.07738693467336684</v>
+        <v>0.0732159406858202</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.3896103896103896</v>
+        <v>0.4050632911392405</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.4054054054054054</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.1236180904522613</v>
+        <v>0.1204819277108434</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.3821138211382114</v>
+        <v>0.3769230769230769</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.3884297520661157</v>
+        <v>0.3828125</v>
       </c>
       <c r="GL8" t="n">
-        <v>0.9361702127659575</v>
+        <v>0.9387755102040817</v>
       </c>
       <c r="GM8" t="n">
-        <v>0.3175879396984925</v>
+        <v>0.3243744207599629</v>
       </c>
       <c r="GN8" t="n">
-        <v>0.2753164556962026</v>
+        <v>0.2771428571428571</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.2788461538461539</v>
+        <v>0.2803468208092486</v>
       </c>
       <c r="GP8" t="n">
-        <v>0.8045977011494253</v>
+        <v>0.8041237113402062</v>
       </c>
       <c r="GQ8" t="n">
-        <v>0.4636363636363636</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="GR8" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="GS8" t="n">
-        <v>0.1944444444444444</v>
+        <v>0.2</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.08403361344537816</v>
       </c>
       <c r="GU8" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="GV8" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="GW8" t="n">
-        <v>0.2090909090909091</v>
+        <v>0.2100840336134454</v>
       </c>
       <c r="GX8" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.36</v>
       </c>
       <c r="GY8" t="n">
-        <v>0.875</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="GZ8" t="n">
-        <v>0.2736842105263158</v>
+        <v>0.2741935483870968</v>
       </c>
       <c r="HA8" t="n">
-        <v>0.6025641025641025</v>
+        <v>0.6352941176470588</v>
       </c>
       <c r="HB8" t="n">
-        <v>0.08771929824561403</v>
+        <v>0.08709677419354839</v>
       </c>
       <c r="HC8" t="n">
-        <v>0.28</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.3543859649122807</v>
+        <v>0.367741935483871</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2871287128712871</v>
+        <v>0.2807017543859649</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.7256281407035176</v>
+        <v>0.7303058387395737</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.2753164556962026</v>
+        <v>0.2771428571428571</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.5507415991902834</v>
+        <v>0.5531684701492536</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.5367835714285714</v>
+        <v>0.54084</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.5313059139784947</v>
+        <v>0.5353184210526315</v>
       </c>
       <c r="HK8" t="n">
-        <v>0.1091743119266055</v>
+        <v>0.1091370558375634</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.1759259259259259</v>
+        <v>0.1773962804005723</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.01131221719457014</v>
+        <v>0.010351966873706</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.1251035625517813</v>
+        <v>0.1254752851711027</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.2916321458160729</v>
+        <v>0.2897338403041825</v>
       </c>
       <c r="HP8" t="n">
-        <v>6.237230215827338</v>
+        <v>6.152086811352254</v>
       </c>
       <c r="HQ8" t="n">
-        <v>25.32396313364055</v>
+        <v>25.32736842105263</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.2909407665505226</v>
+        <v>0.2931726907630522</v>
       </c>
       <c r="HS8" t="n">
         <v>3</v>
       </c>
       <c r="HT8" t="inlineStr"/>
       <c r="HU8" t="n">
-        <v>0.01265822784810127</v>
+        <v>0.01142857142857143</v>
       </c>
     </row>
     <row r="9">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -7133,67 +7133,67 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>32280</v>
+        <v>35160</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>-150</v>
+        <v>-129</v>
       </c>
       <c r="J10" t="n">
-        <v>1064</v>
+        <v>1164</v>
       </c>
       <c r="K10" t="n">
-        <v>1069</v>
+        <v>1169</v>
       </c>
       <c r="L10" t="n">
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="M10" t="n">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="N10" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="O10" t="n">
-        <v>2133</v>
+        <v>2333</v>
       </c>
       <c r="P10" t="n">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="Q10" t="n">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="R10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S10" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="T10" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="V10" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="W10" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="X10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y10" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA10" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
@@ -7202,241 +7202,241 @@
         <v>16</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="AF10" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="AG10" t="n">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="AH10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>76</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>308</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>590</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>147</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>426</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>226</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1283</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1412</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>92</v>
+      </c>
+      <c r="AU10" t="n">
         <v>20</v>
       </c>
-      <c r="AK10" t="n">
-        <v>64</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>282</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>533</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>138</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>392</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>202</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1180</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1330</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>45</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>18</v>
-      </c>
       <c r="AV10" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AW10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="AY10" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="AZ10" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="BA10" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="BB10" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="BC10" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BD10" t="n">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="BE10" t="n">
+        <v>324</v>
+      </c>
+      <c r="BF10" t="n">
         <v>292</v>
       </c>
-      <c r="BF10" t="n">
-        <v>272</v>
-      </c>
       <c r="BG10" t="n">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="BH10" t="n">
         <v>72</v>
       </c>
       <c r="BI10" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BJ10" t="n">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="BK10" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="BL10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="BO10" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="BP10" t="n">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="BQ10" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="BR10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS10" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="BT10" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
         <v>13</v>
       </c>
       <c r="BV10" t="n">
-        <v>634</v>
+        <v>693</v>
       </c>
       <c r="BW10" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="BX10" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="BY10" t="n">
         <v>3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="CA10" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="CB10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CC10" t="n">
-        <v>351</v>
+        <v>393</v>
       </c>
       <c r="CD10" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="CE10" t="n">
-        <v>515</v>
+        <v>575</v>
       </c>
       <c r="CF10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="CG10" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="CH10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="CI10" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="CJ10" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="CK10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CL10" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="CM10" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="CN10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CO10" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="CP10" t="n">
         <v>4</v>
       </c>
       <c r="CQ10" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="CR10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="CS10" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="CT10" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="CU10" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="CV10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CW10" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="CX10" t="n">
         <v>21</v>
       </c>
       <c r="CY10" t="n">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="CZ10" t="n">
         <v>1</v>
       </c>
       <c r="DA10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="DB10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DC10" t="n">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="DD10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="DE10" t="n">
         <v>4</v>
@@ -7445,16 +7445,16 @@
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="DH10" t="n">
         <v>7</v>
       </c>
       <c r="DI10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="DJ10" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="DK10" t="n">
         <v>6</v>
@@ -7463,22 +7463,22 @@
         <v>5</v>
       </c>
       <c r="DM10" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="DQ10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DR10" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="DS10" t="n">
         <v>3</v>
@@ -7487,236 +7487,236 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1012</v>
+        <v>1098</v>
       </c>
       <c r="DV10" t="n">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="DW10" t="n">
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="DX10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="DY10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.5177304964539007</v>
+        <v>0.525974025974026</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5770750988142292</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3520408163265306</v>
+        <v>0.3450704225352113</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.375</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3146067415730337</v>
+        <v>0.3027522935779817</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3520408163265306</v>
+        <v>0.3450704225352113</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5290806754221389</v>
+        <v>0.5220338983050847</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.5378787878787878</v>
+        <v>0.5</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5286486486486487</v>
+        <v>0.5201771653543307</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5413533834586466</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.5113122171945701</v>
+        <v>0.4816849816849817</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5718446601941748</v>
+        <v>0.5638204225352113</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5854430379746836</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5802238805970149</v>
+        <v>0.5474006116207951</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4237837837837838</v>
+        <v>0.4192913385826771</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.002551020408163265</v>
+        <v>0.002347417840375587</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.09380863039399624</v>
+        <v>0.09322033898305085</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1400778210116732</v>
+        <v>0.134020618556701</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.0625</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.03296703296703297</v>
       </c>
       <c r="EV10" t="inlineStr"/>
       <c r="EW10" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5971563981042654</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6962025316455697</v>
+        <v>0.6851851851851852</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.344</v>
+        <v>0.3487544483985765</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.6881720430107527</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.3012048192771085</v>
+        <v>0.2967032967032967</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6871165644171779</v>
+        <v>0.6867030965391621</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3226452905811623</v>
+        <v>0.3231046931407942</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4536082474226804</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2929292929292929</v>
+        <v>0.2844036697247707</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.25</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.3146067415730337</v>
+        <v>0.310880829015544</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2676056338028169</v>
+        <v>0.2625</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.6</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.8360655737704918</v>
+        <v>0.7887323943661971</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.625</v>
+        <v>0.6323529411764706</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.84</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.066</v>
       </c>
       <c r="FQ10" t="n">
-        <v>95.15241635687732</v>
+        <v>95.54948805460751</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="FS10" t="n">
-        <v>15.48242481203008</v>
+        <v>15.2770618556701</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.78643592142189</v>
+        <v>14.86526946107784</v>
       </c>
       <c r="FU10" t="n">
-        <v>14.84389097744361</v>
+        <v>14.63496563573883</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.17034611786717</v>
+        <v>14.21377245508982</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.2778378378378378</v>
+        <v>0.2864173228346457</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6186770428015564</v>
+        <v>0.6116838487972509</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.7194570135746606</v>
+        <v>0.7063492063492064</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5408805031446541</v>
+        <v>0.5561797752808989</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.2075675675675676</v>
+        <v>0.2047244094488189</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.484375</v>
+        <v>0.4759615384615384</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.5138121546961326</v>
+        <v>0.5076923076923077</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.5053763440860215</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.09081081081081081</v>
+        <v>0.08956692913385826</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3406593406593407</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.3522727272727273</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1221621621621622</v>
+        <v>0.1220472440944882</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3716814159292036</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3716814159292036</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="GL10" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.3016216216216216</v>
+        <v>0.297244094488189</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3440860215053764</v>
+        <v>0.3410596026490066</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3453237410071943</v>
+        <v>0.3421926910299004</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7864077669902912</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.4586466165413534</v>
+        <v>0.4652777777777778</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5409836065573771</v>
+        <v>0.5373134328358209</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.1203007518796992</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="GU10" t="n">
         <v>0.375</v>
@@ -7725,77 +7725,77 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2406015037593985</v>
+        <v>0.25</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.375</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.75</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.2895927601809955</v>
+        <v>0.3003663003663004</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.65625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1131221719457014</v>
+        <v>0.1208791208791209</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.32</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2895927601809955</v>
+        <v>0.2783882783882784</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3125</v>
+        <v>0.3026315789473684</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7016216216216217</v>
+        <v>0.7057086614173228</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3440860215053764</v>
+        <v>0.3410596026490066</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5348122559652928</v>
+        <v>0.5392689416419387</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5259648809523809</v>
+        <v>0.5282701086956522</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5191871559633028</v>
+        <v>0.5299041044776119</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1074626865671642</v>
+        <v>0.1076923076923077</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1655737704918033</v>
+        <v>0.1656804733727811</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.01772151898734177</v>
+        <v>0.01631701631701632</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1423728813559322</v>
+        <v>0.1441932969602494</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.2635593220338983</v>
+        <v>0.2790335151987529</v>
       </c>
       <c r="HP10" t="n">
-        <v>6.654033771106942</v>
+        <v>6.540847457627119</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.72046035805627</v>
+        <v>25.68702830188679</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.2612781954887218</v>
+        <v>0.2852233676975945</v>
       </c>
       <c r="HS10" t="n">
         <v>3</v>
       </c>
       <c r="HT10" t="inlineStr"/>
       <c r="HU10" t="n">
-        <v>0.003584229390681004</v>
+        <v>0.003311258278145695</v>
       </c>
     </row>
     <row r="11">
@@ -9921,67 +9921,67 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>40920</v>
+        <v>43800</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" t="n">
-        <v>-142</v>
+        <v>-163</v>
       </c>
       <c r="J14" t="n">
-        <v>1392</v>
+        <v>1491</v>
       </c>
       <c r="K14" t="n">
-        <v>1404</v>
+        <v>1505</v>
       </c>
       <c r="L14" t="n">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="M14" t="n">
-        <v>491</v>
+        <v>546</v>
       </c>
       <c r="N14" t="n">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="O14" t="n">
-        <v>2796</v>
+        <v>2996</v>
       </c>
       <c r="P14" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="Q14" t="n">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="R14" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="S14" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="T14" t="n">
+        <v>69</v>
+      </c>
+      <c r="U14" t="n">
+        <v>121</v>
+      </c>
+      <c r="V14" t="n">
+        <v>111</v>
+      </c>
+      <c r="W14" t="n">
+        <v>312</v>
+      </c>
+      <c r="X14" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>124</v>
+      </c>
+      <c r="Z14" t="n">
         <v>64</v>
       </c>
-      <c r="U14" t="n">
-        <v>113</v>
-      </c>
-      <c r="V14" t="n">
-        <v>107</v>
-      </c>
-      <c r="W14" t="n">
-        <v>298</v>
-      </c>
-      <c r="X14" t="n">
-        <v>43</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>108</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>61</v>
-      </c>
       <c r="AA14" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AB14" t="n">
         <v>10</v>
@@ -9990,239 +9990,239 @@
         <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AF14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG14" t="n">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="AH14" t="n">
         <v>14</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AK14" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="AL14" t="n">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="AM14" t="n">
-        <v>779</v>
+        <v>837</v>
       </c>
       <c r="AN14" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AO14" t="n">
-        <v>506</v>
+        <v>539</v>
       </c>
       <c r="AP14" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1487</v>
+        <v>1569</v>
       </c>
       <c r="AR14" t="n">
-        <v>1629</v>
+        <v>1732</v>
       </c>
       <c r="AS14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT14" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="AU14" t="n">
         <v>24</v>
       </c>
       <c r="AV14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AW14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>262</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>101</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>220</v>
+      </c>
+      <c r="BA14" t="n">
         <v>46</v>
       </c>
-      <c r="AX14" t="n">
-        <v>248</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>207</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>43</v>
-      </c>
       <c r="BB14" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="BC14" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="BD14" t="n">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="BE14" t="n">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="BF14" t="n">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="BG14" t="n">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="BH14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="BI14" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="BJ14" t="n">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="BK14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BL14" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="BM14" t="n">
         <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="BO14" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="BP14" t="n">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="BQ14" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="BR14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="BS14" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="BT14" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BU14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BV14" t="n">
-        <v>780</v>
+        <v>829</v>
       </c>
       <c r="BW14" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="BX14" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="CA14" t="n">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="CB14" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="CC14" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="CD14" t="n">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="CE14" t="n">
-        <v>689</v>
+        <v>748</v>
       </c>
       <c r="CF14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CG14" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="CH14" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="CI14" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="CJ14" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="CK14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CL14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="CM14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="CN14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CO14" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="CR14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CS14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="CT14" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="CU14" t="n">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CX14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CY14" t="n">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="CZ14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DA14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="DB14" t="n">
         <v>30</v>
       </c>
       <c r="DC14" t="n">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="DD14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DE14" t="n">
         <v>1</v>
@@ -10231,16 +10231,16 @@
         <v>4</v>
       </c>
       <c r="DG14" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="DH14" t="n">
         <v>4</v>
       </c>
       <c r="DI14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="DJ14" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="DK14" t="n">
         <v>4</v>
@@ -10249,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="DM14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10258,13 +10258,13 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="DQ14" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="DR14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="DS14" t="n">
         <v>1</v>
@@ -10273,238 +10273,238 @@
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1239</v>
+        <v>1307</v>
       </c>
       <c r="DV14" t="n">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="DW14" t="n">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="DX14" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="DY14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4793388429752066</v>
+        <v>0.4935400516795866</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5370370370370371</v>
+        <v>0.5536231884057971</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8520710059171598</v>
+        <v>0.8514285714285714</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3339920948616601</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3285714285714286</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.3339920948616601</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4659820282413351</v>
+        <v>0.4623655913978494</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.5803571428571429</v>
+        <v>0.5785123966942148</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4589371980676328</v>
+        <v>0.4590909090909091</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.4797665369649806</v>
+        <v>0.4720203488372093</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.5804597701149425</v>
+        <v>0.5668449197860963</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.4747023809523809</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5181437543614794</v>
+        <v>0.5114229765013055</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.6138613861386139</v>
+        <v>0.6036866359447005</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5270935960591133</v>
+        <v>0.5254041570438799</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3937743190661478</v>
+        <v>0.3917151162790697</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01976284584980237</v>
+        <v>0.01855287569573284</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1270860077021823</v>
+        <v>0.1302270011947431</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1715817694369973</v>
+        <v>0.1770573566084788</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.1040268456375839</v>
+        <v>0.1057692307692308</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.04032258064516129</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.02469135802469136</v>
+        <v>0.02325581395348837</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6270270270270271</v>
+        <v>0.6195121951219512</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.9117647058823529</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.131578947368421</v>
+        <v>0.1282051282051282</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6728971962616822</v>
+        <v>0.6676136363636364</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3309002433090024</v>
+        <v>0.3355855855855856</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7190635451505016</v>
+        <v>0.7213622291021672</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2613981762917933</v>
+        <v>0.2584269662921349</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6951612903225807</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.3</v>
+        <v>0.30125</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3962264150943396</v>
+        <v>0.3895348837209303</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3227513227513227</v>
+        <v>0.3266331658291458</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2826086956521739</v>
+        <v>0.284</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.1981132075471698</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.6124031007751938</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.6870229007633588</v>
+        <v>0.6950354609929078</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.7704918032786885</v>
+        <v>0.7611940298507462</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7093596059113301</v>
+        <v>0.7110091743119266</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7395833333333334</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03475513428120063</v>
+        <v>0.03508771929824561</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.39296187683284</v>
+        <v>98.49863013698631</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.7413793103448276</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="FS14" t="n">
-        <v>14.89762931034483</v>
+        <v>14.96197183098591</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.375</v>
+        <v>14.28019933554817</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.15431034482759</v>
+        <v>14.19892689470154</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.80491452991453</v>
+        <v>13.70318936877076</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2902723735408561</v>
+        <v>0.2914244186046512</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5710455764075067</v>
+        <v>0.5660847880299252</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6893203883495146</v>
+        <v>0.6878787878787879</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.5258215962441315</v>
+        <v>0.5330396475770925</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2319066147859922</v>
+        <v>0.2267441860465116</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.3590604026845637</v>
+        <v>0.3557692307692308</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.400749063670412</v>
+        <v>0.3978494623655914</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.411214953271028</v>
+        <v>0.4324324324324325</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0840466926070039</v>
+        <v>0.09011627906976744</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.3981481481481481</v>
+        <v>0.3951612903225806</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.4134615384615384</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.4489795918367347</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1260700389105058</v>
+        <v>0.125</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3765432098765432</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.3860759493670886</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.9836065573770492</v>
+        <v>0.96875</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.267704280155642</v>
+        <v>0.2667151162790697</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.313953488372093</v>
+        <v>0.3024523160762943</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3195266272189349</v>
+        <v>0.3074792243767313</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4482758620689655</v>
+        <v>0.4598930481283423</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.6025641025641025</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.2553191489361702</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.1149425287356322</v>
+        <v>0.106951871657754</v>
       </c>
       <c r="GU14" t="n">
         <v>0.5</v>
@@ -10513,77 +10513,77 @@
         <v>0.9</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.2459893048128342</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="GY14" t="n">
         <v>0.7857142857142857</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3363095238095238</v>
+        <v>0.3361111111111111</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5663716814159292</v>
+        <v>0.5702479338842975</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1101190476190476</v>
+        <v>0.1138888888888889</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.275</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3260869565217391</v>
+        <v>0.3131313131313131</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6840466926070039</v>
+        <v>0.6831395348837209</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.313953488372093</v>
+        <v>0.3024523160762943</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5480781078967943</v>
+        <v>0.5483911678832116</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5466540322580645</v>
+        <v>0.5533604477611941</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5421974320241693</v>
+        <v>0.5442357746478873</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09834888729361091</v>
+        <v>0.09664429530201342</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1504524886877828</v>
+        <v>0.1476793248945148</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.007858546168958742</v>
+        <v>0.007380073800738007</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1667787491593813</v>
+        <v>0.1669853409815169</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2885003362474781</v>
+        <v>0.2906309751434035</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.627086007702182</v>
+        <v>6.688649940262843</v>
       </c>
       <c r="HQ14" t="n">
-        <v>25.00758483033932</v>
+        <v>24.99812734082397</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2852011494252873</v>
+        <v>0.2837022132796781</v>
       </c>
       <c r="HS14" t="n">
         <v>6</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.01744186046511628</v>
+        <v>0.01634877384196185</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -5054,283 +5054,283 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>49860</v>
+        <v>52740</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>1634</v>
+        <v>1734</v>
       </c>
       <c r="K7" t="n">
-        <v>1641</v>
+        <v>1743</v>
       </c>
       <c r="L7" t="n">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="M7" t="n">
-        <v>550</v>
+        <v>592</v>
       </c>
       <c r="N7" t="n">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="O7" t="n">
-        <v>3275</v>
+        <v>3477</v>
       </c>
       <c r="P7" t="n">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="Q7" t="n">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="R7" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U7" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="V7" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="W7" t="n">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="X7" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="Y7" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="Z7" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="AB7" t="n">
         <v>8</v>
       </c>
       <c r="AC7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD7" t="n">
         <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AF7" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="AG7" t="n">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AJ7" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="AK7" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AL7" t="n">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="AM7" t="n">
-        <v>943</v>
+        <v>998</v>
       </c>
       <c r="AN7" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="AO7" t="n">
-        <v>518</v>
+        <v>562</v>
       </c>
       <c r="AP7" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1868</v>
+        <v>1998</v>
       </c>
       <c r="AR7" t="n">
-        <v>1850</v>
+        <v>1943</v>
       </c>
       <c r="AS7" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AT7" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AU7" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AV7" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AW7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX7" t="n">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="AY7" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AZ7" t="n">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="BA7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="BB7" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="BC7" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="BD7" t="n">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="BE7" t="n">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="BF7" t="n">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="BG7" t="n">
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="BH7" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="BI7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BJ7" t="n">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="BK7" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="BL7" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="BM7" t="n">
         <v>4</v>
       </c>
       <c r="BN7" t="n">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BO7" t="n">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="BP7" t="n">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="BQ7" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="BR7" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="BS7" t="n">
+        <v>188</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>69</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1103</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>102</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>173</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>324</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>202</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>57</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>583</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>286</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>869</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>34</v>
+      </c>
+      <c r="CG7" t="n">
         <v>174</v>
       </c>
-      <c r="BT7" t="n">
-        <v>66</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1022</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>92</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>161</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>302</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>187</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>54</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>543</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>263</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>806</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>32</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>159</v>
-      </c>
       <c r="CH7" t="n">
+        <v>106</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>68</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>142</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>33</v>
+      </c>
+      <c r="CL7" t="n">
         <v>97</v>
       </c>
-      <c r="CI7" t="n">
-        <v>62</v>
-      </c>
-      <c r="CJ7" t="n">
+      <c r="CM7" t="n">
         <v>133</v>
       </c>
-      <c r="CK7" t="n">
-        <v>32</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>89</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>127</v>
-      </c>
       <c r="CN7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CO7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CP7" t="n">
         <v>10</v>
       </c>
       <c r="CQ7" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="CR7" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="CS7" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="CT7" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="CU7" t="n">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="CV7" t="n">
         <v>4</v>
@@ -5342,19 +5342,19 @@
         <v>30</v>
       </c>
       <c r="CY7" t="n">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="CZ7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DA7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DB7" t="n">
         <v>23</v>
       </c>
       <c r="DC7" t="n">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="DD7" t="n">
         <v>30</v>
@@ -5364,16 +5364,16 @@
         <v>5</v>
       </c>
       <c r="DG7" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="DH7" t="n">
         <v>6</v>
       </c>
       <c r="DI7" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="DJ7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="DK7" t="n">
         <v>8</v>
@@ -5382,7 +5382,7 @@
         <v>5</v>
       </c>
       <c r="DM7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="DN7" t="n">
         <v>3</v>
@@ -5394,10 +5394,10 @@
         <v>41</v>
       </c>
       <c r="DQ7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="DR7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="DS7" t="n">
         <v>4</v>
@@ -5406,308 +5406,308 @@
         <v>2</v>
       </c>
       <c r="DU7" t="n">
-        <v>1620</v>
+        <v>1718</v>
       </c>
       <c r="DV7" t="n">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="DW7" t="n">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="DX7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="DY7" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.5232323232323233</v>
+        <v>0.5286259541984732</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.556989247311828</v>
+        <v>0.5664621676891616</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.8842105263157894</v>
+        <v>0.8755980861244019</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.3667953667953668</v>
+        <v>0.3718861209964413</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.3943661971830986</v>
+        <v>0.4303797468354431</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.3202614379084967</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.3667953667953668</v>
+        <v>0.3718861209964413</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.5249204665959704</v>
+        <v>0.5250501002004008</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.5102040816326531</v>
+        <v>0.5019455252918288</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.5338809034907598</v>
+        <v>0.5368589743589743</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.5230769230769231</v>
+        <v>0.5467289719626168</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.5</v>
+        <v>0.4939024390243902</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.5661809350333941</v>
+        <v>0.5680523917995444</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.543859649122807</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.550321199143469</v>
+        <v>0.5433467741935484</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.3545516769336071</v>
+        <v>0.3602564102564103</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.007722007722007722</v>
+        <v>0.007117437722419928</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.088016967126193</v>
+        <v>0.08717434869739479</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.1094091903719912</v>
+        <v>0.1086065573770492</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.08288770053475936</v>
+        <v>0.08163265306122448</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.01694915254237288</v>
       </c>
       <c r="EV7" t="inlineStr"/>
       <c r="EW7" t="n">
-        <v>0.5115384615384615</v>
+        <v>0.5163636363636364</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.22</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.5825545171339563</v>
+        <v>0.599406528189911</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.3704496788008566</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.7139479905437353</v>
+        <v>0.7184035476718403</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.2902208201892745</v>
+        <v>0.2991202346041056</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.657258064516129</v>
+        <v>0.6675126903553299</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.3337730870712401</v>
+        <v>0.3403465346534654</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.4171779141104294</v>
+        <v>0.4277456647398844</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.3502304147465438</v>
+        <v>0.3506493506493507</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2786885245901639</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2689075630252101</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.3544303797468354</v>
+        <v>0.3707865168539326</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.6</v>
+        <v>0.6186440677966102</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.5359116022099447</v>
+        <v>0.5531914893617021</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.8</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.7111801242236024</v>
+        <v>0.7130434782608696</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.7227722772277227</v>
+        <v>0.7358490566037735</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0475482912332838</v>
+        <v>0.04728789986091794</v>
       </c>
       <c r="FQ7" t="n">
-        <v>94.58483754512635</v>
+        <v>94.93515358361775</v>
       </c>
       <c r="FR7" t="n">
+        <v>0.4606741573033708</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>15.20121107266436</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>15.13545611015491</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>14.47226066897347</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>14.38313253012048</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0.3128205128205128</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0.6434426229508197</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.7218390804597701</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.5987261146496815</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.2512820512820513</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0.4030612244897959</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.4388888888888889</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.4367088607594937</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0.07564102564102564</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0.4406779661016949</v>
+      </c>
+      <c r="GG7" t="n">
         <v>0.4482758620689655</v>
       </c>
-      <c r="FS7" t="n">
-        <v>15.22417380660955</v>
-      </c>
-      <c r="FT7" t="n">
-        <v>15.22468007312614</v>
-      </c>
-      <c r="FU7" t="n">
-        <v>14.50042839657283</v>
-      </c>
-      <c r="FV7" t="n">
-        <v>14.44326630103595</v>
-      </c>
-      <c r="FW7" t="n">
-        <v>0.3127994524298426</v>
-      </c>
-      <c r="FX7" t="n">
-        <v>0.6411378555798687</v>
-      </c>
-      <c r="FY7" t="n">
-        <v>0.7199017199017199</v>
-      </c>
-      <c r="FZ7" t="n">
-        <v>0.5938566552901023</v>
-      </c>
-      <c r="GA7" t="n">
-        <v>0.2559890485968515</v>
-      </c>
-      <c r="GB7" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="GC7" t="n">
-        <v>0.4489795918367347</v>
-      </c>
-      <c r="GD7" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="GE7" t="n">
-        <v>0.07665982203969883</v>
-      </c>
-      <c r="GF7" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="GG7" t="n">
-        <v>0.4363636363636363</v>
-      </c>
       <c r="GH7" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.08829568788501027</v>
+        <v>0.09358974358974359</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.3720930232558139</v>
+        <v>0.3767123287671233</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.3720930232558139</v>
+        <v>0.3767123287671233</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.9818181818181818</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.2662559890485969</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3650385604113111</v>
+        <v>0.3701923076923077</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.3688311688311688</v>
+        <v>0.3737864077669903</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.852112676056338</v>
+        <v>0.8376623376623377</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4205607476635514</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.5125</v>
+        <v>0.5222222222222223</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2553191489361702</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.1076923076923077</v>
+        <v>0.102803738317757</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="GV7" t="n">
         <v>1</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.2663551401869159</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.4</v>
+        <v>0.456140350877193</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.85</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.3532467532467533</v>
+        <v>0.3365853658536586</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.6323529411764706</v>
+        <v>0.6304347826086957</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.1116883116883117</v>
+        <v>0.1146341463414634</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.3720930232558139</v>
+        <v>0.3404255319148936</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.2519480519480519</v>
+        <v>0.2585365853658537</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.2989690721649484</v>
+        <v>0.3113207547169811</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.6673511293634496</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.3650385604113111</v>
+        <v>0.3701923076923077</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.5506533653846154</v>
+        <v>0.553077380952381</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.5400384057971015</v>
+        <v>0.5456566225165562</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.5540984210526316</v>
+        <v>0.5509719059405941</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.1050656660412758</v>
+        <v>0.1026392961876833</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.1506976744186047</v>
+        <v>0.148636763412489</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.01145038167938931</v>
+        <v>0.01056338028169014</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.132762312633833</v>
+        <v>0.1401401401401401</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.2756959314775161</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="HP7" t="n">
-        <v>6.22237539766702</v>
+        <v>6.19128256513026</v>
       </c>
       <c r="HQ7" t="n">
-        <v>25.72003891050584</v>
+        <v>25.67450628366248</v>
       </c>
       <c r="HR7" t="n">
-        <v>0.2723378212974296</v>
+        <v>0.2722029988465975</v>
       </c>
       <c r="HS7" t="n">
         <v>6</v>
@@ -5716,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="HU7" t="n">
-        <v>0.0102827763496144</v>
+        <v>0.009615384615384616</v>
       </c>
     </row>
     <row r="8">
@@ -5751,67 +5751,67 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>37740</v>
+        <v>40620</v>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>-234</v>
+        <v>-271</v>
       </c>
       <c r="J8" t="n">
-        <v>1245</v>
+        <v>1346</v>
       </c>
       <c r="K8" t="n">
-        <v>1254</v>
+        <v>1355</v>
       </c>
       <c r="L8" t="n">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="M8" t="n">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="N8" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="O8" t="n">
-        <v>2499</v>
+        <v>2701</v>
       </c>
       <c r="P8" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="Q8" t="n">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="R8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S8" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T8" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="U8" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="V8" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="W8" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="X8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Y8" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Z8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="AB8" t="n">
         <v>3</v>
@@ -5820,226 +5820,226 @@
         <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>107</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>384</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI8" t="n">
         <v>27</v>
       </c>
-      <c r="AF8" t="n">
-        <v>97</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>350</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>25</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AL8" t="n">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="AM8" t="n">
-        <v>599</v>
+        <v>636</v>
       </c>
       <c r="AN8" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="AO8" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="AP8" t="n">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1315</v>
+        <v>1408</v>
       </c>
       <c r="AR8" t="n">
-        <v>1549</v>
+        <v>1679</v>
       </c>
       <c r="AS8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AT8" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AU8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AW8" t="n">
         <v>29</v>
       </c>
       <c r="AX8" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AY8" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AZ8" t="n">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="BA8" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="BB8" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="BC8" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="BD8" t="n">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="BE8" t="n">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="BF8" t="n">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="BG8" t="n">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="BH8" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="BI8" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BJ8" t="n">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="BK8" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="BL8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BM8" t="n">
         <v>6</v>
       </c>
       <c r="BN8" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="BO8" t="n">
+        <v>132</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>296</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>85</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>47</v>
+      </c>
+      <c r="BS8" t="n">
         <v>124</v>
       </c>
-      <c r="BP8" t="n">
-        <v>275</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>78</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>113</v>
-      </c>
       <c r="BT8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BU8" t="n">
         <v>14</v>
       </c>
       <c r="BV8" t="n">
-        <v>674</v>
+        <v>724</v>
       </c>
       <c r="BW8" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="BX8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="BY8" t="n">
         <v>3</v>
       </c>
       <c r="BZ8" t="n">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="CA8" t="n">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="CB8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CC8" t="n">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="CD8" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="CE8" t="n">
-        <v>552</v>
+        <v>588</v>
       </c>
       <c r="CF8" t="n">
         <v>15</v>
       </c>
       <c r="CG8" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="CH8" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="CI8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CJ8" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="CK8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CL8" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="CM8" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="CN8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CO8" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="CP8" t="n">
         <v>5</v>
       </c>
       <c r="CQ8" t="n">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="CR8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CS8" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="CT8" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="CU8" t="n">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="CV8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CW8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CX8" t="n">
         <v>17</v>
       </c>
       <c r="CY8" t="n">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="CZ8" t="n">
         <v>3</v>
@@ -6051,10 +6051,10 @@
         <v>19</v>
       </c>
       <c r="DC8" t="n">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="DD8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="DE8" t="n">
         <v>2</v>
@@ -6063,16 +6063,16 @@
         <v>5</v>
       </c>
       <c r="DG8" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="DH8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="DI8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="DJ8" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="DK8" t="n">
         <v>4</v>
@@ -6081,7 +6081,7 @@
         <v>3</v>
       </c>
       <c r="DM8" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
@@ -6090,13 +6090,13 @@
         <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DQ8" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="DR8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="DS8" t="n">
         <v>1</v>
@@ -6105,238 +6105,238 @@
         <v>2</v>
       </c>
       <c r="DU8" t="n">
-        <v>1150</v>
+        <v>1238</v>
       </c>
       <c r="DV8" t="n">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="DW8" t="n">
-        <v>364</v>
+        <v>405</v>
       </c>
       <c r="DX8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="DY8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.4646153846153846</v>
+        <v>0.4739884393063584</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.5189003436426117</v>
+        <v>0.5273311897106109</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.8493150684931506</v>
+        <v>0.8407643312101911</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.3041666666666666</v>
+        <v>0.3019230769230769</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.3428571428571429</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.2767295597484277</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.3041666666666666</v>
+        <v>0.3019230769230769</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.5425709515859767</v>
+        <v>0.5440251572327044</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.5795454545454546</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.5029585798816568</v>
+        <v>0.5133689839572193</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.5041705282669138</v>
+        <v>0.5030276816608996</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.4629032258064516</v>
+        <v>0.4682080924855491</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.5377358490566038</v>
+        <v>0.5379310344827586</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.5857142857142857</v>
+        <v>0.5787671232876712</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.5067024128686327</v>
+        <v>0.5097323600973236</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.4448563484708063</v>
+        <v>0.4498269896193772</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0125</v>
+        <v>0.01153846153846154</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.08347245409015025</v>
+        <v>0.08176100628930817</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.08116883116883117</v>
+        <v>0.08181818181818182</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.1037735849056604</v>
+        <v>0.09865470852017937</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0379746835443038</v>
+        <v>0.03614457831325301</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01538461538461539</v>
+        <v>0.01470588235294118</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.5751295336787565</v>
+        <v>0.586046511627907</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8043478260869565</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.06976744186046512</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.6156716417910447</v>
+        <v>0.608843537414966</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.3088235294117647</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.7290836653386454</v>
+        <v>0.7163636363636363</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.2477064220183486</v>
+        <v>0.2450704225352113</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.6705202312138728</v>
+        <v>0.6608084358523726</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.2754590984974958</v>
+        <v>0.2674961119751166</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.3789473684210526</v>
+        <v>0.3592233009708738</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.2615384615384616</v>
+        <v>0.2481751824817518</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.2978723404255319</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.2357723577235772</v>
+        <v>0.2379182156133829</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.2839506172839506</v>
+        <v>0.2674418604651163</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.5702479338842975</v>
+        <v>0.5572519083969466</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.6513761467889908</v>
+        <v>0.6504065040650406</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.65</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.7554347826086957</v>
+        <v>0.7474747474747475</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.6567164179104478</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.02757352941176471</v>
+        <v>0.02559726962457338</v>
       </c>
       <c r="FQ8" t="n">
-        <v>95.35135135135135</v>
+        <v>95.75184638109306</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.6481481481481481</v>
+        <v>0.6379310344827587</v>
       </c>
       <c r="FS8" t="n">
-        <v>14.44144578313253</v>
+        <v>14.39598811292719</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.75789473684211</v>
+        <v>15.67749077490775</v>
       </c>
       <c r="FU8" t="n">
-        <v>13.87253012048193</v>
+        <v>13.84821693907875</v>
       </c>
       <c r="FV8" t="n">
-        <v>15.08955342902711</v>
+        <v>14.99889298892989</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.2854494902687674</v>
+        <v>0.2854671280276816</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.6915584415584416</v>
+        <v>0.6878787878787879</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.7526501766784452</v>
+        <v>0.7491749174917491</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.5305164319248826</v>
+        <v>0.5462555066079295</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1964782205746061</v>
+        <v>0.1929065743944637</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.3773584905660378</v>
+        <v>0.3766816143497758</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.417910447761194</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.3</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.0732159406858202</v>
+        <v>0.07179930795847751</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.4050632911392405</v>
+        <v>0.4216867469879518</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4375</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.4375</v>
+        <v>0.4</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.1204819277108434</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.3769230769230769</v>
+        <v>0.3676470588235294</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.3828125</v>
+        <v>0.373134328358209</v>
       </c>
       <c r="GL8" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="GM8" t="n">
-        <v>0.3243744207599629</v>
+        <v>0.3321799307958477</v>
       </c>
       <c r="GN8" t="n">
-        <v>0.2771428571428571</v>
+        <v>0.2786458333333333</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.2803468208092486</v>
+        <v>0.281578947368421</v>
       </c>
       <c r="GP8" t="n">
-        <v>0.8041237113402062</v>
+        <v>0.794392523364486</v>
       </c>
       <c r="GQ8" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.48</v>
       </c>
       <c r="GR8" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="GS8" t="n">
-        <v>0.2</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.08403361344537816</v>
+        <v>0.08</v>
       </c>
       <c r="GU8" t="n">
         <v>0.3</v>
@@ -6345,77 +6345,77 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="GW8" t="n">
-        <v>0.2100840336134454</v>
+        <v>0.216</v>
       </c>
       <c r="GX8" t="n">
-        <v>0.36</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="GY8" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9</v>
       </c>
       <c r="GZ8" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.2861271676300578</v>
       </c>
       <c r="HA8" t="n">
-        <v>0.6352941176470588</v>
+        <v>0.6262626262626263</v>
       </c>
       <c r="HB8" t="n">
-        <v>0.08709677419354839</v>
+        <v>0.08092485549132948</v>
       </c>
       <c r="HC8" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.367741935483871</v>
+        <v>0.3786127167630058</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2807017543859649</v>
+        <v>0.2748091603053435</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.7303058387395737</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.2771428571428571</v>
+        <v>0.2786458333333333</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.5531684701492536</v>
+        <v>0.5540986510008703</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.54084</v>
+        <v>0.5413662337662338</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.5353184210526315</v>
+        <v>0.5415969117647059</v>
       </c>
       <c r="HK8" t="n">
-        <v>0.1091370558375634</v>
+        <v>0.1090047393364929</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.1773962804005723</v>
+        <v>0.1767881241565452</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.010351966873706</v>
+        <v>0.01333333333333333</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.1254752851711027</v>
+        <v>0.1207386363636364</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.2897338403041825</v>
+        <v>0.2997159090909091</v>
       </c>
       <c r="HP8" t="n">
-        <v>6.152086811352254</v>
+        <v>6.104245283018868</v>
       </c>
       <c r="HQ8" t="n">
-        <v>25.32736842105263</v>
+        <v>25.34330097087378</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.2931726907630522</v>
+        <v>0.3016344725111441</v>
       </c>
       <c r="HS8" t="n">
         <v>3</v>
       </c>
       <c r="HT8" t="inlineStr"/>
       <c r="HU8" t="n">
-        <v>0.01142857142857143</v>
+        <v>0.01041666666666667</v>
       </c>
     </row>
     <row r="9">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -7133,328 +7133,328 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>35160</v>
+        <v>38040</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>-129</v>
+        <v>-142</v>
       </c>
       <c r="J10" t="n">
-        <v>1164</v>
+        <v>1265</v>
       </c>
       <c r="K10" t="n">
-        <v>1169</v>
+        <v>1271</v>
       </c>
       <c r="L10" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="M10" t="n">
-        <v>323</v>
+        <v>360</v>
       </c>
       <c r="N10" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="O10" t="n">
-        <v>2333</v>
+        <v>2536</v>
       </c>
       <c r="P10" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="Q10" t="n">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="R10" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S10" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U10" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="V10" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="W10" t="n">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="X10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Y10" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="Z10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AA10" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD10" t="n">
         <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AF10" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="AG10" t="n">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="AH10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AL10" t="n">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="AM10" t="n">
-        <v>590</v>
+        <v>641</v>
       </c>
       <c r="AN10" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="AO10" t="n">
-        <v>426</v>
+        <v>467</v>
       </c>
       <c r="AP10" t="n">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1283</v>
+        <v>1397</v>
       </c>
       <c r="AR10" t="n">
-        <v>1412</v>
+        <v>1539</v>
       </c>
       <c r="AS10" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AT10" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AW10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="AX10" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="AY10" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="AZ10" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="BA10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BB10" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="BC10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BD10" t="n">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="BE10" t="n">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="BF10" t="n">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="BG10" t="n">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="BH10" t="n">
         <v>72</v>
       </c>
       <c r="BI10" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="BJ10" t="n">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="BK10" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="BL10" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BN10" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="BO10" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="BP10" t="n">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="BQ10" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="BR10" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="BS10" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="BU10" t="n">
         <v>13</v>
       </c>
       <c r="BV10" t="n">
-        <v>693</v>
+        <v>755</v>
       </c>
       <c r="BW10" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="BX10" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="BY10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="CA10" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="CB10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CC10" t="n">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="CD10" t="n">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="CE10" t="n">
-        <v>575</v>
+        <v>623</v>
       </c>
       <c r="CF10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="CG10" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="CH10" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="CI10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="CJ10" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="CK10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CL10" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="CM10" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="CN10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CO10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="CP10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CQ10" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="CR10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="CS10" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="CT10" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="CU10" t="n">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="CV10" t="n">
         <v>9</v>
       </c>
       <c r="CW10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="CX10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CY10" t="n">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="CZ10" t="n">
         <v>1</v>
       </c>
       <c r="DA10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="DB10" t="n">
         <v>18</v>
       </c>
       <c r="DC10" t="n">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="DD10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DE10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DF10" t="n">
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="DH10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DI10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="DJ10" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="DK10" t="n">
         <v>6</v>
@@ -7463,7 +7463,7 @@
         <v>5</v>
       </c>
       <c r="DM10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
@@ -7472,13 +7472,13 @@
         <v>6</v>
       </c>
       <c r="DP10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DQ10" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="DR10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DS10" t="n">
         <v>3</v>
@@ -7487,315 +7487,315 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1098</v>
+        <v>1197</v>
       </c>
       <c r="DV10" t="n">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="DW10" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="DX10" t="n">
+        <v>39</v>
+      </c>
+      <c r="DY10" t="n">
         <v>31</v>
       </c>
-      <c r="DY10" t="n">
-        <v>27</v>
-      </c>
       <c r="DZ10" t="n">
-        <v>0.525974025974026</v>
+        <v>0.5255255255255256</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.587248322147651</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3450704225352113</v>
+        <v>0.3404710920770878</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.3027522935779817</v>
+        <v>0.293103448275862</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3450704225352113</v>
+        <v>0.3404710920770878</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5220338983050847</v>
+        <v>0.5195007800312013</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.51</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.5</v>
+        <v>0.4916201117318436</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5201771653543307</v>
+        <v>0.5157942238267148</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5254777070063694</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.4816849816849817</v>
+        <v>0.4711864406779661</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5638204225352113</v>
+        <v>0.5615942028985508</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.5854430379746836</v>
+        <v>0.5747126436781609</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5474006116207951</v>
+        <v>0.5434173669467787</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4192913385826771</v>
+        <v>0.4214801444043321</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.002347417840375587</v>
+        <v>0.004282655246252677</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.09322033898305085</v>
+        <v>0.09204368174726989</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.134020618556701</v>
+        <v>0.128125</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0625</v>
+        <v>0.06637168141592921</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.03296703296703297</v>
+        <v>0.03157894736842105</v>
       </c>
       <c r="EV10" t="inlineStr"/>
       <c r="EW10" t="n">
-        <v>0.5971563981042654</v>
+        <v>0.5973451327433629</v>
       </c>
       <c r="EX10" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0.6779661016949152</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0.3550488599348534</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.6790540540540541</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.2980132450331126</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0.6785109983079526</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0.3267651888341543</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0.4841269841269841</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0.2796610169491525</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0.3177570093457944</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0.6291079812206573</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0.8072289156626506</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0.06545454545454546</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>96</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0.5094339622641509</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>15.12648221343873</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>14.87411487018096</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>14.47446640316206</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>14.22541306058222</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0.2888086642599278</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0.603125</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0.6917562724014337</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.5595854922279793</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0.203971119133574</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.4778761061946903</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0.5118483412322274</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0.08574007220216606</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0.3368421052631579</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="GH10" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="GI10" t="n">
+        <v>0.1236462093862816</v>
+      </c>
+      <c r="GJ10" t="n">
+        <v>0.3576642335766423</v>
+      </c>
+      <c r="GK10" t="n">
+        <v>0.3576642335766423</v>
+      </c>
+      <c r="GL10" t="n">
+        <v>0.9591836734693877</v>
+      </c>
+      <c r="GM10" t="n">
+        <v>0.2978339350180506</v>
+      </c>
+      <c r="GN10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="GO10" t="n">
+        <v>0.3353658536585366</v>
+      </c>
+      <c r="GP10" t="n">
         <v>0.8</v>
       </c>
-      <c r="EY10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="EZ10" t="n">
-        <v>0.6851851851851852</v>
-      </c>
-      <c r="FA10" t="n">
-        <v>0.3487544483985765</v>
-      </c>
-      <c r="FB10" t="n">
-        <v>0.6881720430107527</v>
-      </c>
-      <c r="FC10" t="n">
-        <v>0.2967032967032967</v>
-      </c>
-      <c r="FD10" t="n">
-        <v>0.6867030965391621</v>
-      </c>
-      <c r="FE10" t="n">
-        <v>0.3231046931407942</v>
-      </c>
-      <c r="FF10" t="n">
-        <v>0.4642857142857143</v>
-      </c>
-      <c r="FG10" t="n">
-        <v>0.2844036697247707</v>
-      </c>
-      <c r="FH10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="FI10" t="n">
-        <v>0.310880829015544</v>
-      </c>
-      <c r="FJ10" t="n">
-        <v>0.2625</v>
-      </c>
-      <c r="FK10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="FL10" t="n">
-        <v>0.6774193548387096</v>
-      </c>
-      <c r="FM10" t="n">
-        <v>0.7887323943661971</v>
-      </c>
-      <c r="FN10" t="n">
-        <v>0.6323529411764706</v>
-      </c>
-      <c r="FO10" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="FP10" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="FQ10" t="n">
-        <v>95.54948805460751</v>
-      </c>
-      <c r="FR10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="FS10" t="n">
-        <v>15.2770618556701</v>
-      </c>
-      <c r="FT10" t="n">
-        <v>14.86526946107784</v>
-      </c>
-      <c r="FU10" t="n">
-        <v>14.63496563573883</v>
-      </c>
-      <c r="FV10" t="n">
-        <v>14.21377245508982</v>
-      </c>
-      <c r="FW10" t="n">
-        <v>0.2864173228346457</v>
-      </c>
-      <c r="FX10" t="n">
-        <v>0.6116838487972509</v>
-      </c>
-      <c r="FY10" t="n">
-        <v>0.7063492063492064</v>
-      </c>
-      <c r="FZ10" t="n">
-        <v>0.5561797752808989</v>
-      </c>
-      <c r="GA10" t="n">
-        <v>0.2047244094488189</v>
-      </c>
-      <c r="GB10" t="n">
-        <v>0.4759615384615384</v>
-      </c>
-      <c r="GC10" t="n">
-        <v>0.5076923076923077</v>
-      </c>
-      <c r="GD10" t="n">
-        <v>0.5050505050505051</v>
-      </c>
-      <c r="GE10" t="n">
-        <v>0.08956692913385826</v>
-      </c>
-      <c r="GF10" t="n">
-        <v>0.3406593406593407</v>
-      </c>
-      <c r="GG10" t="n">
-        <v>0.3522727272727273</v>
-      </c>
-      <c r="GH10" t="n">
-        <v>0.4193548387096774</v>
-      </c>
-      <c r="GI10" t="n">
-        <v>0.1220472440944882</v>
-      </c>
-      <c r="GJ10" t="n">
-        <v>0.3548387096774194</v>
-      </c>
-      <c r="GK10" t="n">
-        <v>0.3548387096774194</v>
-      </c>
-      <c r="GL10" t="n">
-        <v>0.9545454545454546</v>
-      </c>
-      <c r="GM10" t="n">
-        <v>0.297244094488189</v>
-      </c>
-      <c r="GN10" t="n">
-        <v>0.3410596026490066</v>
-      </c>
-      <c r="GO10" t="n">
-        <v>0.3421926910299004</v>
-      </c>
-      <c r="GP10" t="n">
-        <v>0.7864077669902912</v>
-      </c>
       <c r="GQ10" t="n">
-        <v>0.4652777777777778</v>
+        <v>0.4713375796178344</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5373134328358209</v>
+        <v>0.527027027027027</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1025641025641026</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1082802547770701</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.375</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="GV10" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.25</v>
+        <v>0.2547770700636943</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.375</v>
       </c>
       <c r="GY10" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3003663003663004</v>
+        <v>0.3050847457627119</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5888888888888889</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1208791208791209</v>
+        <v>0.1220338983050848</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.303030303030303</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2783882783882784</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3026315789473684</v>
+        <v>0.3</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7057086614173228</v>
+        <v>0.7102888086642599</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3410596026490066</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5392689416419387</v>
+        <v>0.5410024025385313</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5282701086956522</v>
+        <v>0.5312343137254901</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5299041044776119</v>
+        <v>0.530085</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1076923076923077</v>
+        <v>0.1093620546810273</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1656804733727811</v>
+        <v>0.1682496607869742</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.01631701631701632</v>
+        <v>0.01702127659574468</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1441932969602494</v>
+        <v>0.1431639226914818</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.2790335151987529</v>
+        <v>0.2777380100214746</v>
       </c>
       <c r="HP10" t="n">
-        <v>6.540847457627119</v>
+        <v>6.412948517940717</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.68702830188679</v>
+        <v>25.61010752688172</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.2852233676975945</v>
+        <v>0.2814229249011858</v>
       </c>
       <c r="HS10" t="n">
         <v>3</v>
       </c>
       <c r="HT10" t="inlineStr"/>
       <c r="HU10" t="n">
-        <v>0.003311258278145695</v>
+        <v>0.006060606060606061</v>
       </c>
     </row>
     <row r="11">
@@ -9921,67 +9921,67 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>43800</v>
+        <v>46680</v>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>-163</v>
+        <v>-150</v>
       </c>
       <c r="J14" t="n">
-        <v>1491</v>
+        <v>1592</v>
       </c>
       <c r="K14" t="n">
-        <v>1505</v>
+        <v>1607</v>
       </c>
       <c r="L14" t="n">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="M14" t="n">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="N14" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="O14" t="n">
-        <v>2996</v>
+        <v>3199</v>
       </c>
       <c r="P14" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="Q14" t="n">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="R14" t="n">
+        <v>54</v>
+      </c>
+      <c r="S14" t="n">
+        <v>88</v>
+      </c>
+      <c r="T14" t="n">
+        <v>71</v>
+      </c>
+      <c r="U14" t="n">
+        <v>125</v>
+      </c>
+      <c r="V14" t="n">
+        <v>123</v>
+      </c>
+      <c r="W14" t="n">
+        <v>332</v>
+      </c>
+      <c r="X14" t="n">
         <v>52</v>
       </c>
-      <c r="S14" t="n">
-        <v>86</v>
-      </c>
-      <c r="T14" t="n">
-        <v>69</v>
-      </c>
-      <c r="U14" t="n">
-        <v>121</v>
-      </c>
-      <c r="V14" t="n">
-        <v>111</v>
-      </c>
-      <c r="W14" t="n">
-        <v>312</v>
-      </c>
-      <c r="X14" t="n">
-        <v>49</v>
-      </c>
       <c r="Y14" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="Z14" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AA14" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="AB14" t="n">
         <v>10</v>
@@ -9993,263 +9993,263 @@
         <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="n">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AJ14" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="AK14" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="AL14" t="n">
+        <v>413</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>888</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>189</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>571</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>303</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1696</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1846</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>74</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>127</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>71</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>56</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>288</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>107</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>233</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>51</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>150</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>141</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>508</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>408</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>418</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>486</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>81</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>90</v>
+      </c>
+      <c r="BJ14" t="n">
         <v>387</v>
       </c>
-      <c r="AM14" t="n">
-        <v>837</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>175</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>539</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>270</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1569</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1732</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>121</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>66</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>262</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>101</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>220</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>140</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>116</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>456</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>382</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>392</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>447</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>78</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>84</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>367</v>
-      </c>
       <c r="BK14" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="BL14" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="BM14" t="n">
         <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="BO14" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="BP14" t="n">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="BQ14" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="BR14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="BS14" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="BT14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BU14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BV14" t="n">
-        <v>829</v>
+        <v>894</v>
       </c>
       <c r="BW14" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="BX14" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="CA14" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="CB14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CC14" t="n">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="CD14" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="CE14" t="n">
-        <v>748</v>
+        <v>803</v>
       </c>
       <c r="CF14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CG14" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="CH14" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="CI14" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="CJ14" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="CK14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CL14" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="CM14" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="CN14" t="n">
         <v>13</v>
       </c>
       <c r="CO14" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="CR14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CS14" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="CT14" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="CU14" t="n">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CX14" t="n">
         <v>16</v>
       </c>
       <c r="CY14" t="n">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="CZ14" t="n">
         <v>12</v>
       </c>
       <c r="DA14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="DB14" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>388</v>
+      </c>
+      <c r="DD14" t="n">
         <v>30</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>350</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>29</v>
       </c>
       <c r="DE14" t="n">
         <v>1</v>
       </c>
       <c r="DF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DG14" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="DH14" t="n">
         <v>4</v>
       </c>
       <c r="DI14" t="n">
+        <v>50</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="DM14" t="n">
         <v>42</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK14" t="n">
-        <v>4</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>40</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10258,253 +10258,253 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="DQ14" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="DR14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="DS14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DT14" t="n">
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1307</v>
+        <v>1408</v>
       </c>
       <c r="DV14" t="n">
-        <v>456</v>
+        <v>508</v>
       </c>
       <c r="DW14" t="n">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="DX14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="DY14" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4935400516795866</v>
+        <v>0.4939467312348668</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5536231884057971</v>
+        <v>0.5543478260869565</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8514285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3246753246753247</v>
+        <v>0.3309982486865149</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3943661971830986</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3285714285714286</v>
+        <v>0.34</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.3246753246753247</v>
+        <v>0.3309982486865149</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4623655913978494</v>
+        <v>0.4650900900900901</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.5785123966942148</v>
+        <v>0.5826771653543307</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4590909090909091</v>
+        <v>0.4592274678111588</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.4720203488372093</v>
+        <v>0.4773817683344757</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.5668449197860963</v>
+        <v>0.5858585858585859</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.47911227154047</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5114229765013055</v>
+        <v>0.5183710961420698</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.6036866359447005</v>
+        <v>0.6233766233766234</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5254041570438799</v>
+        <v>0.5382978723404256</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3917151162790697</v>
+        <v>0.3913639479095271</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01855287569573284</v>
+        <v>0.01751313485113835</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1302270011947431</v>
+        <v>0.1261261261261261</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1770573566084788</v>
+        <v>0.1738095238095238</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.1057692307692308</v>
+        <v>0.1024096385542169</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.04032258064516129</v>
+        <v>0.03676470588235294</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.02325581395348837</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6195121951219512</v>
+        <v>0.6351351351351351</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.918918918918919</v>
+        <v>0.9</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.1282051282051282</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6676136363636364</v>
+        <v>0.6613756613756614</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3355855855855856</v>
+        <v>0.3390191897654584</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7213622291021672</v>
+        <v>0.71875</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2584269662921349</v>
+        <v>0.2680965147453083</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.689041095890411</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.30125</v>
+        <v>0.3076009501187649</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3895348837209303</v>
+        <v>0.3944444444444444</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3266331658291458</v>
+        <v>0.3236714975845411</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2560975609756098</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.284</v>
+        <v>0.2895752895752896</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.1981132075471698</v>
+        <v>0.2192982456140351</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.5759493670886076</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.6950354609929078</v>
+        <v>0.7</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.7611940298507462</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7110091743119266</v>
+        <v>0.702928870292887</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7522123893805309</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03508771929824561</v>
+        <v>0.03457814661134163</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.49863013698631</v>
+        <v>98.68380462724936</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6911764705882353</v>
       </c>
       <c r="FS14" t="n">
-        <v>14.96197183098591</v>
+        <v>14.97223618090452</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.28019933554817</v>
+        <v>14.21543248288737</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.19892689470154</v>
+        <v>14.21809045226131</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.70318936877076</v>
+        <v>13.62688238954574</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2914244186046512</v>
+        <v>0.2878684030157642</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5660847880299252</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6878787878787879</v>
+        <v>0.6858789625360231</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.5330396475770925</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2267441860465116</v>
+        <v>0.227553118574366</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.3557692307692308</v>
+        <v>0.3704819277108434</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.3978494623655914</v>
+        <v>0.412751677852349</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.4324324324324325</v>
+        <v>0.4471544715447154</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.09011627906976744</v>
+        <v>0.0932145305003427</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.3951612903225806</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3969465648854962</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.4489795918367347</v>
+        <v>0.4423076923076923</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.125</v>
+        <v>0.1261137765592872</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3720930232558139</v>
+        <v>0.3641304347826087</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3722222222222222</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.96875</v>
+        <v>0.9701492537313433</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.2667151162790697</v>
+        <v>0.2652501713502399</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.3024523160762943</v>
+        <v>0.3152454780361757</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3074792243767313</v>
+        <v>0.3202099737532809</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.7950819672131147</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4598930481283423</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.6046511627906976</v>
+        <v>0.6136363636363636</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.106951871657754</v>
+        <v>0.101010101010101</v>
       </c>
       <c r="GU14" t="n">
         <v>0.5</v>
@@ -10513,77 +10513,77 @@
         <v>0.9</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2459893048128342</v>
+        <v>0.2575757575757576</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="GY14" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3361111111111111</v>
+        <v>0.3263707571801567</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5702479338842975</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1138888888888889</v>
+        <v>0.1148825065274151</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.275</v>
+        <v>0.2767624020887728</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3131313131313131</v>
+        <v>0.3396226415094339</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6831395348837209</v>
+        <v>0.6792323509252913</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.3024523160762943</v>
+        <v>0.3152454780361757</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5483911678832116</v>
+        <v>0.5476803509979353</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5533604477611941</v>
+        <v>0.5530496428571429</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5442357746478873</v>
+        <v>0.5423365079365079</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09664429530201342</v>
+        <v>0.09791535060012634</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1476793248945148</v>
+        <v>0.1496531219028741</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.007380073800738007</v>
+        <v>0.006968641114982578</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1669853409815169</v>
+        <v>0.169811320754717</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2906309751434035</v>
+        <v>0.2995283018867925</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.688649940262843</v>
+        <v>6.779054054054054</v>
       </c>
       <c r="HQ14" t="n">
-        <v>24.99812734082397</v>
+        <v>24.98886925795053</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2837022132796781</v>
+        <v>0.2883165829145728</v>
       </c>
       <c r="HS14" t="n">
         <v>6</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.01634877384196185</v>
+        <v>0.01550387596899225</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -7133,67 +7133,67 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>38040</v>
+        <v>40920</v>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>-142</v>
+        <v>-115</v>
       </c>
       <c r="J10" t="n">
-        <v>1265</v>
+        <v>1363</v>
       </c>
       <c r="K10" t="n">
-        <v>1271</v>
+        <v>1370</v>
       </c>
       <c r="L10" t="n">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="M10" t="n">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="N10" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="O10" t="n">
-        <v>2536</v>
+        <v>2733</v>
       </c>
       <c r="P10" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="Q10" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="R10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S10" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T10" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="U10" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="V10" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="W10" t="n">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="X10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Z10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AA10" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
@@ -7205,13 +7205,13 @@
         <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AF10" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="AG10" t="n">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
@@ -7220,37 +7220,37 @@
         <v>40</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AL10" t="n">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="AM10" t="n">
-        <v>641</v>
+        <v>688</v>
       </c>
       <c r="AN10" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="AO10" t="n">
-        <v>467</v>
+        <v>509</v>
       </c>
       <c r="AP10" t="n">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1397</v>
+        <v>1515</v>
       </c>
       <c r="AR10" t="n">
-        <v>1539</v>
+        <v>1630</v>
       </c>
       <c r="AS10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AT10" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="AU10" t="n">
         <v>21</v>
@@ -7259,184 +7259,184 @@
         <v>57</v>
       </c>
       <c r="AW10" t="n">
+        <v>41</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>214</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>202</v>
+      </c>
+      <c r="BA10" t="n">
         <v>35</v>
       </c>
-      <c r="AX10" t="n">
-        <v>200</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>88</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>179</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>34</v>
-      </c>
       <c r="BB10" t="n">
+        <v>129</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>119</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>424</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>382</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>336</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>447</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>75</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>72</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>359</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>61</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>191</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>149</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>340</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>99</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>117</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>58</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>829</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX10" t="n">
         <v>116</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>110</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>388</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>350</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>316</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>405</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>72</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>70</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>330</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>110</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>59</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>175</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>135</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>310</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>88</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>47</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>108</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>54</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>755</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>90</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>109</v>
       </c>
       <c r="BY10" t="n">
         <v>4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="CA10" t="n">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="CB10" t="n">
         <v>19</v>
       </c>
       <c r="CC10" t="n">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="CD10" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="CE10" t="n">
-        <v>623</v>
+        <v>681</v>
       </c>
       <c r="CF10" t="n">
         <v>36</v>
       </c>
       <c r="CG10" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="CH10" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="CI10" t="n">
         <v>48</v>
       </c>
       <c r="CJ10" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="CK10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL10" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="CM10" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="CN10" t="n">
         <v>12</v>
       </c>
       <c r="CO10" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="CP10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CQ10" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="CR10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="CS10" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="CT10" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="CU10" t="n">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="CV10" t="n">
         <v>9</v>
       </c>
       <c r="CW10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CX10" t="n">
         <v>22</v>
       </c>
       <c r="CY10" t="n">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="CZ10" t="n">
         <v>1</v>
       </c>
       <c r="DA10" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="DB10" t="n">
         <v>18</v>
       </c>
       <c r="DC10" t="n">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="DD10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="DE10" t="n">
         <v>5</v>
@@ -7445,16 +7445,16 @@
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="DH10" t="n">
         <v>8</v>
       </c>
       <c r="DI10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="DJ10" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="DK10" t="n">
         <v>6</v>
@@ -7463,7 +7463,7 @@
         <v>5</v>
       </c>
       <c r="DM10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
@@ -7472,251 +7472,251 @@
         <v>6</v>
       </c>
       <c r="DP10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DQ10" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="DR10" t="n">
         <v>27</v>
       </c>
       <c r="DS10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DT10" t="n">
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1197</v>
+        <v>1301</v>
       </c>
       <c r="DV10" t="n">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="DW10" t="n">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="DX10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="DY10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.5255255255255256</v>
+        <v>0.532033426183844</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.587248322147651</v>
+        <v>0.5913312693498453</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8563218390804598</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3404710920770878</v>
+        <v>0.3418467583497053</v>
       </c>
       <c r="ED10" t="n">
         <v>0.3684210526315789</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.293103448275862</v>
+        <v>0.2713178294573643</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3404710920770878</v>
+        <v>0.3418467583497053</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5195007800312013</v>
+        <v>0.5218023255813954</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.51</v>
+        <v>0.5188679245283019</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4916201117318436</v>
+        <v>0.495049504950495</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5157942238267148</v>
+        <v>0.5179615705931495</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5254777070063694</v>
+        <v>0.5306748466257669</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.4711864406779661</v>
+        <v>0.4607250755287009</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5615942028985508</v>
+        <v>0.5637108792846498</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.5747126436781609</v>
+        <v>0.5815217391304348</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5434173669467787</v>
+        <v>0.5326633165829145</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4214801444043321</v>
+        <v>0.4252297410192147</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.004282655246252677</v>
+        <v>0.005893909626719057</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.09204368174726989</v>
+        <v>0.08866279069767442</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.128125</v>
+        <v>0.1205882352941176</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06637168141592921</v>
+        <v>0.06854838709677419</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.03157894736842105</v>
+        <v>0.03</v>
       </c>
       <c r="EV10" t="inlineStr"/>
       <c r="EW10" t="n">
-        <v>0.5973451327433629</v>
+        <v>0.602510460251046</v>
       </c>
       <c r="EX10" t="n">
         <v>0.8260869565217391</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1481481481481481</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6779661016949152</v>
+        <v>0.6820987654320988</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3550488599348534</v>
+        <v>0.3536585365853658</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.6790540540540541</v>
+        <v>0.6892307692307692</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2980132450331126</v>
+        <v>0.2957317073170732</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6785109983079526</v>
+        <v>0.6856702619414484</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3267651888341543</v>
+        <v>0.3246951219512195</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4841269841269841</v>
+        <v>0.4661654135338346</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2796610169491525</v>
+        <v>0.2900763358778626</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.25</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.3177570093457944</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.25</v>
+        <v>0.2755102040816326</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.5903614457831325</v>
+        <v>0.5876288659793815</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6901408450704225</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7625</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.6291079812206573</v>
+        <v>0.6510638297872341</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.8072289156626506</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.06545454545454546</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="FQ10" t="n">
-        <v>96</v>
+        <v>96.17595307917888</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.5094339622641509</v>
+        <v>0.45</v>
       </c>
       <c r="FS10" t="n">
-        <v>15.12648221343873</v>
+        <v>15.06250917094644</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.87411487018096</v>
+        <v>14.88306569343066</v>
       </c>
       <c r="FU10" t="n">
-        <v>14.47446640316206</v>
+        <v>14.41298606016141</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.22541306058222</v>
+        <v>14.22408759124088</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.2888086642599278</v>
+        <v>0.2840434419381788</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.603125</v>
+        <v>0.6058823529411764</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.6917562724014337</v>
+        <v>0.6889632107023411</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5595854922279793</v>
+        <v>0.5679611650485437</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.203971119133574</v>
+        <v>0.2071846282372598</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4778761061946903</v>
+        <v>0.4717741935483871</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.5118483412322274</v>
+        <v>0.5064935064935064</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.5</v>
+        <v>0.4957264957264957</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.08574007220216606</v>
+        <v>0.0835421888053467</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3368421052631579</v>
+        <v>0.36</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.40625</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.1236462093862816</v>
+        <v>0.12531328320802</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3576642335766423</v>
+        <v>0.3466666666666667</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3576642335766423</v>
+        <v>0.3466666666666667</v>
       </c>
       <c r="GL10" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2978339350180506</v>
+        <v>0.2999164578111946</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3398328690807799</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3353658536585366</v>
+        <v>0.3426966292134832</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8</v>
+        <v>0.8114754098360656</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.4713375796178344</v>
+        <v>0.4662576687116564</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.527027027027027</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.1</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.1082802547770701</v>
+        <v>0.1042944785276074</v>
       </c>
       <c r="GU10" t="n">
         <v>0.3529411764705883</v>
@@ -7725,7 +7725,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.2547770700636943</v>
+        <v>0.245398773006135</v>
       </c>
       <c r="GX10" t="n">
         <v>0.375</v>
@@ -7734,68 +7734,68 @@
         <v>0.8</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.3050847457627119</v>
+        <v>0.2960725075528701</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5888888888888889</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1220338983050848</v>
+        <v>0.1238670694864048</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2711864406779661</v>
+        <v>0.2658610271903323</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.3</v>
+        <v>0.2840909090909091</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7102888086642599</v>
+        <v>0.7092731829573935</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3398328690807799</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5410024025385313</v>
+        <v>0.5412078925272881</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5312343137254901</v>
+        <v>0.5290923809523809</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.530085</v>
+        <v>0.5285976923076923</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1093620546810273</v>
+        <v>0.1089792785878741</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1682496607869742</v>
+        <v>0.1694058154235145</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.01702127659574468</v>
+        <v>0.015625</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1431639226914818</v>
+        <v>0.1412541254125413</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.2777380100214746</v>
+        <v>0.2798679867986799</v>
       </c>
       <c r="HP10" t="n">
-        <v>6.412948517940717</v>
+        <v>6.422674418604651</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.61010752688172</v>
+        <v>25.58557312252964</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.2814229249011858</v>
+        <v>0.2905355832721937</v>
       </c>
       <c r="HS10" t="n">
         <v>3</v>
       </c>
       <c r="HT10" t="inlineStr"/>
       <c r="HU10" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.008356545961002786</v>
       </c>
     </row>
     <row r="11">
@@ -9921,67 +9921,67 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>46680</v>
+        <v>49560</v>
       </c>
       <c r="H14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>-150</v>
+        <v>-177</v>
       </c>
       <c r="J14" t="n">
-        <v>1592</v>
+        <v>1690</v>
       </c>
       <c r="K14" t="n">
-        <v>1607</v>
+        <v>1706</v>
       </c>
       <c r="L14" t="n">
-        <v>459</v>
+        <v>488</v>
       </c>
       <c r="M14" t="n">
-        <v>571</v>
+        <v>612</v>
       </c>
       <c r="N14" t="n">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="O14" t="n">
-        <v>3199</v>
+        <v>3396</v>
       </c>
       <c r="P14" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="Q14" t="n">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="R14" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="S14" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="T14" t="n">
+        <v>73</v>
+      </c>
+      <c r="U14" t="n">
+        <v>130</v>
+      </c>
+      <c r="V14" t="n">
+        <v>132</v>
+      </c>
+      <c r="W14" t="n">
+        <v>351</v>
+      </c>
+      <c r="X14" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>145</v>
+      </c>
+      <c r="Z14" t="n">
         <v>71</v>
       </c>
-      <c r="U14" t="n">
-        <v>125</v>
-      </c>
-      <c r="V14" t="n">
-        <v>123</v>
-      </c>
-      <c r="W14" t="n">
-        <v>332</v>
-      </c>
-      <c r="X14" t="n">
-        <v>52</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>136</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>67</v>
-      </c>
       <c r="AA14" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AB14" t="n">
         <v>10</v>
@@ -9990,193 +9990,193 @@
         <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AF14" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="n">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AJ14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AK14" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AL14" t="n">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="AM14" t="n">
-        <v>888</v>
+        <v>942</v>
       </c>
       <c r="AN14" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="AO14" t="n">
-        <v>571</v>
+        <v>612</v>
       </c>
       <c r="AP14" t="n">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1696</v>
+        <v>1787</v>
       </c>
       <c r="AR14" t="n">
-        <v>1846</v>
+        <v>1964</v>
       </c>
       <c r="AS14" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AT14" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="AU14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV14" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AW14" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AX14" t="n">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="AY14" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AZ14" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="BA14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="BB14" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="BC14" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BD14" t="n">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="BE14" t="n">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="BF14" t="n">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="BG14" t="n">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="BH14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="BI14" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="BJ14" t="n">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="BK14" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="BL14" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="BM14" t="n">
         <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="BO14" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="BP14" t="n">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="BQ14" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="BR14" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="BS14" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="BT14" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="BU14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BV14" t="n">
-        <v>894</v>
+        <v>947</v>
       </c>
       <c r="BW14" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="BX14" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="CA14" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="CB14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CC14" t="n">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="CD14" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="CE14" t="n">
-        <v>803</v>
+        <v>851</v>
       </c>
       <c r="CF14" t="n">
         <v>25</v>
       </c>
       <c r="CG14" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="CH14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="CI14" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="CK14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="CL14" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="CM14" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="CN14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CO14" t="n">
         <v>68</v>
@@ -10185,44 +10185,44 @@
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="CR14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CS14" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="CT14" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="CU14" t="n">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="CX14" t="n">
         <v>16</v>
       </c>
       <c r="CY14" t="n">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="CZ14" t="n">
         <v>12</v>
       </c>
       <c r="DA14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="DB14" t="n">
         <v>31</v>
       </c>
       <c r="DC14" t="n">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="DD14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="DE14" t="n">
         <v>1</v>
@@ -10231,22 +10231,22 @@
         <v>5</v>
       </c>
       <c r="DG14" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="DH14" t="n">
         <v>4</v>
       </c>
       <c r="DI14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="DJ14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DK14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DL14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DM14" t="n">
         <v>42</v>
@@ -10258,13 +10258,13 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="DQ14" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="DR14" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="DS14" t="n">
         <v>2</v>
@@ -10273,238 +10273,238 @@
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1408</v>
+        <v>1481</v>
       </c>
       <c r="DV14" t="n">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="DW14" t="n">
-        <v>459</v>
+        <v>488</v>
       </c>
       <c r="DX14" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="DY14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4939467312348668</v>
+        <v>0.4954337899543379</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5543478260869565</v>
+        <v>0.5578406169665809</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8592964824120602</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3309982486865149</v>
+        <v>0.3251633986928105</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.3943661971830986</v>
+        <v>0.3815789473684211</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.34</v>
+        <v>0.3212121212121212</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.3309982486865149</v>
+        <v>0.3251633986928105</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4650900900900901</v>
+        <v>0.464968152866242</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.5826771653543307</v>
+        <v>0.5984848484848485</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4592274678111588</v>
+        <v>0.4508196721311475</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.4773817683344757</v>
+        <v>0.4739382239382239</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.5858585858585859</v>
+        <v>0.5889423076923077</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.47911227154047</v>
+        <v>0.4633251833740831</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5183710961420698</v>
+        <v>0.5147143681477208</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.6233766233766234</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5382978723404256</v>
+        <v>0.5231388329979879</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3913639479095271</v>
+        <v>0.3938223938223938</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01751313485113835</v>
+        <v>0.01633986928104575</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1261261261261261</v>
+        <v>0.1263269639065817</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1738095238095238</v>
+        <v>0.1771300448430493</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.1024096385542169</v>
+        <v>0.09971509971509972</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.03676470588235294</v>
+        <v>0.03448275862068965</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.02173913043478261</v>
+        <v>0.02051282051282051</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6351351351351351</v>
+        <v>0.6297872340425532</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.9</v>
+        <v>0.9024390243902439</v>
       </c>
       <c r="EY14" t="n">
         <v>0.119047619047619</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6613756613756614</v>
+        <v>0.6616541353383458</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3390191897654584</v>
+        <v>0.3353413654618474</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.71875</v>
+        <v>0.7195767195767195</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2680965147453083</v>
+        <v>0.263681592039801</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.689041095890411</v>
+        <v>0.6898326898326899</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.3076009501187649</v>
+        <v>0.3033333333333333</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3944444444444444</v>
+        <v>0.3969072164948453</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3236714975845411</v>
+        <v>0.3179723502304148</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2560975609756098</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2895752895752896</v>
+        <v>0.2775800711743772</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.2192982456140351</v>
+        <v>0.231404958677686</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.5759493670886076</v>
+        <v>0.5878787878787879</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.7</v>
+        <v>0.6932515337423313</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7605633802816901</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.702928870292887</v>
+        <v>0.7137254901960784</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7522123893805309</v>
+        <v>0.7317073170731707</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03457814661134163</v>
+        <v>0.03229974160206718</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.68380462724936</v>
+        <v>98.67312348668281</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.6911764705882353</v>
+        <v>0.6901408450704225</v>
       </c>
       <c r="FS14" t="n">
-        <v>14.97223618090452</v>
+        <v>14.98260355029586</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.21543248288737</v>
+        <v>14.20832356389215</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.21809045226131</v>
+        <v>14.22585798816568</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.62688238954574</v>
+        <v>13.61846424384525</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2878684030157642</v>
+        <v>0.287001287001287</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5605381165919282</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6858789625360231</v>
+        <v>0.6811989100817438</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.528</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.227553118574366</v>
+        <v>0.2258687258687259</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.3704819277108434</v>
+        <v>0.3760683760683761</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.412751677852349</v>
+        <v>0.4177215189873418</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.4471544715447154</v>
+        <v>0.4621212121212121</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0932145305003427</v>
+        <v>0.09330759330759331</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.3823529411764706</v>
+        <v>0.3862068965517241</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.3969465648854962</v>
+        <v>0.4</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.4423076923076923</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1261137765592872</v>
+        <v>0.1254826254826255</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3641304347826087</v>
+        <v>0.3641025641025641</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.3722222222222222</v>
+        <v>0.3717277486910995</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.9701492537313433</v>
+        <v>0.971830985915493</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.2652501713502399</v>
+        <v>0.2683397683397684</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.3152454780361757</v>
+        <v>0.3069544364508393</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3202099737532809</v>
+        <v>0.3114355231143552</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.7950819672131147</v>
+        <v>0.796875</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4471153846153846</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.6136363636363636</v>
+        <v>0.6344086021505376</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.2542372881355932</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.101010101010101</v>
+        <v>0.09615384615384616</v>
       </c>
       <c r="GU14" t="n">
         <v>0.5</v>
@@ -10513,77 +10513,77 @@
         <v>0.9</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2575757575757576</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="GY14" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3263707571801567</v>
+        <v>0.3178484107579462</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5615384615384615</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1148825065274151</v>
+        <v>0.1149144254278729</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.3404255319148936</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.2767624020887728</v>
+        <v>0.2885085574572127</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3396226415094339</v>
+        <v>0.3135593220338983</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6792323509252913</v>
+        <v>0.6808236808236808</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.3152454780361757</v>
+        <v>0.3069544364508393</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5476803509979353</v>
+        <v>0.5467297026502909</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5530496428571429</v>
+        <v>0.5523819727891156</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5423365079365079</v>
+        <v>0.5416579207920792</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09791535060012634</v>
+        <v>0.09571938168846611</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1496531219028741</v>
+        <v>0.1471415182755389</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.006968641114982578</v>
+        <v>0.006504065040650406</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.169811320754717</v>
+        <v>0.1712367095691102</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2995283018867925</v>
+        <v>0.2921096810296586</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.779054054054054</v>
+        <v>6.808917197452229</v>
       </c>
       <c r="HQ14" t="n">
-        <v>24.98886925795053</v>
+        <v>25.02590759075908</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2883165829145728</v>
+        <v>0.2887573964497042</v>
       </c>
       <c r="HS14" t="n">
         <v>6</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.01550387596899225</v>
+        <v>0.01438848920863309</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -7133,328 +7133,328 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>40920</v>
+        <v>43800</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>-115</v>
+        <v>-107</v>
       </c>
       <c r="J10" t="n">
-        <v>1363</v>
+        <v>1455</v>
       </c>
       <c r="K10" t="n">
-        <v>1370</v>
+        <v>1463</v>
       </c>
       <c r="L10" t="n">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="M10" t="n">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="N10" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="O10" t="n">
-        <v>2733</v>
+        <v>2918</v>
       </c>
       <c r="P10" t="n">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="Q10" t="n">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="R10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="S10" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="T10" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U10" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="V10" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="W10" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="X10" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Y10" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="Z10" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
         <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AF10" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="n">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK10" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AL10" t="n">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="AM10" t="n">
-        <v>688</v>
+        <v>736</v>
       </c>
       <c r="AN10" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="AO10" t="n">
-        <v>509</v>
+        <v>549</v>
       </c>
       <c r="AP10" t="n">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1515</v>
+        <v>1626</v>
       </c>
       <c r="AR10" t="n">
-        <v>1630</v>
+        <v>1733</v>
       </c>
       <c r="AS10" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="AT10" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="AW10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX10" t="n">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="AY10" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AZ10" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="BA10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BB10" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="BC10" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BD10" t="n">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="BE10" t="n">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="BF10" t="n">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="BG10" t="n">
-        <v>447</v>
+        <v>486</v>
       </c>
       <c r="BH10" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="BI10" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="BJ10" t="n">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="BK10" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="BL10" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="BM10" t="n">
         <v>3</v>
       </c>
       <c r="BN10" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="BO10" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="BP10" t="n">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="BQ10" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="BR10" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="BS10" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="BT10" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
         <v>16</v>
       </c>
       <c r="BV10" t="n">
-        <v>829</v>
+        <v>884</v>
       </c>
       <c r="BW10" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="BX10" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="BY10" t="n">
         <v>4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="CA10" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="CB10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CC10" t="n">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="CD10" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="CE10" t="n">
-        <v>681</v>
+        <v>728</v>
       </c>
       <c r="CF10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CG10" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="CH10" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="CI10" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="CJ10" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="CK10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CL10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="CM10" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="CN10" t="n">
         <v>12</v>
       </c>
       <c r="CO10" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="CP10" t="n">
         <v>7</v>
       </c>
       <c r="CQ10" t="n">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="CR10" t="n">
         <v>28</v>
       </c>
       <c r="CS10" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="CT10" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="CU10" t="n">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="CV10" t="n">
         <v>9</v>
       </c>
       <c r="CW10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="CX10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CY10" t="n">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="CZ10" t="n">
         <v>1</v>
       </c>
       <c r="DA10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DB10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DC10" t="n">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="DD10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="DE10" t="n">
         <v>5</v>
       </c>
       <c r="DF10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG10" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="DH10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DI10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="DJ10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="DK10" t="n">
         <v>6</v>
@@ -7463,7 +7463,7 @@
         <v>5</v>
       </c>
       <c r="DM10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
@@ -7475,10 +7475,10 @@
         <v>17</v>
       </c>
       <c r="DQ10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="DR10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DS10" t="n">
         <v>4</v>
@@ -7487,315 +7487,315 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>1301</v>
+        <v>1395</v>
       </c>
       <c r="DV10" t="n">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="DW10" t="n">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="DX10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="DY10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.532033426183844</v>
+        <v>0.5209424083769634</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5913312693498453</v>
+        <v>0.5835777126099707</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.8563218390804598</v>
+        <v>0.8481675392670157</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.3418467583497053</v>
+        <v>0.3479052823315119</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.2713178294573643</v>
+        <v>0.2627737226277372</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3418467583497053</v>
+        <v>0.3479052823315119</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.5218023255813954</v>
+        <v>0.5190217391304348</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.5188679245283019</v>
+        <v>0.5304347826086957</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.495049504950495</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.5179615705931495</v>
+        <v>0.5202334630350195</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.5306748466257669</v>
+        <v>0.5310734463276836</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.4607250755287009</v>
+        <v>0.4553314121037464</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.5637108792846498</v>
+        <v>0.5643254520166898</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.5815217391304348</v>
+        <v>0.5775</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5326633165829145</v>
+        <v>0.5253012048192771</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.4252297410192147</v>
+        <v>0.4272373540856031</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.005893909626719057</v>
+        <v>0.00546448087431694</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.08866279069767442</v>
+        <v>0.08967391304347826</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1205882352941176</v>
+        <v>0.1243243243243243</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06854838709677419</v>
+        <v>0.06563706563706563</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.03</v>
+        <v>0.02803738317757009</v>
       </c>
       <c r="EV10" t="inlineStr"/>
       <c r="EW10" t="n">
-        <v>0.602510460251046</v>
+        <v>0.6095617529880478</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.84</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.6820987654320988</v>
+        <v>0.6772334293948127</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.3536585365853658</v>
+        <v>0.3569405099150141</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.6892307692307692</v>
+        <v>0.6867816091954023</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2957317073170732</v>
+        <v>0.2934472934472934</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.6856702619414484</v>
+        <v>0.6820143884892086</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3246951219512195</v>
+        <v>0.3252840909090909</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.4661654135338346</v>
+        <v>0.4625850340136055</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2900763358778626</v>
+        <v>0.2898550724637681</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.25</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.3032786885245902</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.2755102040816326</v>
+        <v>0.2710280373831775</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.5876288659793815</v>
+        <v>0.5904761904761905</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.6901408450704225</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.6510638297872341</v>
+        <v>0.6456692913385826</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.05965463108320251</v>
       </c>
       <c r="FQ10" t="n">
-        <v>96.17595307917888</v>
+        <v>95.93424657534247</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.45</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="FS10" t="n">
-        <v>15.06250917094644</v>
+        <v>15.0992439862543</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.88306569343066</v>
+        <v>14.92180451127819</v>
       </c>
       <c r="FU10" t="n">
-        <v>14.41298606016141</v>
+        <v>14.46048109965636</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.22408759124088</v>
+        <v>14.23732057416268</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.2840434419381788</v>
+        <v>0.2879377431906615</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.6889632107023411</v>
+        <v>0.6851851851851852</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.5679611650485437</v>
+        <v>0.5540540540540541</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.2071846282372598</v>
+        <v>0.201556420233463</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.4717741935483871</v>
+        <v>0.4671814671814672</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.5064935064935064</v>
+        <v>0.5</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4957264957264957</v>
+        <v>0.4958677685950413</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0835421888053467</v>
+        <v>0.08326848249027237</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.36</v>
+        <v>0.3644859813084112</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.375</v>
       </c>
       <c r="GH10" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="GI10" t="n">
-        <v>0.12531328320802</v>
+        <v>0.1260700389105058</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.3466666666666667</v>
+        <v>0.3395061728395062</v>
       </c>
       <c r="GK10" t="n">
-        <v>0.3466666666666667</v>
+        <v>0.3395061728395062</v>
       </c>
       <c r="GL10" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.9636363636363636</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.2999164578111946</v>
+        <v>0.3011673151750973</v>
       </c>
       <c r="GN10" t="n">
-        <v>0.3398328690807799</v>
+        <v>0.3514211886304909</v>
       </c>
       <c r="GO10" t="n">
-        <v>0.3426966292134832</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="GP10" t="n">
-        <v>0.8114754098360656</v>
+        <v>0.8014705882352942</v>
       </c>
       <c r="GQ10" t="n">
-        <v>0.4662576687116564</v>
+        <v>0.4745762711864407</v>
       </c>
       <c r="GR10" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="GS10" t="n">
-        <v>0.1</v>
+        <v>0.08888888888888889</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.1042944785276074</v>
+        <v>0.1016949152542373</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="GV10" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="GW10" t="n">
-        <v>0.245398773006135</v>
+        <v>0.2485875706214689</v>
       </c>
       <c r="GX10" t="n">
-        <v>0.375</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="GY10" t="n">
         <v>0.8</v>
       </c>
       <c r="GZ10" t="n">
-        <v>0.2960725075528701</v>
+        <v>0.2939481268011527</v>
       </c>
       <c r="HA10" t="n">
-        <v>0.5918367346938775</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="HB10" t="n">
-        <v>0.1238670694864048</v>
+        <v>0.1296829971181556</v>
       </c>
       <c r="HC10" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.2658610271903323</v>
+        <v>0.2651296829971181</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.2840909090909091</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.7092731829573935</v>
+        <v>0.7151750972762646</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3398328690807799</v>
+        <v>0.3514211886304909</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.5412078925272881</v>
+        <v>0.5427612978889758</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.5290923809523809</v>
+        <v>0.5335943478260869</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.5285976923076923</v>
+        <v>0.5291774193548388</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.1089792785878741</v>
+        <v>0.1072961373390558</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.1694058154235145</v>
+        <v>0.1668639053254438</v>
       </c>
       <c r="HM10" t="n">
-        <v>0.015625</v>
+        <v>0.0162748643761302</v>
       </c>
       <c r="HN10" t="n">
-        <v>0.1412541254125413</v>
+        <v>0.1420664206642066</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.2798679867986799</v>
+        <v>0.2681426814268142</v>
       </c>
       <c r="HP10" t="n">
-        <v>6.422674418604651</v>
+        <v>6.394157608695653</v>
       </c>
       <c r="HQ10" t="n">
-        <v>25.58557312252964</v>
+        <v>25.56062271062271</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.2905355832721937</v>
+        <v>0.2831615120274914</v>
       </c>
       <c r="HS10" t="n">
         <v>3</v>
       </c>
       <c r="HT10" t="inlineStr"/>
       <c r="HU10" t="n">
-        <v>0.008356545961002786</v>
+        <v>0.007751937984496124</v>
       </c>
     </row>
     <row r="11">
@@ -9921,73 +9921,73 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>49560</v>
+        <v>52440</v>
       </c>
       <c r="H14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
-        <v>-177</v>
+        <v>-185</v>
       </c>
       <c r="J14" t="n">
-        <v>1690</v>
+        <v>1782</v>
       </c>
       <c r="K14" t="n">
-        <v>1706</v>
+        <v>1799</v>
       </c>
       <c r="L14" t="n">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="M14" t="n">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="N14" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="O14" t="n">
-        <v>3396</v>
+        <v>3581</v>
       </c>
       <c r="P14" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q14" t="n">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="R14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S14" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="T14" t="n">
         <v>73</v>
       </c>
       <c r="U14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V14" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="W14" t="n">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="X14" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="Y14" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="Z14" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AA14" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD14" t="n">
         <v>16</v>
@@ -9996,233 +9996,233 @@
         <v>47</v>
       </c>
       <c r="AF14" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="AG14" t="n">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="AJ14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AK14" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="AL14" t="n">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="AM14" t="n">
-        <v>942</v>
+        <v>990</v>
       </c>
       <c r="AN14" t="n">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="AO14" t="n">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="AP14" t="n">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1787</v>
+        <v>1890</v>
       </c>
       <c r="AR14" t="n">
-        <v>1964</v>
+        <v>2075</v>
       </c>
       <c r="AS14" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AT14" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AU14" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="AV14" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AW14" t="n">
         <v>61</v>
       </c>
       <c r="AX14" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AY14" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="AZ14" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="BA14" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="BB14" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="BC14" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="BD14" t="n">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="BE14" t="n">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="BF14" t="n">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="BG14" t="n">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="BH14" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="BI14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="BJ14" t="n">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="BK14" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="BL14" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BM14" t="n">
         <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="BO14" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="BP14" t="n">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="BQ14" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="BR14" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="BS14" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="BT14" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BU14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BV14" t="n">
-        <v>947</v>
+        <v>1004</v>
       </c>
       <c r="BW14" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="BX14" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="CA14" t="n">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="CB14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="CC14" t="n">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="CD14" t="n">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="CE14" t="n">
-        <v>851</v>
+        <v>902</v>
       </c>
       <c r="CF14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="CG14" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="CH14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="CI14" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="CJ14" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="CK14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="CL14" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="CM14" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="CN14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CO14" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="CR14" t="n">
         <v>29</v>
       </c>
       <c r="CS14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="CT14" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="CU14" t="n">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CX14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CY14" t="n">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="CZ14" t="n">
         <v>12</v>
       </c>
       <c r="DA14" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="DB14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="DC14" t="n">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="DD14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DE14" t="n">
         <v>1</v>
@@ -10231,16 +10231,16 @@
         <v>5</v>
       </c>
       <c r="DG14" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="DH14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DI14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="DJ14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="DK14" t="n">
         <v>6</v>
@@ -10249,7 +10249,7 @@
         <v>3</v>
       </c>
       <c r="DM14" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10261,10 +10261,10 @@
         <v>21</v>
       </c>
       <c r="DQ14" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="DR14" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="DS14" t="n">
         <v>2</v>
@@ -10273,317 +10273,317 @@
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1481</v>
+        <v>1564</v>
       </c>
       <c r="DV14" t="n">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="DW14" t="n">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="DX14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="DY14" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4954337899543379</v>
+        <v>0.4946004319654428</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5578406169665809</v>
+        <v>0.5558252427184466</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8592964824120602</v>
+        <v>0.8625592417061612</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3251633986928105</v>
+        <v>0.325115562403698</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.3882352941176471</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3212121212121212</v>
+        <v>0.3218390804597701</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.3251633986928105</v>
+        <v>0.325115562403698</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.464968152866242</v>
+        <v>0.4676767676767677</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.5984848484848485</v>
+        <v>0.6014492753623188</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4508196721311475</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.4739382239382239</v>
+        <v>0.475594874923734</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.5889423076923077</v>
+        <v>0.594170403587444</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.4633251833740831</v>
+        <v>0.4660421545667447</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5147143681477208</v>
+        <v>0.5161378555798687</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.6317829457364341</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5231388329979879</v>
+        <v>0.5251450676982592</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3938223938223938</v>
+        <v>0.3959731543624161</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01633986928104575</v>
+        <v>0.01540832049306626</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1263269639065817</v>
+        <v>0.1222222222222222</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1771300448430493</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.09971509971509972</v>
+        <v>0.09308510638297872</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.03448275862068965</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.02051282051282051</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6297872340425532</v>
+        <v>0.6305220883534136</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.9024390243902439</v>
+        <v>0.9069767441860465</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.119047619047619</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6616541353383458</v>
+        <v>0.6580188679245284</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3353413654618474</v>
+        <v>0.3378119001919386</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7195767195767195</v>
+        <v>0.7206982543640897</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.263681592039801</v>
+        <v>0.2682352941176471</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6898326898326899</v>
+        <v>0.6884848484848485</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.3033333333333333</v>
+        <v>0.306553911205074</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3969072164948453</v>
+        <v>0.3960396039603961</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3179723502304148</v>
+        <v>0.3231441048034934</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.2444444444444444</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2775800711743772</v>
+        <v>0.2866666666666667</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.231404958677686</v>
+        <v>0.224</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.5878787878787879</v>
+        <v>0.5865921787709497</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.6932515337423313</v>
+        <v>0.6941176470588235</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.7605633802816901</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7137254901960784</v>
+        <v>0.7137546468401487</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.7348484848484849</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03229974160206718</v>
+        <v>0.03300733496332518</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.67312348668281</v>
+        <v>98.33409610983982</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.6901408450704225</v>
+        <v>0.6973684210526315</v>
       </c>
       <c r="FS14" t="n">
-        <v>14.98260355029586</v>
+        <v>15.01762065095398</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.20832356389215</v>
+        <v>14.27381878821567</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.22585798816568</v>
+        <v>14.2446127946128</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.61846424384525</v>
+        <v>13.6899388549194</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.287001287001287</v>
+        <v>0.2800488102501525</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5605381165919282</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6811989100817438</v>
+        <v>0.6746031746031746</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.528</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2258687258687259</v>
+        <v>0.2294081757169006</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.3760683760683761</v>
+        <v>0.3856382978723404</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.4177215189873418</v>
+        <v>0.4252199413489736</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.4621212121212121</v>
+        <v>0.4620689655172414</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.09330759330759331</v>
+        <v>0.09456985967053082</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.3862068965517241</v>
+        <v>0.4064516129032258</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="GH14" t="n">
         <v>0.4285714285714285</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1254826254826255</v>
+        <v>0.1244661378889567</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3641025641025641</v>
+        <v>0.3676470588235294</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.3717277486910995</v>
+        <v>0.375</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.971830985915493</v>
+        <v>0.9733333333333334</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.2683397683397684</v>
+        <v>0.2715070164734594</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.3069544364508393</v>
+        <v>0.3056179775280899</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3114355231143552</v>
+        <v>0.3097949886104784</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.796875</v>
+        <v>0.8014705882352942</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4471153846153846</v>
+        <v>0.4349775784753363</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.6344086021505376</v>
+        <v>0.6391752577319587</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.2542372881355932</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.09615384615384616</v>
+        <v>0.09417040358744394</v>
       </c>
       <c r="GU14" t="n">
-        <v>0.5</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="GV14" t="n">
-        <v>0.9</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2869955156950673</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.3392857142857143</v>
+        <v>0.34375</v>
       </c>
       <c r="GY14" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3178484107579462</v>
+        <v>0.3067915690866511</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5615384615384615</v>
+        <v>0.5572519083969466</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1149144254278729</v>
+        <v>0.1100702576112412</v>
       </c>
       <c r="HC14" t="n">
         <v>0.3404255319148936</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.2885085574572127</v>
+        <v>0.297423887587822</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3135593220338983</v>
+        <v>0.3149606299212598</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6808236808236808</v>
+        <v>0.6760219646125687</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.3069544364508393</v>
+        <v>0.3056179775280899</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5467297026502909</v>
+        <v>0.544954018404908</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5523819727891156</v>
+        <v>0.5521885350318472</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5416579207920792</v>
+        <v>0.5383096428571429</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09571938168846611</v>
+        <v>0.09577464788732394</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1471415182755389</v>
+        <v>0.1470588235294118</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.006504065040650406</v>
+        <v>0.007656967840735069</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1712367095691102</v>
+        <v>0.1724867724867725</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2921096810296586</v>
+        <v>0.2883597883597884</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.808917197452229</v>
+        <v>6.899393939393939</v>
       </c>
       <c r="HQ14" t="n">
-        <v>25.02590759075908</v>
+        <v>25.03619344773791</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2887573964497042</v>
+        <v>0.2845117845117845</v>
       </c>
       <c r="HS14" t="n">
         <v>6</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.01438848920863309</v>
+        <v>0.01348314606741573</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -5751,310 +5751,310 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>40620</v>
+        <v>43500</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>-271</v>
+        <v>-281</v>
       </c>
       <c r="J8" t="n">
-        <v>1346</v>
+        <v>1445</v>
       </c>
       <c r="K8" t="n">
-        <v>1355</v>
+        <v>1455</v>
       </c>
       <c r="L8" t="n">
-        <v>406</v>
+        <v>457</v>
       </c>
       <c r="M8" t="n">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="N8" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="O8" t="n">
-        <v>2701</v>
+        <v>2900</v>
       </c>
       <c r="P8" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="Q8" t="n">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="R8" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="T8" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="U8" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="V8" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="W8" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="X8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y8" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Z8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AA8" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="AB8" t="n">
         <v>3</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="AF8" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="n">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="AH8" t="n">
         <v>10</v>
       </c>
       <c r="AI8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AJ8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="AL8" t="n">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="AM8" t="n">
-        <v>636</v>
+        <v>682</v>
       </c>
       <c r="AN8" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="AO8" t="n">
-        <v>520</v>
+        <v>563</v>
       </c>
       <c r="AP8" t="n">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1408</v>
+        <v>1503</v>
       </c>
       <c r="AR8" t="n">
-        <v>1679</v>
+        <v>1784</v>
       </c>
       <c r="AS8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AT8" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="AU8" t="n">
         <v>13</v>
       </c>
       <c r="AV8" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AW8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="AX8" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="AY8" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AZ8" t="n">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="BA8" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="BB8" t="n">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="BC8" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="BD8" t="n">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="BE8" t="n">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="BF8" t="n">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="BG8" t="n">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="BH8" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="BI8" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="BJ8" t="n">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="BK8" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="BL8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="BM8" t="n">
         <v>6</v>
       </c>
       <c r="BN8" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="BO8" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="BP8" t="n">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="BQ8" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="BR8" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="BS8" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="BT8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BU8" t="n">
         <v>14</v>
       </c>
       <c r="BV8" t="n">
-        <v>724</v>
+        <v>766</v>
       </c>
       <c r="BW8" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="BX8" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="BY8" t="n">
         <v>3</v>
       </c>
       <c r="BZ8" t="n">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="CA8" t="n">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="CB8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CC8" t="n">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="CD8" t="n">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="CE8" t="n">
-        <v>588</v>
+        <v>645</v>
       </c>
       <c r="CF8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CG8" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="CH8" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="CI8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CJ8" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="CK8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CL8" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="CM8" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="CN8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CO8" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="CP8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CQ8" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="CR8" t="n">
         <v>20</v>
       </c>
       <c r="CS8" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="CT8" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="CU8" t="n">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="CV8" t="n">
         <v>4</v>
       </c>
       <c r="CW8" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="CX8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CY8" t="n">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="CZ8" t="n">
         <v>3</v>
       </c>
       <c r="DA8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DB8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DC8" t="n">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="DD8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DE8" t="n">
         <v>2</v>
@@ -6063,25 +6063,25 @@
         <v>5</v>
       </c>
       <c r="DG8" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="DH8" t="n">
         <v>7</v>
       </c>
       <c r="DI8" t="n">
+        <v>42</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>56</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>5</v>
+      </c>
+      <c r="DM8" t="n">
         <v>39</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>54</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>4</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>3</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>37</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
@@ -6093,329 +6093,329 @@
         <v>16</v>
       </c>
       <c r="DQ8" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="DR8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="DS8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DT8" t="n">
         <v>2</v>
       </c>
       <c r="DU8" t="n">
-        <v>1238</v>
+        <v>1319</v>
       </c>
       <c r="DV8" t="n">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="DW8" t="n">
-        <v>405</v>
+        <v>456</v>
       </c>
       <c r="DX8" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="DY8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.4739884393063584</v>
+        <v>0.4632152588555858</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.5273311897106109</v>
+        <v>0.5182926829268293</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.8407643312101911</v>
+        <v>0.8452380952380952</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.3019230769230769</v>
+        <v>0.2984014209591474</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.2767295597484277</v>
+        <v>0.287292817679558</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.3019230769230769</v>
+        <v>0.2984014209591474</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.5440251572327044</v>
+        <v>0.5381231671554252</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.5795454545454546</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.5133689839572193</v>
+        <v>0.5095238095238095</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.5030276816608996</v>
+        <v>0.4971887550200803</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5471014492753623</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.4682080924855491</v>
+        <v>0.4731457800511509</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.5379310344827586</v>
+        <v>0.533072546230441</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.5787671232876712</v>
+        <v>0.5648148148148148</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.5097323600973236</v>
+        <v>0.5119305856832972</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.4498269896193772</v>
+        <v>0.4522088353413655</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.01153846153846154</v>
+        <v>0.01065719360568384</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.08176100628930817</v>
+        <v>0.08211143695014662</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.08181818181818182</v>
+        <v>0.07932011331444759</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.09865470852017937</v>
+        <v>0.1024590163934426</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.03614457831325301</v>
+        <v>0.03529411764705882</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01470588235294118</v>
+        <v>0.01333333333333333</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.586046511627907</v>
+        <v>0.5877192982456141</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.8043478260869565</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.06521739130434782</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.608843537414966</v>
+        <v>0.6265432098765432</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.2951388888888889</v>
+        <v>0.2971246006389776</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.7163636363636363</v>
+        <v>0.707641196013289</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.2450704225352113</v>
+        <v>0.2461139896373057</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.6608084358523726</v>
+        <v>0.6656</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.2674961119751166</v>
+        <v>0.2689556509298999</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.3592233009708738</v>
+        <v>0.3603603603603603</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.2481751824817518</v>
+        <v>0.2549019607843137</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.2379182156133829</v>
+        <v>0.2397260273972603</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.2674418604651163</v>
+        <v>0.2659574468085106</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.5572519083969466</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.6504065040650406</v>
+        <v>0.6518518518518519</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.65</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.7474747474747475</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.02559726962457338</v>
+        <v>0.02664576802507837</v>
       </c>
       <c r="FQ8" t="n">
-        <v>95.75184638109306</v>
+        <v>96</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.6379310344827587</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="FS8" t="n">
-        <v>14.39598811292719</v>
+        <v>14.30228373702422</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.67749077490775</v>
+        <v>15.69292096219931</v>
       </c>
       <c r="FU8" t="n">
-        <v>13.84821693907875</v>
+        <v>13.75328719723183</v>
       </c>
       <c r="FV8" t="n">
-        <v>14.99889298892989</v>
+        <v>15.03147766323024</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.2854671280276816</v>
+        <v>0.2835341365461848</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.6878787878787879</v>
+        <v>0.6855524079320113</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.7491749174917491</v>
+        <v>0.7446153846153846</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.5462555066079295</v>
+        <v>0.5289256198347108</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1929065743944637</v>
+        <v>0.1959839357429719</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.3766816143497758</v>
+        <v>0.3647540983606558</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.417910447761194</v>
+        <v>0.4063926940639269</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.3146067415730337</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.07179930795847751</v>
+        <v>0.06827309236947791</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.4216867469879518</v>
+        <v>0.4235294117647059</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.4375</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.4</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1204819277108434</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.3676470588235294</v>
+        <v>0.3733333333333334</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.373134328358209</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="GL8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="GM8" t="n">
-        <v>0.3321799307958477</v>
+        <v>0.3317269076305221</v>
       </c>
       <c r="GN8" t="n">
-        <v>0.2786458333333333</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.281578947368421</v>
+        <v>0.273838630806846</v>
       </c>
       <c r="GP8" t="n">
-        <v>0.794392523364486</v>
+        <v>0.7946428571428571</v>
       </c>
       <c r="GQ8" t="n">
-        <v>0.48</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="GR8" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="GS8" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.1956521739130435</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.08</v>
+        <v>0.07971014492753623</v>
       </c>
       <c r="GU8" t="n">
-        <v>0.3</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="GV8" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="GW8" t="n">
-        <v>0.216</v>
+        <v>0.2246376811594203</v>
       </c>
       <c r="GX8" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="GY8" t="n">
         <v>0.9</v>
       </c>
       <c r="GZ8" t="n">
-        <v>0.2861271676300578</v>
+        <v>0.2787723785166241</v>
       </c>
       <c r="HA8" t="n">
-        <v>0.6262626262626263</v>
+        <v>0.6422018348623854</v>
       </c>
       <c r="HB8" t="n">
-        <v>0.08092485549132948</v>
+        <v>0.09462915601023018</v>
       </c>
       <c r="HC8" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.3786127167630058</v>
+        <v>0.3682864450127877</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2748091603053435</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.7357429718875502</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.2786458333333333</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.5540986510008703</v>
+        <v>0.553350605815832</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.5413662337662338</v>
+        <v>0.547697619047619</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.5415969117647059</v>
+        <v>0.5417277922077922</v>
       </c>
       <c r="HK8" t="n">
-        <v>0.1090047393364929</v>
+        <v>0.1092375366568915</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.1767881241565452</v>
+        <v>0.178391959798995</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.01232394366197183</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.1207386363636364</v>
+        <v>0.1224218230206254</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.2997159090909091</v>
+        <v>0.3160345974717232</v>
       </c>
       <c r="HP8" t="n">
-        <v>6.104245283018868</v>
+        <v>6.078299120234604</v>
       </c>
       <c r="HQ8" t="n">
-        <v>25.34330097087378</v>
+        <v>25.35125448028674</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.3016344725111441</v>
+        <v>0.3162629757785467</v>
       </c>
       <c r="HS8" t="n">
         <v>3</v>
       </c>
       <c r="HT8" t="inlineStr"/>
       <c r="HU8" t="n">
-        <v>0.01041666666666667</v>
+        <v>0.009685230024213076</v>
       </c>
     </row>
     <row r="9">
@@ -9921,85 +9921,85 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>52440</v>
+        <v>55320</v>
       </c>
       <c r="H14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-175</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1881</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1899</v>
+      </c>
+      <c r="L14" t="n">
+        <v>529</v>
+      </c>
+      <c r="M14" t="n">
+        <v>681</v>
+      </c>
+      <c r="N14" t="n">
+        <v>278</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3780</v>
+      </c>
+      <c r="P14" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>488</v>
+      </c>
+      <c r="R14" t="n">
+        <v>68</v>
+      </c>
+      <c r="S14" t="n">
+        <v>107</v>
+      </c>
+      <c r="T14" t="n">
+        <v>77</v>
+      </c>
+      <c r="U14" t="n">
+        <v>136</v>
+      </c>
+      <c r="V14" t="n">
+        <v>151</v>
+      </c>
+      <c r="W14" t="n">
+        <v>394</v>
+      </c>
+      <c r="X14" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>166</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>83</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>217</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD14" t="n">
         <v>18</v>
       </c>
-      <c r="I14" t="n">
-        <v>-185</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1782</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1799</v>
-      </c>
-      <c r="L14" t="n">
-        <v>507</v>
-      </c>
-      <c r="M14" t="n">
-        <v>629</v>
-      </c>
-      <c r="N14" t="n">
-        <v>262</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3581</v>
-      </c>
-      <c r="P14" t="n">
-        <v>255</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>459</v>
-      </c>
-      <c r="R14" t="n">
-        <v>62</v>
-      </c>
-      <c r="S14" t="n">
-        <v>97</v>
-      </c>
-      <c r="T14" t="n">
-        <v>73</v>
-      </c>
-      <c r="U14" t="n">
-        <v>131</v>
-      </c>
-      <c r="V14" t="n">
-        <v>145</v>
-      </c>
-      <c r="W14" t="n">
-        <v>376</v>
-      </c>
-      <c r="X14" t="n">
-        <v>63</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>155</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>204</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>16</v>
-      </c>
       <c r="AE14" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF14" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AG14" t="n">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="AH14" t="n">
         <v>22</v>
@@ -10011,218 +10011,218 @@
         <v>40</v>
       </c>
       <c r="AK14" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="AL14" t="n">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="AM14" t="n">
-        <v>990</v>
+        <v>1048</v>
       </c>
       <c r="AN14" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="AO14" t="n">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="AP14" t="n">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1890</v>
+        <v>1995</v>
       </c>
       <c r="AR14" t="n">
-        <v>2075</v>
+        <v>2170</v>
       </c>
       <c r="AS14" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="AT14" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="AU14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AV14" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW14" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AX14" t="n">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="AY14" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="AZ14" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="BA14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="BB14" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="BC14" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="BD14" t="n">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="BE14" t="n">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="BF14" t="n">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="BG14" t="n">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="BH14" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="BI14" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="BJ14" t="n">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="BK14" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BL14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN14" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="BO14" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="BP14" t="n">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="BQ14" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="BR14" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="BS14" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="BT14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BU14" t="n">
         <v>27</v>
       </c>
       <c r="BV14" t="n">
-        <v>1004</v>
+        <v>1054</v>
       </c>
       <c r="BW14" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="BX14" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="CA14" t="n">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="CB14" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="CC14" t="n">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="CD14" t="n">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="CE14" t="n">
-        <v>902</v>
+        <v>961</v>
       </c>
       <c r="CF14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CG14" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="CH14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="CI14" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="CJ14" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="CK14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="CL14" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="CM14" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="CN14" t="n">
         <v>15</v>
       </c>
       <c r="CO14" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="CR14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CS14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="CT14" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="CU14" t="n">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CX14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CY14" t="n">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="CZ14" t="n">
         <v>12</v>
       </c>
       <c r="DA14" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="DB14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DC14" t="n">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="DD14" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="DE14" t="n">
         <v>1</v>
@@ -10231,16 +10231,16 @@
         <v>5</v>
       </c>
       <c r="DG14" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="DH14" t="n">
         <v>5</v>
       </c>
       <c r="DI14" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="DJ14" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DK14" t="n">
         <v>6</v>
@@ -10249,7 +10249,7 @@
         <v>3</v>
       </c>
       <c r="DM14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10258,13 +10258,13 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="DQ14" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="DR14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="DS14" t="n">
         <v>2</v>
@@ -10273,247 +10273,247 @@
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1564</v>
+        <v>1646</v>
       </c>
       <c r="DV14" t="n">
-        <v>545</v>
+        <v>573</v>
       </c>
       <c r="DW14" t="n">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="DX14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="DY14" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4946004319654428</v>
+        <v>0.4867617107942974</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5558252427184466</v>
+        <v>0.5481651376146789</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8625592417061612</v>
+        <v>0.8648648648648649</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.325115562403698</v>
+        <v>0.3236151603498542</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.3882352941176471</v>
+        <v>0.4022988505747127</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3218390804597701</v>
+        <v>0.3169398907103825</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.325115562403698</v>
+        <v>0.3236151603498542</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4676767676767677</v>
+        <v>0.4685114503816794</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.6014492753623188</v>
+        <v>0.6040268456375839</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4638783269961977</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.475594874923734</v>
+        <v>0.47520184544406</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.594170403587444</v>
+        <v>0.6038135593220338</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.4660421545667447</v>
+        <v>0.468609865470852</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5161378555798687</v>
+        <v>0.5157949249093734</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.6317829457364341</v>
+        <v>0.6415441176470589</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5251450676982592</v>
+        <v>0.5305555555555556</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3959731543624161</v>
+        <v>0.3956170703575548</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01540832049306626</v>
+        <v>0.01749271137026239</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1222222222222222</v>
+        <v>0.1173664122137405</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1700819672131147</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.09308510638297872</v>
+        <v>0.08883248730964467</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.03012048192771084</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.0184331797235023</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6305220883534136</v>
+        <v>0.624031007751938</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.9069767441860465</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6580188679245284</v>
+        <v>0.6592427616926503</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3378119001919386</v>
+        <v>0.3303085299455535</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7206982543640897</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2682352941176471</v>
+        <v>0.2749445676274945</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6884848484848485</v>
+        <v>0.6901248581157775</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.306553911205074</v>
+        <v>0.3053892215568862</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3960396039603961</v>
+        <v>0.3867924528301887</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3231441048034934</v>
+        <v>0.3236514522821577</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2244897959183673</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2866666666666667</v>
+        <v>0.2990654205607476</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.224</v>
+        <v>0.2153846153846154</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.5865921787709497</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.6941176470588235</v>
+        <v>0.6935483870967742</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7137546468401487</v>
+        <v>0.7157534246575342</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7348484848484849</v>
+        <v>0.7357142857142858</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03300733496332518</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.33409610983982</v>
+        <v>98.39479392624729</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.6973684210526315</v>
+        <v>0.675</v>
       </c>
       <c r="FS14" t="n">
-        <v>15.01762065095398</v>
+        <v>15.07262094630516</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.27381878821567</v>
+        <v>14.2013691416535</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.2446127946128</v>
+        <v>14.31749069643806</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.6899388549194</v>
+        <v>13.6187467087941</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2800488102501525</v>
+        <v>0.2814302191464821</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5614754098360656</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6746031746031746</v>
+        <v>0.6765432098765433</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5218978102189781</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2294081757169006</v>
+        <v>0.2272202998846597</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.3856382978723404</v>
+        <v>0.383248730964467</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.4252199413489736</v>
+        <v>0.4206128133704735</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.4620689655172414</v>
+        <v>0.456953642384106</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.09456985967053082</v>
+        <v>0.09573241061130335</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.4064516129032258</v>
+        <v>0.3975903614457831</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.42</v>
+        <v>0.4099378881987578</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1244661378889567</v>
+        <v>0.1251441753171857</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3676470588235294</v>
+        <v>0.3824884792626728</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.375</v>
+        <v>0.3896713615023474</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.963855421686747</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.2715070164734594</v>
+        <v>0.2704728950403691</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.3056179775280899</v>
+        <v>0.2963752665245202</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3097949886104784</v>
+        <v>0.3015184381778742</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.8014705882352942</v>
+        <v>0.8057553956834532</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4349775784753363</v>
+        <v>0.4533898305084746</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.6391752577319587</v>
+        <v>0.6355140186915887</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.25</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.09417040358744394</v>
+        <v>0.09745762711864407</v>
       </c>
       <c r="GU14" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="GV14" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2869955156950673</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="GX14" t="n">
         <v>0.34375</v>
@@ -10522,68 +10522,68 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3067915690866511</v>
+        <v>0.304932735426009</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5572519083969466</v>
+        <v>0.5661764705882353</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1100702576112412</v>
+        <v>0.1098654708520179</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.3404255319148936</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.297423887587822</v>
+        <v>0.3004484304932735</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3149606299212598</v>
+        <v>0.2985074626865671</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6760219646125687</v>
+        <v>0.6770472895040369</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.3056179775280899</v>
+        <v>0.2963752665245202</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.544954018404908</v>
+        <v>0.5439556554524362</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5521885350318472</v>
+        <v>0.5534698170731707</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5383096428571429</v>
+        <v>0.5386813926940639</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09577464788732394</v>
+        <v>0.09445037353255069</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1470588235294118</v>
+        <v>0.1452702702702703</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.007656967840735069</v>
+        <v>0.007246376811594203</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1724867724867725</v>
+        <v>0.174937343358396</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2883597883597884</v>
+        <v>0.2882205513784461</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.899393939393939</v>
+        <v>6.882347328244275</v>
       </c>
       <c r="HQ14" t="n">
-        <v>25.03619344773791</v>
+        <v>25.05598227474151</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2845117845117845</v>
+        <v>0.2812333864965444</v>
       </c>
       <c r="HS14" t="n">
         <v>6</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.01348314606741573</v>
+        <v>0.01705756929637527</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -5751,67 +5751,67 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>43500</v>
+        <v>46380</v>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>-281</v>
+        <v>-282</v>
       </c>
       <c r="J8" t="n">
-        <v>1445</v>
+        <v>1541</v>
       </c>
       <c r="K8" t="n">
-        <v>1455</v>
+        <v>1553</v>
       </c>
       <c r="L8" t="n">
-        <v>457</v>
+        <v>498</v>
       </c>
       <c r="M8" t="n">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="N8" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="O8" t="n">
-        <v>2900</v>
+        <v>3094</v>
       </c>
       <c r="P8" t="n">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="Q8" t="n">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S8" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="T8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="V8" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="W8" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="X8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Z8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AA8" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="AB8" t="n">
         <v>3</v>
@@ -5823,256 +5823,256 @@
         <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF8" t="n">
+        <v>121</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>436</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>154</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>393</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>731</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>179</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>593</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>284</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1607</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1889</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>58</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>43</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>194</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>230</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>56</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>193</v>
+      </c>
+      <c r="BC8" t="n">
         <v>112</v>
       </c>
-      <c r="AG8" t="n">
-        <v>413</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>31</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>144</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>367</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>682</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>168</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>563</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>265</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1503</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1784</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>56</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>96</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>33</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>184</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>107</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>210</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>52</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>181</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>105</v>
-      </c>
       <c r="BD8" t="n">
-        <v>475</v>
+        <v>520</v>
       </c>
       <c r="BE8" t="n">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="BF8" t="n">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="BG8" t="n">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="BH8" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="BI8" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="BK8" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="BL8" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="BM8" t="n">
         <v>6</v>
       </c>
       <c r="BN8" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="BO8" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="BP8" t="n">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="BQ8" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="BR8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BS8" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="BT8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BU8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BV8" t="n">
-        <v>766</v>
+        <v>818</v>
       </c>
       <c r="BW8" t="n">
+        <v>99</v>
+      </c>
+      <c r="BX8" t="n">
         <v>95</v>
       </c>
-      <c r="BX8" t="n">
-        <v>93</v>
-      </c>
       <c r="BY8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="CA8" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="CB8" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="CC8" t="n">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="CD8" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="CE8" t="n">
-        <v>645</v>
+        <v>690</v>
       </c>
       <c r="CF8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CG8" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="CH8" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="CI8" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="CJ8" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="CK8" t="n">
         <v>22</v>
       </c>
       <c r="CL8" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="CM8" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="CN8" t="n">
         <v>20</v>
       </c>
       <c r="CO8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="CP8" t="n">
         <v>6</v>
       </c>
       <c r="CQ8" t="n">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="CR8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CS8" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="CT8" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="CU8" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="CV8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CW8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CX8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CY8" t="n">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="CZ8" t="n">
         <v>3</v>
       </c>
       <c r="DA8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="DB8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DC8" t="n">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="DD8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="DE8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DF8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DG8" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="DH8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DI8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="DJ8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="DK8" t="n">
         <v>6</v>
@@ -6081,7 +6081,7 @@
         <v>5</v>
       </c>
       <c r="DM8" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
@@ -6090,13 +6090,13 @@
         <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="DQ8" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="DR8" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="DS8" t="n">
         <v>2</v>
@@ -6105,238 +6105,238 @@
         <v>2</v>
       </c>
       <c r="DU8" t="n">
-        <v>1319</v>
+        <v>1413</v>
       </c>
       <c r="DV8" t="n">
-        <v>475</v>
+        <v>520</v>
       </c>
       <c r="DW8" t="n">
-        <v>456</v>
+        <v>497</v>
       </c>
       <c r="DX8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="DY8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.4632152588555858</v>
+        <v>0.4681933842239186</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.5182926829268293</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.8452380952380952</v>
+        <v>0.8379888268156425</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.2984014209591474</v>
+        <v>0.3018549747048904</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.287292817679558</v>
+        <v>0.2901554404145077</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.2984014209591474</v>
+        <v>0.3018549747048904</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.5381231671554252</v>
+        <v>0.5376196990424077</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.58</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.5095238095238095</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.4971887550200803</v>
+        <v>0.4996223564954683</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.5471014492753623</v>
+        <v>0.5524475524475524</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.4731457800511509</v>
+        <v>0.4822695035460993</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.533072546230441</v>
+        <v>0.535427807486631</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.5648148148148148</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.5119305856832972</v>
+        <v>0.5201207243460765</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.4522088353413655</v>
+        <v>0.4478851963746224</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.01065719360568384</v>
+        <v>0.01011804384485666</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.08211143695014662</v>
+        <v>0.08481532147742818</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.07932011331444759</v>
+        <v>0.08311688311688312</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.1024590163934426</v>
+        <v>0.10546875</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.03529411764705882</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.01273885350318471</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.5877192982456141</v>
+        <v>0.5942622950819673</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.82</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.06122448979591837</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.6265432098765432</v>
+        <v>0.6260623229461756</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.2971246006389776</v>
+        <v>0.2844311377245509</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.707641196013289</v>
+        <v>0.7098765432098766</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.2461139896373057</v>
+        <v>0.245049504950495</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.6656</v>
+        <v>0.6661742983751846</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.2689556509298999</v>
+        <v>0.2628726287262872</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.3603603603603603</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.2549019607843137</v>
+        <v>0.24375</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2745098039215687</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.2397260273972603</v>
+        <v>0.239344262295082</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.2659574468085106</v>
+        <v>0.2626262626262627</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.574468085106383</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.6518518518518519</v>
+        <v>0.6438356164383562</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.726027397260274</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6555555555555556</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.02664576802507837</v>
+        <v>0.02831594634873323</v>
       </c>
       <c r="FQ8" t="n">
-        <v>96</v>
+        <v>96.0620957309185</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.5942028985507246</v>
       </c>
       <c r="FS8" t="n">
-        <v>14.30228373702422</v>
+        <v>14.25405580791694</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.69292096219931</v>
+        <v>15.72086284610431</v>
       </c>
       <c r="FU8" t="n">
-        <v>13.75328719723183</v>
+        <v>13.71979234263465</v>
       </c>
       <c r="FV8" t="n">
-        <v>15.03147766323024</v>
+        <v>15.06226658081133</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.2835341365461848</v>
+        <v>0.290785498489426</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.6855524079320113</v>
+        <v>0.6805194805194805</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.7446153846153846</v>
+        <v>0.7422096317280453</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.5289256198347108</v>
+        <v>0.5343511450381679</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1959839357429719</v>
+        <v>0.1933534743202417</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.3647540983606558</v>
+        <v>0.36328125</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.4063926940639269</v>
+        <v>0.4061135371179039</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.3146067415730337</v>
+        <v>0.3118279569892473</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.06827309236947791</v>
+        <v>0.06797583081570997</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.4235294117647059</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4367816091954023</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.1204819277108434</v>
+        <v>0.1185800604229607</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.3733333333333334</v>
+        <v>0.3694267515923567</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.3783783783783784</v>
+        <v>0.3741935483870968</v>
       </c>
       <c r="GL8" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="GM8" t="n">
-        <v>0.3317269076305221</v>
+        <v>0.3293051359516616</v>
       </c>
       <c r="GN8" t="n">
-        <v>0.2711864406779661</v>
+        <v>0.2775229357798165</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.273838630806846</v>
+        <v>0.2800925925925926</v>
       </c>
       <c r="GP8" t="n">
-        <v>0.7946428571428571</v>
+        <v>0.7933884297520661</v>
       </c>
       <c r="GQ8" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.4825174825174825</v>
       </c>
       <c r="GR8" t="n">
-        <v>0.696969696969697</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="GS8" t="n">
-        <v>0.1956521739130435</v>
+        <v>0.1875</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.07971014492753623</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="GU8" t="n">
         <v>0.2727272727272727</v>
@@ -6345,77 +6345,77 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="GW8" t="n">
-        <v>0.2246376811594203</v>
+        <v>0.2237762237762238</v>
       </c>
       <c r="GX8" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.34375</v>
       </c>
       <c r="GY8" t="n">
-        <v>0.9</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="GZ8" t="n">
-        <v>0.2787723785166241</v>
+        <v>0.2884160756501182</v>
       </c>
       <c r="HA8" t="n">
-        <v>0.6422018348623854</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="HB8" t="n">
-        <v>0.09462915601023018</v>
+        <v>0.09219858156028368</v>
       </c>
       <c r="HC8" t="n">
-        <v>0.3783783783783784</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.3682864450127877</v>
+        <v>0.3640661938534279</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2638888888888889</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.7357429718875502</v>
+        <v>0.7386706948640483</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.2711864406779661</v>
+        <v>0.2775229357798165</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.553350605815832</v>
+        <v>0.5549758358662614</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.547697619047619</v>
+        <v>0.5489912790697674</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.5417277922077922</v>
+        <v>0.5434645432692308</v>
       </c>
       <c r="HK8" t="n">
-        <v>0.1092375366568915</v>
+        <v>0.1115702479338843</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.178391959798995</v>
+        <v>0.180327868852459</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.01232394366197183</v>
+        <v>0.01337792642140468</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.1224218230206254</v>
+        <v>0.1207218419415059</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.3160345974717232</v>
+        <v>0.3235843186060983</v>
       </c>
       <c r="HP8" t="n">
-        <v>6.078299120234604</v>
+        <v>5.979753761969904</v>
       </c>
       <c r="HQ8" t="n">
-        <v>25.35125448028674</v>
+        <v>25.3298126064736</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.3162629757785467</v>
+        <v>0.3231667748215444</v>
       </c>
       <c r="HS8" t="n">
         <v>3</v>
       </c>
       <c r="HT8" t="inlineStr"/>
       <c r="HU8" t="n">
-        <v>0.009685230024213076</v>
+        <v>0.009174311926605505</v>
       </c>
     </row>
     <row r="9">
@@ -9921,67 +9921,67 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>55320</v>
+        <v>58200</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I14" t="n">
-        <v>-175</v>
+        <v>-174</v>
       </c>
       <c r="J14" t="n">
-        <v>1881</v>
+        <v>1978</v>
       </c>
       <c r="K14" t="n">
-        <v>1899</v>
+        <v>1996</v>
       </c>
       <c r="L14" t="n">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="M14" t="n">
-        <v>681</v>
+        <v>723</v>
       </c>
       <c r="N14" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="O14" t="n">
-        <v>3780</v>
+        <v>3974</v>
       </c>
       <c r="P14" t="n">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="Q14" t="n">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="R14" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="S14" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="T14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="V14" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="W14" t="n">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="X14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="AA14" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="AB14" t="n">
         <v>13</v>
@@ -9990,236 +9990,236 @@
         <v>23</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF14" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="AG14" t="n">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AJ14" t="n">
         <v>40</v>
       </c>
       <c r="AK14" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AL14" t="n">
-        <v>491</v>
+        <v>513</v>
       </c>
       <c r="AM14" t="n">
-        <v>1048</v>
+        <v>1099</v>
       </c>
       <c r="AN14" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="AO14" t="n">
-        <v>686</v>
+        <v>724</v>
       </c>
       <c r="AP14" t="n">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1995</v>
+        <v>2100</v>
       </c>
       <c r="AR14" t="n">
-        <v>2170</v>
+        <v>2274</v>
       </c>
       <c r="AS14" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AT14" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="AU14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AV14" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AW14" t="n">
         <v>64</v>
       </c>
       <c r="AX14" t="n">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="AY14" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AZ14" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="BA14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BB14" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="BC14" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="BD14" t="n">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="BE14" t="n">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="BF14" t="n">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="BG14" t="n">
-        <v>576</v>
+        <v>618</v>
       </c>
       <c r="BH14" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="BI14" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BJ14" t="n">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="BK14" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="BL14" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="BM14" t="n">
         <v>12</v>
       </c>
       <c r="BN14" t="n">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="BO14" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="BP14" t="n">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="BQ14" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="BR14" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="BS14" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="BT14" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="BU14" t="n">
         <v>27</v>
       </c>
       <c r="BV14" t="n">
-        <v>1054</v>
+        <v>1126</v>
       </c>
       <c r="BW14" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BX14" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="CA14" t="n">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="CB14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CC14" t="n">
-        <v>650</v>
+        <v>685</v>
       </c>
       <c r="CD14" t="n">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="CE14" t="n">
-        <v>961</v>
+        <v>1013</v>
       </c>
       <c r="CF14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CG14" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="CH14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="CI14" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="CJ14" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="CK14" t="n">
         <v>30</v>
       </c>
       <c r="CL14" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="CM14" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="CN14" t="n">
         <v>15</v>
       </c>
       <c r="CO14" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="CR14" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="CS14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="CT14" t="n">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="CU14" t="n">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
+        <v>39</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>19</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>442</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB14" t="n">
         <v>37</v>
       </c>
-      <c r="CX14" t="n">
-        <v>18</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>422</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>12</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>53</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>35</v>
-      </c>
       <c r="DC14" t="n">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="DD14" t="n">
         <v>36</v>
@@ -10231,16 +10231,16 @@
         <v>5</v>
       </c>
       <c r="DG14" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="DH14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="DI14" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="DJ14" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="DK14" t="n">
         <v>6</v>
@@ -10249,7 +10249,7 @@
         <v>3</v>
       </c>
       <c r="DM14" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10258,253 +10258,253 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="DQ14" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="DR14" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="DS14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DT14" t="n">
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1646</v>
+        <v>1737</v>
       </c>
       <c r="DV14" t="n">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="DW14" t="n">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="DX14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="DY14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4867617107942974</v>
+        <v>0.4951267056530214</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5481651376146789</v>
+        <v>0.5557986870897156</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.869198312236287</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3236151603498542</v>
+        <v>0.3273480662983426</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.4022988505747127</v>
+        <v>0.4065934065934066</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3169398907103825</v>
+        <v>0.3189189189189189</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.3236151603498542</v>
+        <v>0.3273480662983426</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4685114503816794</v>
+        <v>0.4667879890809827</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.6040268456375839</v>
+        <v>0.6025641025641025</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4638783269961977</v>
+        <v>0.4612546125461255</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.47520184544406</v>
+        <v>0.4764125068568294</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.6038135593220338</v>
+        <v>0.6052631578947368</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.468609865470852</v>
+        <v>0.4682017543859649</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5157949249093734</v>
+        <v>0.5167570231641203</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.6415441176470589</v>
+        <v>0.6413427561837456</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5305555555555556</v>
+        <v>0.5288808664259927</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3956170703575548</v>
+        <v>0.3971475589687329</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01749271137026239</v>
+        <v>0.01657458563535912</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1173664122137405</v>
+        <v>0.1182893539581438</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1700819672131147</v>
+        <v>0.1695906432748538</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.08883248730964467</v>
+        <v>0.09223300970873786</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.03012048192771084</v>
+        <v>0.02873563218390805</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0184331797235023</v>
+        <v>0.01724137931034483</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.624031007751938</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.8979591836734694</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1041666666666667</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6592427616926503</v>
+        <v>0.6702127659574468</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3303085299455535</v>
+        <v>0.3327586206896552</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7244444444444444</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2749445676274945</v>
+        <v>0.2742616033755274</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6901248581157775</v>
+        <v>0.6967391304347826</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.3053892215568862</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3867924528301887</v>
+        <v>0.3856502242152466</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3236514522821577</v>
+        <v>0.3293650793650794</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2244897959183673</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2990654205607476</v>
+        <v>0.2946428571428572</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.2153846153846154</v>
+        <v>0.2246376811594203</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.6030150753768844</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.6935483870967742</v>
+        <v>0.7046632124352331</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.75</v>
+        <v>0.7564102564102564</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7157534246575342</v>
+        <v>0.7180327868852459</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7357142857142858</v>
+        <v>0.7379310344827587</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03497267759562842</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.39479392624729</v>
+        <v>98.32577319587629</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.675</v>
+        <v>0.6976744186046512</v>
       </c>
       <c r="FS14" t="n">
-        <v>15.07262094630516</v>
+        <v>15.13291203235592</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.2013691416535</v>
+        <v>14.16187374749499</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.31749069643806</v>
+        <v>14.38427704752275</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.6187467087941</v>
+        <v>13.59253507014028</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2814302191464821</v>
+        <v>0.2814042786615469</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5614754098360656</v>
+        <v>0.5614035087719298</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6765432098765433</v>
+        <v>0.676056338028169</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.5218978102189781</v>
+        <v>0.53125</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2272202998846597</v>
+        <v>0.2260010970927043</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.383248730964467</v>
+        <v>0.383495145631068</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.4206128133704735</v>
+        <v>0.4224598930481284</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.456953642384106</v>
+        <v>0.4683544303797468</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.09573241061130335</v>
+        <v>0.09544706527701591</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.3975903614457831</v>
+        <v>0.3850574712643678</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.4099378881987578</v>
+        <v>0.3964497041420119</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4029850746268657</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1251441753171857</v>
+        <v>0.1272627537026879</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3824884792626728</v>
+        <v>0.3879310344827586</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.3896713615023474</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.963855421686747</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.2704728950403691</v>
+        <v>0.269884805266045</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.2963752665245202</v>
+        <v>0.298780487804878</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3015184381778742</v>
+        <v>0.3037190082644628</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.8057553956834532</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4533898305084746</v>
+        <v>0.4534412955465587</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.6355140186915887</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.25</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.09745762711864407</v>
+        <v>0.0931174089068826</v>
       </c>
       <c r="GU14" t="n">
         <v>0.5652173913043478</v>
@@ -10513,77 +10513,77 @@
         <v>0.9230769230769231</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2711864406779661</v>
+        <v>0.2753036437246963</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.34375</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="GY14" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.304932735426009</v>
+        <v>0.3026315789473684</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5661764705882353</v>
+        <v>0.572463768115942</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1098654708520179</v>
+        <v>0.1096491228070175</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.3673469387755102</v>
+        <v>0.38</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.3004484304932735</v>
+        <v>0.2960526315789473</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.2985074626865671</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6770472895040369</v>
+        <v>0.6785518376302797</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.2963752665245202</v>
+        <v>0.298780487804878</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5439556554524362</v>
+        <v>0.5442722007722007</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5534698170731707</v>
+        <v>0.5578744117647059</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5386813926940639</v>
+        <v>0.5379924107142857</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09445037353255069</v>
+        <v>0.09247967479674797</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1452702702702703</v>
+        <v>0.1406628940986257</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.007246376811594203</v>
+        <v>0.01094391244870041</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.174937343358396</v>
+        <v>0.1728571428571428</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2882205513784461</v>
+        <v>0.28</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.882347328244275</v>
+        <v>6.875614194722475</v>
       </c>
       <c r="HQ14" t="n">
-        <v>25.05598227474151</v>
+        <v>25.04083916083916</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2812333864965444</v>
+        <v>0.2745197168857432</v>
       </c>
       <c r="HS14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.01705756929637527</v>
+        <v>0.01626016260162602</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -5751,73 +5751,73 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>46380</v>
+        <v>49260</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>-282</v>
+        <v>-278</v>
       </c>
       <c r="J8" t="n">
-        <v>1541</v>
+        <v>1634</v>
       </c>
       <c r="K8" t="n">
-        <v>1553</v>
+        <v>1645</v>
       </c>
       <c r="L8" t="n">
-        <v>498</v>
+        <v>533</v>
       </c>
       <c r="M8" t="n">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="N8" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="O8" t="n">
-        <v>3094</v>
+        <v>3279</v>
       </c>
       <c r="P8" t="n">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="Q8" t="n">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="R8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S8" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U8" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="V8" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W8" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="X8" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Y8" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="Z8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="AB8" t="n">
         <v>3</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
@@ -5826,10 +5826,10 @@
         <v>39</v>
       </c>
       <c r="AF8" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="n">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="AH8" t="n">
         <v>11</v>
@@ -5838,253 +5838,253 @@
         <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AK8" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="AL8" t="n">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="AM8" t="n">
-        <v>731</v>
+        <v>781</v>
       </c>
       <c r="AN8" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="AO8" t="n">
-        <v>593</v>
+        <v>627</v>
       </c>
       <c r="AP8" t="n">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1607</v>
+        <v>1722</v>
       </c>
       <c r="AR8" t="n">
-        <v>1889</v>
+        <v>2000</v>
       </c>
       <c r="AS8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AT8" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="AU8" t="n">
         <v>14</v>
       </c>
       <c r="AV8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AW8" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AX8" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="AY8" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AZ8" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="BA8" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="BB8" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="BC8" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="BD8" t="n">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="BE8" t="n">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="BF8" t="n">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="BG8" t="n">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="BH8" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="BI8" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="BJ8" t="n">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="BK8" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="BL8" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="BM8" t="n">
         <v>6</v>
       </c>
       <c r="BN8" t="n">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="BO8" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="BP8" t="n">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="BQ8" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="BR8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="BS8" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="BT8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BU8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BV8" t="n">
-        <v>818</v>
+        <v>885</v>
       </c>
       <c r="BW8" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="BX8" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="BY8" t="n">
         <v>4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="CA8" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="CB8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="CC8" t="n">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="CD8" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="CE8" t="n">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="CF8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CG8" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="CH8" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="CI8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="CJ8" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="CK8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CL8" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CM8" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="CN8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CO8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="CP8" t="n">
         <v>6</v>
       </c>
       <c r="CQ8" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="CR8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CS8" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="CT8" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="CU8" t="n">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="CV8" t="n">
         <v>5</v>
       </c>
       <c r="CW8" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="CX8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CY8" t="n">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="CZ8" t="n">
         <v>3</v>
       </c>
       <c r="DA8" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="DB8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DC8" t="n">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="DD8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="DE8" t="n">
         <v>3</v>
       </c>
       <c r="DF8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DG8" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="DH8" t="n">
         <v>8</v>
       </c>
       <c r="DI8" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="DJ8" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="DK8" t="n">
+        <v>8</v>
+      </c>
+      <c r="DL8" t="n">
         <v>6</v>
       </c>
-      <c r="DL8" t="n">
-        <v>5</v>
-      </c>
       <c r="DM8" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DO8" t="n">
         <v>1</v>
@@ -6093,10 +6093,10 @@
         <v>19</v>
       </c>
       <c r="DQ8" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="DR8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="DS8" t="n">
         <v>2</v>
@@ -6105,247 +6105,247 @@
         <v>2</v>
       </c>
       <c r="DU8" t="n">
-        <v>1413</v>
+        <v>1518</v>
       </c>
       <c r="DV8" t="n">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="DW8" t="n">
-        <v>497</v>
+        <v>531</v>
       </c>
       <c r="DX8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="DY8" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.4681933842239186</v>
+        <v>0.4785714285714286</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.5227272727272727</v>
+        <v>0.5317460317460317</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.8379888268156425</v>
+        <v>0.8429319371727748</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.3018549747048904</v>
+        <v>0.3046251993620415</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.2901554404145077</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.3018549747048904</v>
+        <v>0.3046251993620415</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.5376196990424077</v>
+        <v>0.5377720870678617</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.58</v>
+        <v>0.5660377358490566</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.508</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.4996223564954683</v>
+        <v>0.5017755681818182</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.5524475524475524</v>
+        <v>0.5364238410596026</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.4822695035460993</v>
+        <v>0.4779735682819383</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.535427807486631</v>
+        <v>0.5385821831869511</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5642458100558659</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.5201207243460765</v>
+        <v>0.5196261682242991</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.4478851963746224</v>
+        <v>0.4453125</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.01011804384485666</v>
+        <v>0.009569377990430622</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.08481532147742818</v>
+        <v>0.08706786171574904</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.08311688311688312</v>
+        <v>0.08653846153846154</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.10546875</v>
+        <v>0.1078066914498141</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03125</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01273885350318471</v>
+        <v>0.01212121212121212</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.5942622950819673</v>
+        <v>0.5912698412698413</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.82</v>
+        <v>0.8301886792452831</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.6260623229461756</v>
+        <v>0.623342175066313</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.2844311377245509</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.7098765432098766</v>
+        <v>0.7060518731988472</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.245049504950495</v>
+        <v>0.2464788732394366</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.6661742983751846</v>
+        <v>0.6629834254143646</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.2628726287262872</v>
+        <v>0.264367816091954</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3507462686567164</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.24375</v>
+        <v>0.239766081871345</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.2745098039215687</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.239344262295082</v>
+        <v>0.2429906542056075</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.2626262626262627</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="FK8" t="n">
+        <v>0.56875</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0.6392405063291139</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0.7288135593220338</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0.7235772357723578</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0.6633663366336634</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0.02957746478873239</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>95.85383678440925</v>
+      </c>
+      <c r="FR8" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="FL8" t="n">
-        <v>0.6438356164383562</v>
-      </c>
-      <c r="FM8" t="n">
-        <v>0.7090909090909091</v>
-      </c>
-      <c r="FN8" t="n">
-        <v>0.7307692307692307</v>
-      </c>
-      <c r="FO8" t="n">
-        <v>0.6555555555555556</v>
-      </c>
-      <c r="FP8" t="n">
-        <v>0.02831594634873323</v>
-      </c>
-      <c r="FQ8" t="n">
-        <v>96.0620957309185</v>
-      </c>
-      <c r="FR8" t="n">
-        <v>0.5942028985507246</v>
-      </c>
       <c r="FS8" t="n">
-        <v>14.25405580791694</v>
+        <v>14.2703182374541</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.72086284610431</v>
+        <v>15.77039513677811</v>
       </c>
       <c r="FU8" t="n">
-        <v>13.71979234263465</v>
+        <v>13.73947368421053</v>
       </c>
       <c r="FV8" t="n">
-        <v>15.06226658081133</v>
+        <v>15.11197568389058</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.290785498489426</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.6805194805194805</v>
+        <v>0.6778846153846154</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.7422096317280453</v>
+        <v>0.7421052631578947</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.5343511450381679</v>
+        <v>0.5390070921985816</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1933534743202417</v>
+        <v>0.1910511363636364</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.36328125</v>
+        <v>0.3531598513011153</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.4061135371179039</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.3118279569892473</v>
+        <v>0.3263157894736842</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.06797583081570997</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.4367816091954023</v>
+        <v>0.4623655913978494</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.1185800604229607</v>
+        <v>0.1171875</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.3694267515923567</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.3741935483870968</v>
+        <v>0.3680981595092024</v>
       </c>
       <c r="GL8" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="GM8" t="n">
-        <v>0.3293051359516616</v>
+        <v>0.328125</v>
       </c>
       <c r="GN8" t="n">
-        <v>0.2775229357798165</v>
+        <v>0.2835497835497836</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.2800925925925926</v>
+        <v>0.2860262008733624</v>
       </c>
       <c r="GP8" t="n">
-        <v>0.7933884297520661</v>
+        <v>0.8015267175572519</v>
       </c>
       <c r="GQ8" t="n">
-        <v>0.4825174825174825</v>
+        <v>0.4834437086092715</v>
       </c>
       <c r="GR8" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="GS8" t="n">
-        <v>0.1875</v>
+        <v>0.2</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08609271523178808</v>
       </c>
       <c r="GU8" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="GV8" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="GW8" t="n">
-        <v>0.2237762237762238</v>
+        <v>0.2119205298013245</v>
       </c>
       <c r="GX8" t="n">
         <v>0.34375</v>
@@ -6354,68 +6354,68 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="GZ8" t="n">
-        <v>0.2884160756501182</v>
+        <v>0.2973568281938326</v>
       </c>
       <c r="HA8" t="n">
-        <v>0.6557377049180327</v>
+        <v>0.6370370370370371</v>
       </c>
       <c r="HB8" t="n">
-        <v>0.09219858156028368</v>
+        <v>0.08590308370044053</v>
       </c>
       <c r="HC8" t="n">
         <v>0.358974358974359</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.3640661938534279</v>
+        <v>0.3634361233480176</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2787878787878788</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.7386706948640483</v>
+        <v>0.7407670454545454</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.2775229357798165</v>
+        <v>0.2835497835497836</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.5549758358662614</v>
+        <v>0.556605</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.5489912790697674</v>
+        <v>0.5505510869565218</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.5434645432692308</v>
+        <v>0.5447450782997763</v>
       </c>
       <c r="HK8" t="n">
-        <v>0.1115702479338843</v>
+        <v>0.1114711600777706</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.180327868852459</v>
+        <v>0.1800219538968167</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.01337792642140468</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.1207218419415059</v>
+        <v>0.1184668989547038</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.3235843186060983</v>
+        <v>0.3246225319396051</v>
       </c>
       <c r="HP8" t="n">
-        <v>5.979753761969904</v>
+        <v>5.904097311139565</v>
       </c>
       <c r="HQ8" t="n">
-        <v>25.3298126064736</v>
+        <v>25.33558776167472</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.3231667748215444</v>
+        <v>0.3261933904528764</v>
       </c>
       <c r="HS8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="HT8" t="inlineStr"/>
       <c r="HU8" t="n">
-        <v>0.009174311926605505</v>
+        <v>0.008658008658008658</v>
       </c>
     </row>
     <row r="9">
@@ -9921,308 +9921,308 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>58200</v>
+        <v>61080</v>
       </c>
       <c r="H14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" t="n">
-        <v>-174</v>
+        <v>-178</v>
       </c>
       <c r="J14" t="n">
-        <v>1978</v>
+        <v>2069</v>
       </c>
       <c r="K14" t="n">
-        <v>1996</v>
+        <v>2090</v>
       </c>
       <c r="L14" t="n">
-        <v>543</v>
+        <v>570</v>
       </c>
       <c r="M14" t="n">
-        <v>723</v>
+        <v>759</v>
       </c>
       <c r="N14" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="O14" t="n">
-        <v>3974</v>
+        <v>4159</v>
       </c>
       <c r="P14" t="n">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="Q14" t="n">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="R14" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="S14" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T14" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="U14" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="V14" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="W14" t="n">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="X14" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Y14" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="Z14" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA14" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="AB14" t="n">
         <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AD14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AF14" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="AG14" t="n">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AK14" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="AL14" t="n">
-        <v>513</v>
+        <v>540</v>
       </c>
       <c r="AM14" t="n">
-        <v>1099</v>
+        <v>1150</v>
       </c>
       <c r="AN14" t="n">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="AO14" t="n">
-        <v>724</v>
+        <v>761</v>
       </c>
       <c r="AP14" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2100</v>
+        <v>2211</v>
       </c>
       <c r="AR14" t="n">
-        <v>2274</v>
+        <v>2389</v>
       </c>
       <c r="AS14" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="AT14" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="AU14" t="n">
         <v>37</v>
       </c>
       <c r="AV14" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AW14" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="AX14" t="n">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="AY14" t="n">
+        <v>133</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>287</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>67</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>195</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>167</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>634</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>522</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>558</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>651</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>99</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>122</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>512</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>155</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>135</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>261</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>217</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>478</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>125</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>271</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>59</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>185</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>161</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>588</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>508</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>518</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>618</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>93</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>112</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>492</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>147</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>130</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>254</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>206</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>460</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>119</v>
-      </c>
       <c r="BR14" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="BS14" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="BT14" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BU14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BV14" t="n">
-        <v>1126</v>
+        <v>1173</v>
       </c>
       <c r="BW14" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="BX14" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="BY14" t="n">
         <v>5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="CA14" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="CB14" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="CC14" t="n">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="CD14" t="n">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="CE14" t="n">
-        <v>1013</v>
+        <v>1067</v>
       </c>
       <c r="CF14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CG14" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="CH14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="CI14" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="CJ14" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="CK14" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="CL14" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="CM14" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="CN14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CO14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="CR14" t="n">
         <v>35</v>
       </c>
       <c r="CS14" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="CT14" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="CU14" t="n">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="CX14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CY14" t="n">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="CZ14" t="n">
         <v>13</v>
       </c>
       <c r="DA14" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="DB14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="DC14" t="n">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="DD14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="DE14" t="n">
         <v>1</v>
@@ -10231,16 +10231,16 @@
         <v>5</v>
       </c>
       <c r="DG14" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="DH14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DI14" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="DJ14" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="DK14" t="n">
         <v>6</v>
@@ -10249,7 +10249,7 @@
         <v>3</v>
       </c>
       <c r="DM14" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10258,13 +10258,13 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DQ14" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="DR14" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="DS14" t="n">
         <v>3</v>
@@ -10273,317 +10273,317 @@
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1737</v>
+        <v>1827</v>
       </c>
       <c r="DV14" t="n">
-        <v>586</v>
+        <v>632</v>
       </c>
       <c r="DW14" t="n">
-        <v>542</v>
+        <v>569</v>
       </c>
       <c r="DX14" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="DY14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4951267056530214</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5557986870897156</v>
+        <v>0.5448851774530271</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.869198312236287</v>
+        <v>0.868</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3273480662983426</v>
+        <v>0.328515111695138</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.4065934065934066</v>
+        <v>0.3936170212765958</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3189189189189189</v>
+        <v>0.3435897435897436</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.3273480662983426</v>
+        <v>0.328515111695138</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4667879890809827</v>
+        <v>0.4695652173913044</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.6025641025641025</v>
+        <v>0.6035502958579881</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4612546125461255</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.4764125068568294</v>
+        <v>0.478806907378336</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.5988593155893536</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.4682017543859649</v>
+        <v>0.4844398340248963</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5167570231641203</v>
+        <v>0.5190409026798307</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.6413427561837456</v>
+        <v>0.6378737541528239</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5288808664259927</v>
+        <v>0.541095890410959</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3971475589687329</v>
+        <v>0.3982208267922553</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01657458563535912</v>
+        <v>0.01839684625492773</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1182893539581438</v>
+        <v>0.1173913043478261</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1695906432748538</v>
+        <v>0.1713221601489758</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.09223300970873786</v>
+        <v>0.08816705336426914</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.02873563218390805</v>
+        <v>0.02747252747252747</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.01724137931034483</v>
+        <v>0.02008032128514056</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6118881118881119</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.9056603773584906</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.09803921568627451</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6702127659574468</v>
+        <v>0.6713995943204868</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3327586206896552</v>
+        <v>0.3360927152317881</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7244444444444444</v>
+        <v>0.7245762711864406</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2742616033755274</v>
+        <v>0.2776659959758551</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6967391304347826</v>
+        <v>0.6974093264248704</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.3097184377838329</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3856502242152466</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3293650793650794</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.2201834862385321</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2946428571428572</v>
+        <v>0.2988505747126437</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.2246376811594203</v>
+        <v>0.2281879194630873</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.6030150753768844</v>
+        <v>0.6</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.7046632124352331</v>
+        <v>0.7107843137254902</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.7564102564102564</v>
+        <v>0.759493670886076</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7180327868852459</v>
+        <v>0.7165109034267912</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7379310344827587</v>
+        <v>0.7417218543046358</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03497267759562842</v>
+        <v>0.0356020942408377</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.32577319587629</v>
+        <v>98.05108055009823</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.6976744186046512</v>
+        <v>0.6847826086956522</v>
       </c>
       <c r="FS14" t="n">
-        <v>15.13291203235592</v>
+        <v>15.20575157080715</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.16187374749499</v>
+        <v>14.17191387559809</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.38427704752275</v>
+        <v>14.46089898501692</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.59253507014028</v>
+        <v>13.60708133971292</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2814042786615469</v>
+        <v>0.2810047095761382</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5614035087719298</v>
+        <v>0.5661080074487895</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.676056338028169</v>
+        <v>0.6831460674157304</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.53125</v>
+        <v>0.5164473684210527</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2260010970927043</v>
+        <v>0.2255363683935112</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.383495145631068</v>
+        <v>0.382830626450116</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.4224598930481284</v>
+        <v>0.4198473282442748</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.4683544303797468</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.09544706527701591</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.3850574712643678</v>
+        <v>0.3901098901098901</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.3964497041420119</v>
+        <v>0.4011299435028249</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.4029850746268657</v>
+        <v>0.4084507042253521</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1272627537026879</v>
+        <v>0.130298273155416</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3879310344827586</v>
+        <v>0.3815261044176707</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.389344262295082</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.968421052631579</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.269884805266045</v>
+        <v>0.2679225536368394</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.298780487804878</v>
+        <v>0.302734375</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3037190082644628</v>
+        <v>0.3081510934393638</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4534412955465587</v>
+        <v>0.4600760456273764</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6446280991735537</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.0931174089068826</v>
+        <v>0.09505703422053231</v>
       </c>
       <c r="GU14" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.52</v>
       </c>
       <c r="GV14" t="n">
         <v>0.9230769230769231</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2753036437246963</v>
+        <v>0.2623574144486692</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="GY14" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3026315789473684</v>
+        <v>0.3070539419087137</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.572463768115942</v>
+        <v>0.581081081081081</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1096491228070175</v>
+        <v>0.1120331950207469</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.38</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.2960526315789473</v>
+        <v>0.2925311203319502</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.3191489361702128</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6785518376302797</v>
+        <v>0.6792255363683936</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.298780487804878</v>
+        <v>0.302734375</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5442722007722007</v>
+        <v>0.544013229879011</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5578744117647059</v>
+        <v>0.5576074585635359</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5379924107142857</v>
+        <v>0.5382723628691983</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09247967479674797</v>
+        <v>0.09258361609306835</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1406628940986257</v>
+        <v>0.1406491499227202</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.01094391244870041</v>
+        <v>0.011703511053316</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1728571428571428</v>
+        <v>0.1736770691994572</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.28</v>
+        <v>0.2867480777928539</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.875614194722475</v>
+        <v>6.856695652173913</v>
       </c>
       <c r="HQ14" t="n">
-        <v>25.04083916083916</v>
+        <v>25.01635638297872</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2745197168857432</v>
+        <v>0.2754954084098598</v>
       </c>
       <c r="HS14" t="n">
         <v>8</v>
       </c>
       <c r="HT14" t="inlineStr"/>
       <c r="HU14" t="n">
-        <v>0.01626016260162602</v>
+        <v>0.017578125</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -5751,67 +5751,67 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>49260</v>
+        <v>52140</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
-        <v>-278</v>
+        <v>-279</v>
       </c>
       <c r="J8" t="n">
-        <v>1634</v>
+        <v>1727</v>
       </c>
       <c r="K8" t="n">
-        <v>1645</v>
+        <v>1738</v>
       </c>
       <c r="L8" t="n">
-        <v>533</v>
+        <v>573</v>
       </c>
       <c r="M8" t="n">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="N8" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="O8" t="n">
-        <v>3279</v>
+        <v>3465</v>
       </c>
       <c r="P8" t="n">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="Q8" t="n">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="R8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S8" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="T8" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="U8" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="V8" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="W8" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="X8" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Y8" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA8" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="AB8" t="n">
         <v>3</v>
@@ -5820,193 +5820,193 @@
         <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AG8" t="n">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="AH8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="AK8" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="AL8" t="n">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="AM8" t="n">
-        <v>781</v>
+        <v>824</v>
       </c>
       <c r="AN8" t="n">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="AO8" t="n">
-        <v>627</v>
+        <v>670</v>
       </c>
       <c r="AP8" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1722</v>
+        <v>1828</v>
       </c>
       <c r="AR8" t="n">
-        <v>2000</v>
+        <v>2107</v>
       </c>
       <c r="AS8" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AT8" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AU8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV8" t="n">
+        <v>49</v>
+      </c>
+      <c r="AW8" t="n">
         <v>45</v>
       </c>
-      <c r="AW8" t="n">
-        <v>42</v>
-      </c>
       <c r="AX8" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="AY8" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="AZ8" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="BA8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB8" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="BC8" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="BD8" t="n">
-        <v>559</v>
+        <v>601</v>
       </c>
       <c r="BE8" t="n">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="BF8" t="n">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="BG8" t="n">
-        <v>483</v>
+        <v>531</v>
       </c>
       <c r="BH8" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="BI8" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="BJ8" t="n">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="BK8" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="BL8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="BM8" t="n">
         <v>6</v>
       </c>
       <c r="BN8" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="BO8" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="BP8" t="n">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="BQ8" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="BR8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="BS8" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="BT8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BU8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BV8" t="n">
-        <v>885</v>
+        <v>949</v>
       </c>
       <c r="BW8" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BX8" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="BY8" t="n">
         <v>4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="CA8" t="n">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="CB8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="CC8" t="n">
-        <v>524</v>
+        <v>557</v>
       </c>
       <c r="CD8" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="CE8" t="n">
-        <v>735</v>
+        <v>783</v>
       </c>
       <c r="CF8" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="CG8" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="CH8" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="CI8" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="CJ8" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="CK8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CL8" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="CM8" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="CN8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CO8" t="n">
         <v>56</v>
@@ -6015,43 +6015,43 @@
         <v>6</v>
       </c>
       <c r="CQ8" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="CR8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CS8" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="CT8" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="CU8" t="n">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="CV8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CW8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="CX8" t="n">
         <v>22</v>
       </c>
       <c r="CY8" t="n">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="CZ8" t="n">
         <v>3</v>
       </c>
       <c r="DA8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="DB8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DC8" t="n">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="DD8" t="n">
         <v>34</v>
@@ -6060,43 +6060,43 @@
         <v>3</v>
       </c>
       <c r="DF8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DG8" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="DH8" t="n">
         <v>8</v>
       </c>
       <c r="DI8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="DJ8" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="DK8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="DL8" t="n">
         <v>6</v>
       </c>
       <c r="DM8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="DN8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DO8" t="n">
         <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DQ8" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="DR8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="DS8" t="n">
         <v>2</v>
@@ -6105,238 +6105,238 @@
         <v>2</v>
       </c>
       <c r="DU8" t="n">
-        <v>1518</v>
+        <v>1614</v>
       </c>
       <c r="DV8" t="n">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="DW8" t="n">
-        <v>531</v>
+        <v>571</v>
       </c>
       <c r="DX8" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="DY8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.4785714285714286</v>
+        <v>0.4760820045558087</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.5317460317460317</v>
+        <v>0.529113924050633</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.8429319371727748</v>
+        <v>0.8509615384615384</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.3046251993620415</v>
+        <v>0.3104477611940298</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.3061224489795918</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2968036529680365</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.3046251993620415</v>
+        <v>0.3104477611940298</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.5377720870678617</v>
+        <v>0.5327669902912622</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.5660377358490566</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.508</v>
+        <v>0.5093632958801498</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.5017755681818182</v>
+        <v>0.5026773761713521</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.5364238410596026</v>
+        <v>0.5248447204968945</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.4779735682819383</v>
+        <v>0.4804526748971193</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.5385821831869511</v>
+        <v>0.5390532544378698</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.5642458100558659</v>
+        <v>0.5549738219895288</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.5196261682242991</v>
+        <v>0.5218531468531469</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.4453125</v>
+        <v>0.4484605087014726</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.009569377990430622</v>
+        <v>0.008955223880597015</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.08706786171574904</v>
+        <v>0.08737864077669903</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.08653846153846154</v>
+        <v>0.0867579908675799</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.1078066914498141</v>
+        <v>0.1103202846975089</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.03125</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01212121212121212</v>
+        <v>0.01123595505617977</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.5912698412698413</v>
+        <v>0.5871212121212122</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.8301886792452831</v>
+        <v>0.8245614035087719</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06896551724137931</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.623342175066313</v>
+        <v>0.6284289276807981</v>
       </c>
       <c r="FA8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0.7087912087912088</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0.2389380530973451</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0.2668269230769231</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0.3698630136986301</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0.247191011235955</v>
+      </c>
+      <c r="FH8" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="FB8" t="n">
-        <v>0.7060518731988472</v>
-      </c>
-      <c r="FC8" t="n">
-        <v>0.2464788732394366</v>
-      </c>
-      <c r="FD8" t="n">
-        <v>0.6629834254143646</v>
-      </c>
-      <c r="FE8" t="n">
-        <v>0.264367816091954</v>
-      </c>
-      <c r="FF8" t="n">
-        <v>0.3507462686567164</v>
-      </c>
-      <c r="FG8" t="n">
-        <v>0.239766081871345</v>
-      </c>
-      <c r="FH8" t="n">
-        <v>0.2692307692307692</v>
-      </c>
       <c r="FI8" t="n">
-        <v>0.2429906542056075</v>
+        <v>0.2339181286549707</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.2545454545454545</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.56875</v>
+        <v>0.5654761904761905</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.6392405063291139</v>
+        <v>0.6529411764705882</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.7288135593220338</v>
+        <v>0.7301587301587301</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.7235772357723578</v>
+        <v>0.7244094488188977</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.6633663366336634</v>
+        <v>0.6727272727272727</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.02957746478873239</v>
+        <v>0.03841059602649007</v>
       </c>
       <c r="FQ8" t="n">
-        <v>95.85383678440925</v>
+        <v>95.69620253164557</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5875</v>
       </c>
       <c r="FS8" t="n">
-        <v>14.2703182374541</v>
+        <v>14.32565141864505</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.77039513677811</v>
+        <v>15.76501726121979</v>
       </c>
       <c r="FU8" t="n">
-        <v>13.73947368421053</v>
+        <v>13.80011580775912</v>
       </c>
       <c r="FV8" t="n">
-        <v>15.11197568389058</v>
+        <v>15.1078250863061</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.2931726907630522</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.6778846153846154</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.7421052631578947</v>
+        <v>0.73</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.5390070921985816</v>
+        <v>0.5308219178082192</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1910511363636364</v>
+        <v>0.1880856760374833</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.3531598513011153</v>
+        <v>0.3558718861209965</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.3263157894736842</v>
+        <v>0.33</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.07028112449799197</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4476190476190476</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.4623655913978494</v>
+        <v>0.4607843137254902</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.4468085106382979</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.1171875</v>
+        <v>0.1191432396251673</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3820224719101123</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.3680981595092024</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="GL8" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9264705882352942</v>
       </c>
       <c r="GM8" t="n">
-        <v>0.328125</v>
+        <v>0.3293172690763052</v>
       </c>
       <c r="GN8" t="n">
-        <v>0.2835497835497836</v>
+        <v>0.2845528455284553</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.2860262008733624</v>
+        <v>0.2868852459016393</v>
       </c>
       <c r="GP8" t="n">
-        <v>0.8015267175572519</v>
+        <v>0.8142857142857143</v>
       </c>
       <c r="GQ8" t="n">
-        <v>0.4834437086092715</v>
+        <v>0.484472049689441</v>
       </c>
       <c r="GR8" t="n">
-        <v>0.684931506849315</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="GS8" t="n">
-        <v>0.2</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.08609271523178808</v>
+        <v>0.08074534161490683</v>
       </c>
       <c r="GU8" t="n">
         <v>0.2307692307692308</v>
@@ -6345,77 +6345,79 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="GW8" t="n">
-        <v>0.2119205298013245</v>
+        <v>0.2236024844720497</v>
       </c>
       <c r="GX8" t="n">
-        <v>0.34375</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="GY8" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="GZ8" t="n">
-        <v>0.2973568281938326</v>
+        <v>0.2901234567901235</v>
       </c>
       <c r="HA8" t="n">
-        <v>0.6370370370370371</v>
+        <v>0.6382978723404256</v>
       </c>
       <c r="HB8" t="n">
-        <v>0.08590308370044053</v>
+        <v>0.09053497942386832</v>
       </c>
       <c r="HC8" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.3634361233480176</v>
+        <v>0.360082304526749</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2787878787878788</v>
+        <v>0.28</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.7407670454545454</v>
+        <v>0.7416331994645248</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.2835497835497836</v>
+        <v>0.2845528455284553</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.556605</v>
+        <v>0.5568386944818304</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.5505510869565218</v>
+        <v>0.5513232323232323</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.5447450782997763</v>
+        <v>0.5438168058455115</v>
       </c>
       <c r="HK8" t="n">
-        <v>0.1114711600777706</v>
+        <v>0.1094132029339853</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.1800219538968167</v>
+        <v>0.1779396462018731</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.01265822784810127</v>
+        <v>0.01185185185185185</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.1184668989547038</v>
+        <v>0.1170678336980306</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.3246225319396051</v>
+        <v>0.3287746170678337</v>
       </c>
       <c r="HP8" t="n">
-        <v>5.904097311139565</v>
+        <v>5.924271844660194</v>
       </c>
       <c r="HQ8" t="n">
-        <v>25.33558776167472</v>
+        <v>25.31069277108434</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.3261933904528764</v>
+        <v>0.3317892298784019</v>
       </c>
       <c r="HS8" t="n">
-        <v>4</v>
-      </c>
-      <c r="HT8" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="HT8" t="n">
+        <v>1</v>
+      </c>
       <c r="HU8" t="n">
-        <v>0.008658008658008658</v>
+        <v>0.008130081300813009</v>
       </c>
     </row>
     <row r="9">
@@ -9921,326 +9923,326 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>61080</v>
+        <v>63960</v>
       </c>
       <c r="H14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" t="n">
-        <v>-178</v>
+        <v>-177</v>
       </c>
       <c r="J14" t="n">
-        <v>2069</v>
+        <v>2161</v>
       </c>
       <c r="K14" t="n">
-        <v>2090</v>
+        <v>2184</v>
       </c>
       <c r="L14" t="n">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="M14" t="n">
-        <v>759</v>
+        <v>800</v>
       </c>
       <c r="N14" t="n">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="O14" t="n">
-        <v>4159</v>
+        <v>4345</v>
       </c>
       <c r="P14" t="n">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="Q14" t="n">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="R14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="S14" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="T14" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="U14" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="V14" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="W14" t="n">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="X14" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Y14" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="Z14" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="AA14" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AD14" t="n">
         <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AF14" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="n">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AJ14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK14" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AL14" t="n">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="AM14" t="n">
-        <v>1150</v>
+        <v>1196</v>
       </c>
       <c r="AN14" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="AO14" t="n">
-        <v>761</v>
+        <v>793</v>
       </c>
       <c r="AP14" t="n">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2211</v>
+        <v>2318</v>
       </c>
       <c r="AR14" t="n">
-        <v>2389</v>
+        <v>2495</v>
       </c>
       <c r="AS14" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AT14" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AU14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AV14" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AW14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AX14" t="n">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="AY14" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AZ14" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="BA14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BB14" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="BC14" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="BD14" t="n">
-        <v>634</v>
+        <v>656</v>
       </c>
       <c r="BE14" t="n">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="BF14" t="n">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="BG14" t="n">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="BH14" t="n">
         <v>99</v>
       </c>
       <c r="BI14" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BJ14" t="n">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="BK14" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="BL14" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BM14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN14" t="n">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="BO14" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="BP14" t="n">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="BQ14" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="BR14" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="BT14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BU14" t="n">
         <v>29</v>
       </c>
       <c r="BV14" t="n">
-        <v>1173</v>
+        <v>1234</v>
       </c>
       <c r="BW14" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="BX14" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="BY14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BZ14" t="n">
+        <v>365</v>
+      </c>
+      <c r="CA14" t="n">
         <v>342</v>
       </c>
-      <c r="CA14" t="n">
-        <v>331</v>
-      </c>
       <c r="CB14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="CC14" t="n">
-        <v>721</v>
+        <v>757</v>
       </c>
       <c r="CD14" t="n">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="CE14" t="n">
-        <v>1067</v>
+        <v>1115</v>
       </c>
       <c r="CF14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CG14" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="CH14" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="CI14" t="n">
         <v>88</v>
       </c>
       <c r="CJ14" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="CK14" t="n">
         <v>34</v>
       </c>
       <c r="CL14" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="CM14" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="CN14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CO14" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="CR14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="CS14" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="CT14" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="CU14" t="n">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="CX14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CY14" t="n">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="CZ14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DA14" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="DB14" t="n">
         <v>38</v>
       </c>
       <c r="DC14" t="n">
-        <v>483</v>
+        <v>511</v>
       </c>
       <c r="DD14" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="DE14" t="n">
         <v>1</v>
       </c>
       <c r="DF14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DG14" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="DH14" t="n">
         <v>9</v>
       </c>
       <c r="DI14" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="DJ14" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="DK14" t="n">
         <v>6</v>
@@ -10249,7 +10251,7 @@
         <v>3</v>
       </c>
       <c r="DM14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10258,13 +10260,13 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="DQ14" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="DR14" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="DS14" t="n">
         <v>3</v>
@@ -10273,317 +10275,319 @@
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1827</v>
+        <v>1920</v>
       </c>
       <c r="DV14" t="n">
-        <v>632</v>
+        <v>654</v>
       </c>
       <c r="DW14" t="n">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="DX14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="DY14" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.4795008912655971</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5448851774530271</v>
+        <v>0.5401606425702812</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.868</v>
+        <v>0.8754716981132076</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.328515111695138</v>
+        <v>0.3341740226986128</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.3936170212765958</v>
+        <v>0.4</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3435897435897436</v>
+        <v>0.3366336633663367</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.328515111695138</v>
+        <v>0.3341740226986128</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4695652173913044</v>
+        <v>0.4690635451505017</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.6035502958579881</v>
+        <v>0.6011560693641619</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4662162162162162</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.478806907378336</v>
+        <v>0.4819004524886878</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.5988593155893536</v>
+        <v>0.6007326007326007</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.4844398340248963</v>
+        <v>0.4819277108433735</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5190409026798307</v>
+        <v>0.5218764095624718</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.6378737541528239</v>
+        <v>0.639871382636656</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.541095890410959</v>
+        <v>0.5378912685337727</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3982208267922553</v>
+        <v>0.3986928104575164</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01839684625492773</v>
+        <v>0.0201765447667087</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1173913043478261</v>
+        <v>0.1145484949832776</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1713221601489758</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.08816705336426914</v>
+        <v>0.08705357142857142</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.02747252747252747</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.02008032128514056</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6118881118881119</v>
+        <v>0.6146179401993356</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.1090909090909091</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6713995943204868</v>
+        <v>0.6627906976744186</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3360927152317881</v>
+        <v>0.3343949044585987</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7245762711864406</v>
+        <v>0.7329317269076305</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2776659959758551</v>
+        <v>0.2762645914396887</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6974093264248704</v>
+        <v>0.6972386587771203</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.3097184377838329</v>
+        <v>0.308231173380035</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.397489539748954</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2201834862385321</v>
+        <v>0.2212389380530974</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2988505747126437</v>
+        <v>0.2977528089887641</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.2281879194630873</v>
+        <v>0.2278481012658228</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.6</v>
+        <v>0.5900900900900901</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.7107843137254902</v>
+        <v>0.7061611374407583</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.759493670886076</v>
+        <v>0.7469879518072289</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7165109034267912</v>
+        <v>0.7280701754385965</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7417218543046358</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0356020942408377</v>
+        <v>0.03629032258064516</v>
       </c>
       <c r="FQ14" t="n">
-        <v>98.05108055009823</v>
+        <v>97.82363977485929</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.6847826086956522</v>
+        <v>0.6875</v>
       </c>
       <c r="FS14" t="n">
-        <v>15.20575157080715</v>
+        <v>15.23276260990282</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.17191387559809</v>
+        <v>14.21336996336996</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.46089898501692</v>
+        <v>14.49227209625174</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.60708133971292</v>
+        <v>13.65444139194139</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2810047095761382</v>
+        <v>0.2805429864253394</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.5661080074487895</v>
+        <v>0.568100358422939</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6831460674157304</v>
+        <v>0.6817204301075269</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.5164473684210527</v>
+        <v>0.5173501577287066</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2255363683935112</v>
+        <v>0.2252388134741076</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.382830626450116</v>
+        <v>0.3772321428571428</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.4198473282442748</v>
+        <v>0.4132029339853301</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4497041420118343</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.0955253896430367</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.3901098901098901</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.4011299435028249</v>
+        <v>0.4054054054054054</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.4084507042253521</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.130298273155416</v>
+        <v>0.1337355455002514</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.3815261044176707</v>
+        <v>0.387218045112782</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.389344262295082</v>
+        <v>0.3976833976833977</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.968421052631579</v>
+        <v>0.970873786407767</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.2679225536368394</v>
+        <v>0.264957264957265</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.302734375</v>
+        <v>0.3074003795066413</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3081510934393638</v>
+        <v>0.3127413127413127</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4600760456273764</v>
+        <v>0.4578754578754579</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.6446280991735537</v>
+        <v>0.64</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2625</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.09505703422053231</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="GU14" t="n">
-        <v>0.52</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="GV14" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2623574144486692</v>
+        <v>0.2673992673992674</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="GY14" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3070539419087137</v>
+        <v>0.3032128514056225</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.581081081081081</v>
+        <v>0.5894039735099338</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1120331950207469</v>
+        <v>0.1144578313253012</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.3859649122807017</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.2925311203319502</v>
+        <v>0.2911646586345382</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3191489361702128</v>
+        <v>0.3172413793103449</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6792255363683936</v>
+        <v>0.6792357968828557</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.302734375</v>
+        <v>0.3074003795066413</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.544013229879011</v>
+        <v>0.5437941889843355</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5576074585635359</v>
+        <v>0.5561423684210527</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5382723628691983</v>
+        <v>0.5381666326530612</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09258361609306835</v>
+        <v>0.09357541899441341</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1406491499227202</v>
+        <v>0.1425389755011136</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.011703511053316</v>
+        <v>0.01123595505617977</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1736770691994572</v>
+        <v>0.1716997411561691</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2867480777928539</v>
+        <v>0.2830025884383089</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.856695652173913</v>
+        <v>6.877508361204013</v>
       </c>
       <c r="HQ14" t="n">
-        <v>25.01635638297872</v>
+        <v>24.99604591836735</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2754954084098598</v>
+        <v>0.2739472466450718</v>
       </c>
       <c r="HS14" t="n">
         <v>8</v>
       </c>
-      <c r="HT14" t="inlineStr"/>
+      <c r="HT14" t="n">
+        <v>1</v>
+      </c>
       <c r="HU14" t="n">
-        <v>0.017578125</v>
+        <v>0.01707779886148008</v>
       </c>
     </row>
     <row r="15">

--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -5751,307 +5751,307 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>52140</v>
+        <v>55020</v>
       </c>
       <c r="H8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>-279</v>
+        <v>-283</v>
       </c>
       <c r="J8" t="n">
-        <v>1727</v>
+        <v>1817</v>
       </c>
       <c r="K8" t="n">
-        <v>1738</v>
+        <v>1827</v>
       </c>
       <c r="L8" t="n">
-        <v>573</v>
+        <v>595</v>
       </c>
       <c r="M8" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="N8" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="O8" t="n">
-        <v>3465</v>
+        <v>3644</v>
       </c>
       <c r="P8" t="n">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="Q8" t="n">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="R8" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="S8" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="T8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U8" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V8" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="W8" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="X8" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Y8" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="Z8" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AA8" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="AB8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD8" t="n">
         <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AF8" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AG8" t="n">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="AH8" t="n">
         <v>12</v>
       </c>
       <c r="AI8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AJ8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK8" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AL8" t="n">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="AM8" t="n">
-        <v>824</v>
+        <v>873</v>
       </c>
       <c r="AN8" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="AO8" t="n">
-        <v>670</v>
+        <v>708</v>
       </c>
       <c r="AP8" t="n">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1828</v>
+        <v>1918</v>
       </c>
       <c r="AR8" t="n">
-        <v>2107</v>
+        <v>2201</v>
       </c>
       <c r="AS8" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="AT8" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="AU8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AW8" t="n">
         <v>45</v>
       </c>
       <c r="AX8" t="n">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="AY8" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="AZ8" t="n">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="BA8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BB8" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="BC8" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BD8" t="n">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="BE8" t="n">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="BF8" t="n">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="BG8" t="n">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="BH8" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="BI8" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="BK8" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="BL8" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="BM8" t="n">
         <v>6</v>
       </c>
       <c r="BN8" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="BO8" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="BP8" t="n">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="BQ8" t="n">
+        <v>120</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>67</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>160</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>995</v>
+      </c>
+      <c r="BW8" t="n">
         <v>114</v>
       </c>
-      <c r="BR8" t="n">
-        <v>63</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>155</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>33</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>949</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>108</v>
-      </c>
       <c r="BX8" t="n">
+        <v>124</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>275</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>268</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>49</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>592</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>243</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>835</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>31</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>135</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>81</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>54</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>163</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>27</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>102</v>
+      </c>
+      <c r="CM8" t="n">
         <v>114</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>258</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>252</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>47</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>557</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>226</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>783</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>29</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>129</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>78</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>51</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>155</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>25</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>99</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>109</v>
       </c>
       <c r="CN8" t="n">
         <v>22</v>
       </c>
       <c r="CO8" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="CP8" t="n">
         <v>6</v>
       </c>
       <c r="CQ8" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="CR8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CS8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="CT8" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="CU8" t="n">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="CV8" t="n">
         <v>6</v>
       </c>
       <c r="CW8" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="CX8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CY8" t="n">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="CZ8" t="n">
         <v>3</v>
       </c>
       <c r="DA8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="DB8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="DC8" t="n">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="DD8" t="n">
         <v>34</v>
@@ -6063,352 +6063,352 @@
         <v>8</v>
       </c>
       <c r="DG8" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="DH8" t="n">
         <v>8</v>
       </c>
       <c r="DI8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="DJ8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="DK8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="DL8" t="n">
         <v>6</v>
       </c>
       <c r="DM8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="DN8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="DO8" t="n">
         <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="DQ8" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="DR8" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="DS8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DT8" t="n">
         <v>2</v>
       </c>
       <c r="DU8" t="n">
-        <v>1614</v>
+        <v>1687</v>
       </c>
       <c r="DV8" t="n">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="DW8" t="n">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="DX8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="DY8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.4760820045558087</v>
+        <v>0.4717391304347826</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.529113924050633</v>
+        <v>0.5254237288135594</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.8509615384615384</v>
+        <v>0.85</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.3104477611940298</v>
+        <v>0.3107344632768362</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.3061224489795918</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.2968036529680365</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.3104477611940298</v>
+        <v>0.3107344632768362</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.5327669902912622</v>
+        <v>0.5269186712485682</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.5535714285714286</v>
+        <v>0.5564516129032258</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.5093632958801498</v>
+        <v>0.5071428571428571</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.5026773761713521</v>
+        <v>0.4996837444655282</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.5248447204968945</v>
+        <v>0.5284090909090909</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.4804526748971193</v>
+        <v>0.4744094488188976</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.5390532544378698</v>
+        <v>0.5352743561030235</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.5549738219895288</v>
+        <v>0.5558252427184466</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.5218531468531469</v>
+        <v>0.5142140468227425</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.4484605087014726</v>
+        <v>0.4478178368121442</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.008955223880597015</v>
+        <v>0.008474576271186441</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.08737864077669903</v>
+        <v>0.08705612829324169</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0867579908675799</v>
+        <v>0.08441558441558442</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.1103202846975089</v>
+        <v>0.1140939597315436</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.02654867256637168</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01123595505617977</v>
+        <v>0.01036269430051814</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.5871212121212122</v>
+        <v>0.5884476534296029</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.8245614035087719</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.6284289276807981</v>
+        <v>0.6218097447795824</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.3</v>
+        <v>0.3046683046683047</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.7087912087912088</v>
+        <v>0.7087628865979382</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.2389380530973451</v>
+        <v>0.2389937106918239</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.663003663003663</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.2668269230769231</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3694267515923567</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.247191011235955</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2786885245901639</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.2339181286549707</v>
+        <v>0.2408963585434174</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.2545454545454545</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.5654761904761905</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.6529411764705882</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.7301587301587301</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.7244094488188977</v>
+        <v>0.7185185185185186</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.6727272727272727</v>
+        <v>0.6864406779661016</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.03841059602649007</v>
+        <v>0.03860523038605231</v>
       </c>
       <c r="FQ8" t="n">
-        <v>95.69620253164557</v>
+        <v>95.37186477644492</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.5875</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="FS8" t="n">
-        <v>14.32565141864505</v>
+        <v>14.33935057787562</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.76501726121979</v>
+        <v>15.85407772304324</v>
       </c>
       <c r="FU8" t="n">
-        <v>13.80011580775912</v>
+        <v>13.78574573472757</v>
       </c>
       <c r="FV8" t="n">
-        <v>15.1078250863061</v>
+        <v>15.15703338806787</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.2931726907630522</v>
+        <v>0.2922201138519924</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.658008658008658</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.73</v>
+        <v>0.7186761229314421</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.5308219178082192</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1880856760374833</v>
+        <v>0.1884882985452245</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.3558718861209965</v>
+        <v>0.3557046979865772</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.4</v>
+        <v>0.4015151515151515</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.33</v>
+        <v>0.3207547169811321</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.07028112449799197</v>
+        <v>0.07147375079063883</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.4476190476190476</v>
+        <v>0.4424778761061947</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.4607843137254902</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.4468085106382979</v>
+        <v>0.46</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.1191432396251673</v>
+        <v>0.1220746363061354</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.3820224719101123</v>
+        <v>0.3782383419689119</v>
       </c>
       <c r="GK8" t="n">
-        <v>0.3863636363636364</v>
+        <v>0.3821989528795812</v>
       </c>
       <c r="GL8" t="n">
-        <v>0.9264705882352942</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="GM8" t="n">
-        <v>0.3293172690763052</v>
+        <v>0.3257432005060089</v>
       </c>
       <c r="GN8" t="n">
-        <v>0.2845528455284553</v>
+        <v>0.2854368932038835</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.2868852459016393</v>
+        <v>0.2876712328767123</v>
       </c>
       <c r="GP8" t="n">
-        <v>0.8142857142857143</v>
+        <v>0.8163265306122449</v>
       </c>
       <c r="GQ8" t="n">
-        <v>0.484472049689441</v>
+        <v>0.4943181818181818</v>
       </c>
       <c r="GR8" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="GS8" t="n">
-        <v>0.1923076923076923</v>
+        <v>0.1896551724137931</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.08074534161490683</v>
+        <v>0.08522727272727272</v>
       </c>
       <c r="GU8" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="GV8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="GW8" t="n">
-        <v>0.2236024844720497</v>
+        <v>0.2102272727272727</v>
       </c>
       <c r="GX8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3243243243243243</v>
       </c>
       <c r="GY8" t="n">
         <v>0.9166666666666666</v>
       </c>
       <c r="GZ8" t="n">
-        <v>0.2901234567901235</v>
+        <v>0.2893700787401575</v>
       </c>
       <c r="HA8" t="n">
-        <v>0.6382978723404256</v>
+        <v>0.6258503401360545</v>
       </c>
       <c r="HB8" t="n">
-        <v>0.09053497942386832</v>
+        <v>0.09251968503937008</v>
       </c>
       <c r="HC8" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3404255319148936</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.360082304526749</v>
+        <v>0.3562992125984252</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.28</v>
+        <v>0.2762430939226519</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.7416331994645248</v>
+        <v>0.7400379506641366</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.2845528455284553</v>
+        <v>0.2854368932038835</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.5568386944818304</v>
+        <v>0.5563166348600509</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.5513232323232323</v>
+        <v>0.5501689189189189</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.5438168058455115</v>
+        <v>0.5427064</v>
       </c>
       <c r="HK8" t="n">
-        <v>0.1094132029339853</v>
+        <v>0.107514450867052</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.1779396462018731</v>
+        <v>0.1750245821042281</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.01185185185185185</v>
+        <v>0.01122019635343618</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.1170678336980306</v>
+        <v>0.1204379562043796</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.3287746170678337</v>
+        <v>0.3227320125130344</v>
       </c>
       <c r="HP8" t="n">
-        <v>5.924271844660194</v>
+        <v>5.950400916380298</v>
       </c>
       <c r="HQ8" t="n">
-        <v>25.31069277108434</v>
+        <v>25.30128388017118</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.3317892298784019</v>
+        <v>0.3274628508530545</v>
       </c>
       <c r="HS8" t="n">
         <v>5</v>
@@ -6417,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="HU8" t="n">
-        <v>0.008130081300813009</v>
+        <v>0.007766990291262136</v>
       </c>
     </row>
     <row r="9">
@@ -9923,305 +9923,305 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>63960</v>
+        <v>66840</v>
       </c>
       <c r="H14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" t="n">
-        <v>-177</v>
+        <v>-173</v>
       </c>
       <c r="J14" t="n">
-        <v>2161</v>
+        <v>2250</v>
       </c>
       <c r="K14" t="n">
-        <v>2184</v>
+        <v>2274</v>
       </c>
       <c r="L14" t="n">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="M14" t="n">
-        <v>800</v>
+        <v>822</v>
       </c>
       <c r="N14" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="O14" t="n">
-        <v>4345</v>
+        <v>4524</v>
       </c>
       <c r="P14" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="Q14" t="n">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="R14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S14" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="T14" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U14" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="V14" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="W14" t="n">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="X14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Y14" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="Z14" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AA14" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="AB14" t="n">
         <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD14" t="n">
         <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AF14" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="n">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AL14" t="n">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="AM14" t="n">
-        <v>1196</v>
+        <v>1246</v>
       </c>
       <c r="AN14" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AO14" t="n">
-        <v>793</v>
+        <v>830</v>
       </c>
       <c r="AP14" t="n">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2318</v>
+        <v>2412</v>
       </c>
       <c r="AR14" t="n">
-        <v>2495</v>
+        <v>2585</v>
       </c>
       <c r="AS14" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AT14" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="AU14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV14" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AW14" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>412</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>143</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>310</v>
+      </c>
+      <c r="BA14" t="n">
         <v>70</v>
       </c>
-      <c r="AX14" t="n">
-        <v>398</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>138</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>296</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>68</v>
-      </c>
       <c r="BB14" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="BC14" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="BD14" t="n">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="BE14" t="n">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="BF14" t="n">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="BG14" t="n">
-        <v>696</v>
+        <v>723</v>
       </c>
       <c r="BH14" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="BI14" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BJ14" t="n">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="BK14" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="BL14" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="BM14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BN14" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="BO14" t="n">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="BP14" t="n">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="BQ14" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="BR14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BS14" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BT14" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BU14" t="n">
         <v>29</v>
       </c>
       <c r="BV14" t="n">
-        <v>1234</v>
+        <v>1271</v>
       </c>
       <c r="BW14" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="BX14" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="BY14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BZ14" t="n">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="CA14" t="n">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="CB14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="CC14" t="n">
-        <v>757</v>
+        <v>794</v>
       </c>
       <c r="CD14" t="n">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="CE14" t="n">
-        <v>1115</v>
+        <v>1174</v>
       </c>
       <c r="CF14" t="n">
         <v>36</v>
       </c>
       <c r="CG14" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="CH14" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="CI14" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="CJ14" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="CK14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CL14" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="CM14" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="CN14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CO14" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="CP14" t="n">
         <v>3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="CR14" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="CS14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="CT14" t="n">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="CU14" t="n">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="CX14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CY14" t="n">
-        <v>484</v>
+        <v>506</v>
       </c>
       <c r="CZ14" t="n">
         <v>14</v>
       </c>
       <c r="DA14" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="DB14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="DC14" t="n">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="DD14" t="n">
         <v>41</v>
@@ -10233,16 +10233,16 @@
         <v>6</v>
       </c>
       <c r="DG14" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DH14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="DI14" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="DJ14" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="DK14" t="n">
         <v>6</v>
@@ -10251,7 +10251,7 @@
         <v>3</v>
       </c>
       <c r="DM14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="DN14" t="n">
         <v>3</v>
@@ -10260,325 +10260,325 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="DQ14" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="DR14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="DS14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DT14" t="n">
         <v>1</v>
       </c>
       <c r="DU14" t="n">
-        <v>1920</v>
+        <v>2000</v>
       </c>
       <c r="DV14" t="n">
-        <v>654</v>
+        <v>676</v>
       </c>
       <c r="DW14" t="n">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="DX14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="DY14" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.4795008912655971</v>
+        <v>0.4724137931034483</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.5401606425702812</v>
+        <v>0.5310077519379846</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8754716981132076</v>
+        <v>0.8700361010830325</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.3341740226986128</v>
+        <v>0.3337349397590361</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.4</v>
+        <v>0.3980582524271845</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.3366336633663367</v>
+        <v>0.3349282296650718</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.3341740226986128</v>
+        <v>0.3337349397590361</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.4690635451505017</v>
+        <v>0.4654895666131621</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.6011560693641619</v>
+        <v>0.5824175824175825</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.4662162162162162</v>
+        <v>0.4612903225806452</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.4819004524886878</v>
+        <v>0.4795279383429673</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.6007326007326007</v>
+        <v>0.5877192982456141</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.4819277108433735</v>
+        <v>0.4778420038535646</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.5218764095624718</v>
+        <v>0.5198618307426598</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.639871382636656</v>
+        <v>0.6299694189602446</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.5378912685337727</v>
+        <v>0.5347003154574133</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.3986928104575164</v>
+        <v>0.3998073217726397</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0201765447667087</v>
+        <v>0.02168674698795181</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.1145484949832776</v>
+        <v>0.1139646869983949</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1649484536082474</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.08705357142857142</v>
+        <v>0.08817204301075268</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.02512562814070352</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.03260869565217391</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.6146179401993356</v>
+        <v>0.6063492063492063</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.1090909090909091</v>
+        <v>0.1206896551724138</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.6627906976744186</v>
+        <v>0.6611418047882136</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.3343949044585987</v>
+        <v>0.3404255319148936</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.7329317269076305</v>
+        <v>0.734225621414914</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.2762645914396887</v>
+        <v>0.2769516728624535</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.6972386587771203</v>
+        <v>0.6969981238273921</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.308231173380035</v>
+        <v>0.3118729096989967</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.397489539748954</v>
+        <v>0.3937007874015748</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.3260869565217391</v>
+        <v>0.3356643356643357</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.2212389380530974</v>
+        <v>0.2372881355932203</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.2977528089887641</v>
+        <v>0.3010752688172043</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.2278481012658228</v>
+        <v>0.2228915662650602</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.5900900900900901</v>
+        <v>0.592274678111588</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.7061611374407583</v>
+        <v>0.6981981981981982</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.7469879518072289</v>
+        <v>0.75</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.7280701754385965</v>
+        <v>0.7226890756302521</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.7590361445783133</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.03629032258064516</v>
+        <v>0.03464870067372473</v>
       </c>
       <c r="FQ14" t="n">
-        <v>97.82363977485929</v>
+        <v>97.46499102333932</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.6875</v>
+        <v>0.67</v>
       </c>
       <c r="FS14" t="n">
-        <v>15.23276260990282</v>
+        <v>15.32613333333333</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.21336996336996</v>
+        <v>14.2287598944591</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.49227209625174</v>
+        <v>14.55657777777778</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.65444139194139</v>
+        <v>13.64872471416007</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.2805429864253394</v>
+        <v>0.2803468208092486</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.568100358422939</v>
+        <v>0.5601374570446735</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.6817204301075269</v>
+        <v>0.6707818930041153</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.5173501577287066</v>
+        <v>0.50920245398773</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.2252388134741076</v>
+        <v>0.2239884393063584</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.3772321428571428</v>
+        <v>0.378494623655914</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.4132029339853301</v>
+        <v>0.4150943396226415</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.4497041420118343</v>
+        <v>0.4488636363636364</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0955253896430367</v>
+        <v>0.09585741811175337</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.3919597989949749</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.4054054054054054</v>
+        <v>0.4020618556701031</v>
       </c>
       <c r="GH14" t="n">
-        <v>0.3866666666666667</v>
+        <v>0.3717948717948718</v>
       </c>
       <c r="GI14" t="n">
-        <v>0.1337355455002514</v>
+        <v>0.1329479768786127</v>
       </c>
       <c r="GJ14" t="n">
-        <v>0.387218045112782</v>
+        <v>0.3804347826086957</v>
       </c>
       <c r="GK14" t="n">
-        <v>0.3976833976833977</v>
+        <v>0.3932584269662922</v>
       </c>
       <c r="GL14" t="n">
-        <v>0.970873786407767</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="GM14" t="n">
-        <v>0.264957264957265</v>
+        <v>0.266859344894027</v>
       </c>
       <c r="GN14" t="n">
-        <v>0.3074003795066413</v>
+        <v>0.3104693140794224</v>
       </c>
       <c r="GO14" t="n">
-        <v>0.3127413127413127</v>
+        <v>0.3155963302752294</v>
       </c>
       <c r="GP14" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.8081395348837209</v>
       </c>
       <c r="GQ14" t="n">
-        <v>0.4578754578754579</v>
+        <v>0.4631578947368421</v>
       </c>
       <c r="GR14" t="n">
-        <v>0.64</v>
+        <v>0.6212121212121212</v>
       </c>
       <c r="GS14" t="n">
-        <v>0.2625</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="GT14" t="n">
-        <v>0.0989010989010989</v>
+        <v>0.09824561403508772</v>
       </c>
       <c r="GU14" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.5</v>
       </c>
       <c r="GV14" t="n">
         <v>0.9285714285714286</v>
       </c>
       <c r="GW14" t="n">
-        <v>0.2673992673992674</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="GX14" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.36</v>
       </c>
       <c r="GY14" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="GZ14" t="n">
-        <v>0.3032128514056225</v>
+        <v>0.3044315992292871</v>
       </c>
       <c r="HA14" t="n">
-        <v>0.5894039735099338</v>
+        <v>0.5759493670886076</v>
       </c>
       <c r="HB14" t="n">
-        <v>0.1144578313253012</v>
+        <v>0.1136801541425819</v>
       </c>
       <c r="HC14" t="n">
-        <v>0.3859649122807017</v>
+        <v>0.3728813559322034</v>
       </c>
       <c r="HD14" t="n">
-        <v>0.2911646586345382</v>
+        <v>0.2890173410404624</v>
       </c>
       <c r="HE14" t="n">
-        <v>0.3172413793103449</v>
+        <v>0.32</v>
       </c>
       <c r="HF14" t="n">
-        <v>0.6792357968828557</v>
+        <v>0.6801541425818882</v>
       </c>
       <c r="HG14" t="n">
-        <v>0.3074003795066413</v>
+        <v>0.3104693140794224</v>
       </c>
       <c r="HH14" t="n">
-        <v>0.5437941889843355</v>
+        <v>0.5431715150048403</v>
       </c>
       <c r="HI14" t="n">
-        <v>0.5561423684210527</v>
+        <v>0.5543529850746268</v>
       </c>
       <c r="HJ14" t="n">
-        <v>0.5381666326530612</v>
+        <v>0.5374737769080234</v>
       </c>
       <c r="HK14" t="n">
-        <v>0.09357541899441341</v>
+        <v>0.0927743086529884</v>
       </c>
       <c r="HL14" t="n">
-        <v>0.1425389755011136</v>
+        <v>0.1399000713775874</v>
       </c>
       <c r="HM14" t="n">
-        <v>0.01123595505617977</v>
+        <v>0.01426872770511296</v>
       </c>
       <c r="HN14" t="n">
-        <v>0.1716997411561691</v>
+        <v>0.1708126036484245</v>
       </c>
       <c r="HO14" t="n">
-        <v>0.2830025884383089</v>
+        <v>0.2823383084577115</v>
       </c>
       <c r="HP14" t="n">
-        <v>6.877508361204013</v>
+        <v>6.886837881219904</v>
       </c>
       <c r="HQ14" t="n">
-        <v>24.99604591836735</v>
+        <v>25.01705237515225</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2739472466450718</v>
+        <v>0.2733333333333333</v>
       </c>
       <c r="HS14" t="n">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1</v>
       </c>
       <c r="HU14" t="n">
-        <v>0.01707779886148008</v>
+        <v>0.01624548736462094</v>
       </c>
     </row>
     <row r="15">
